--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,16 @@
           <t>espn_fantasy_pts</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>vlahakis</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>williams</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -566,6 +576,8 @@
       <c r="R2" t="n">
         <v>117</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,6 +636,8 @@
       <c r="R3" t="n">
         <v>113</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -682,6 +696,8 @@
       <c r="R4" t="n">
         <v>117</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -740,6 +756,8 @@
       <c r="R5" t="n">
         <v>117</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -798,6 +816,8 @@
       <c r="R6" t="n">
         <v>114</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -856,6 +876,8 @@
       <c r="R7" t="n">
         <v>106</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -914,6 +936,8 @@
       <c r="R8" t="n">
         <v>93</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -972,6 +996,8 @@
       <c r="R9" t="n">
         <v>91</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1030,6 +1056,8 @@
       <c r="R10" t="n">
         <v>88</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1088,6 +1116,8 @@
       <c r="R11" t="n">
         <v>113</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1146,6 +1176,8 @@
       <c r="R12" t="n">
         <v>90</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1204,6 +1236,8 @@
       <c r="R13" t="n">
         <v>112</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1262,6 +1296,8 @@
       <c r="R14" t="n">
         <v>89</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1320,6 +1356,8 @@
       <c r="R15" t="n">
         <v>91</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1378,6 +1416,8 @@
       <c r="R16" t="n">
         <v>94</v>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1436,6 +1476,8 @@
       <c r="R17" t="n">
         <v>86</v>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1494,6 +1536,8 @@
       <c r="R18" t="n">
         <v>91</v>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1552,6 +1596,8 @@
       <c r="R19" t="n">
         <v>87</v>
       </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1610,6 +1656,8 @@
       <c r="R20" t="n">
         <v>88</v>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1668,6 +1716,8 @@
       <c r="R21" t="n">
         <v>97</v>
       </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1726,6 +1776,8 @@
       <c r="R22" t="n">
         <v>97</v>
       </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1784,6 +1836,8 @@
       <c r="R23" t="n">
         <v>91</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1842,6 +1896,8 @@
       <c r="R24" t="n">
         <v>66</v>
       </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1900,6 +1956,8 @@
       <c r="R25" t="n">
         <v>81</v>
       </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1958,6 +2016,8 @@
       <c r="R26" t="n">
         <v>87</v>
       </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2016,6 +2076,8 @@
       <c r="R27" t="n">
         <v>86</v>
       </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2074,6 +2136,8 @@
       <c r="R28" t="n">
         <v>96</v>
       </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2132,6 +2196,8 @@
       <c r="R29" t="n">
         <v>91</v>
       </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2190,6 +2256,8 @@
       <c r="R30" t="n">
         <v>91</v>
       </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2248,6 +2316,8 @@
       <c r="R31" t="n">
         <v>95</v>
       </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2306,6 +2376,8 @@
       <c r="R32" t="n">
         <v>86</v>
       </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2364,6 +2436,8 @@
       <c r="R33" t="n">
         <v>88</v>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2376,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K545"/>
+  <dimension ref="A1:M545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2435,6 +2509,16 @@
           <t>fantasy_pts</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>fantasy_pts_floor</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fantasy_pts_ceiling</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2474,6 +2558,12 @@
       <c r="K2" t="n">
         <v>5.541</v>
       </c>
+      <c r="L2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26.066</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2513,6 +2603,12 @@
       <c r="K3" t="n">
         <v>4.497</v>
       </c>
+      <c r="L3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>26.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2552,6 +2648,12 @@
       <c r="K4" t="n">
         <v>5.087</v>
       </c>
+      <c r="L4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24.972</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2591,6 +2693,12 @@
       <c r="K5" t="n">
         <v>4.416</v>
       </c>
+      <c r="L5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22.224</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2630,6 +2738,12 @@
       <c r="K6" t="n">
         <v>4.862</v>
       </c>
+      <c r="L6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24.208</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2669,6 +2783,12 @@
       <c r="K7" t="n">
         <v>4.395</v>
       </c>
+      <c r="L7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22.386</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2708,6 +2828,12 @@
       <c r="K8" t="n">
         <v>5.343</v>
       </c>
+      <c r="L8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>28.268</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2747,6 +2873,12 @@
       <c r="K9" t="n">
         <v>4.959</v>
       </c>
+      <c r="L9" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27.542</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2786,6 +2918,12 @@
       <c r="K10" t="n">
         <v>4.367</v>
       </c>
+      <c r="L10" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>23.32</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2825,6 +2963,12 @@
       <c r="K11" t="n">
         <v>4.493</v>
       </c>
+      <c r="L11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25.566</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2864,6 +3008,12 @@
       <c r="K12" t="n">
         <v>4.444</v>
       </c>
+      <c r="L12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2903,6 +3053,12 @@
       <c r="K13" t="n">
         <v>5.651</v>
       </c>
+      <c r="L13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>29.298</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2942,6 +3098,12 @@
       <c r="K14" t="n">
         <v>4.641</v>
       </c>
+      <c r="L14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25.692</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2981,6 +3143,12 @@
       <c r="K15" t="n">
         <v>5.083</v>
       </c>
+      <c r="L15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27.946</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3020,6 +3188,12 @@
       <c r="K16" t="n">
         <v>5.215</v>
       </c>
+      <c r="L16" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25.156</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3059,6 +3233,12 @@
       <c r="K17" t="n">
         <v>4.816</v>
       </c>
+      <c r="L17" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27.022</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3098,6 +3278,12 @@
       <c r="K18" t="n">
         <v>5.208</v>
       </c>
+      <c r="L18" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28.192</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3137,6 +3323,12 @@
       <c r="K19" t="n">
         <v>6.011</v>
       </c>
+      <c r="L19" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30.14</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3176,6 +3368,12 @@
       <c r="K20" t="n">
         <v>6.154</v>
       </c>
+      <c r="L20" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30.404</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3215,6 +3413,12 @@
       <c r="K21" t="n">
         <v>6.293</v>
       </c>
+      <c r="L21" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>27.974</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3254,6 +3458,12 @@
       <c r="K22" t="n">
         <v>6.256</v>
       </c>
+      <c r="L22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>30.552</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3293,6 +3503,12 @@
       <c r="K23" t="n">
         <v>6.377</v>
       </c>
+      <c r="L23" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>30.66</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3332,6 +3548,12 @@
       <c r="K24" t="n">
         <v>5.929</v>
       </c>
+      <c r="L24" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>29.938</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3371,6 +3593,12 @@
       <c r="K25" t="n">
         <v>6.24</v>
       </c>
+      <c r="L25" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>30.572</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3410,6 +3638,12 @@
       <c r="K26" t="n">
         <v>5.729</v>
       </c>
+      <c r="L26" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M26" t="n">
+        <v>29.418</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3449,6 +3683,12 @@
       <c r="K27" t="n">
         <v>6.121</v>
       </c>
+      <c r="L27" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>30.214</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3488,6 +3728,12 @@
       <c r="K28" t="n">
         <v>5.72</v>
       </c>
+      <c r="L28" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29.392</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3527,6 +3773,12 @@
       <c r="K29" t="n">
         <v>5.635</v>
       </c>
+      <c r="L29" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>29.25</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3566,6 +3818,12 @@
       <c r="K30" t="n">
         <v>6.016</v>
       </c>
+      <c r="L30" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>29.954</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3605,6 +3863,12 @@
       <c r="K31" t="n">
         <v>5.82</v>
       </c>
+      <c r="L31" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>29.692</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3644,6 +3908,12 @@
       <c r="K32" t="n">
         <v>6.17</v>
       </c>
+      <c r="L32" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>30.492</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3683,6 +3953,12 @@
       <c r="K33" t="n">
         <v>5.943</v>
       </c>
+      <c r="L33" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M33" t="n">
+        <v>29.828</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3722,6 +3998,12 @@
       <c r="K34" t="n">
         <v>6.531</v>
       </c>
+      <c r="L34" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>31.082</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3761,6 +4043,12 @@
       <c r="K35" t="n">
         <v>6.054</v>
       </c>
+      <c r="L35" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M35" t="n">
+        <v>30.214</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3800,6 +4088,12 @@
       <c r="K36" t="n">
         <v>6.613</v>
       </c>
+      <c r="L36" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>30.776</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3839,6 +4133,12 @@
       <c r="K37" t="n">
         <v>7.516</v>
       </c>
+      <c r="L37" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M37" t="n">
+        <v>30.418</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3878,6 +4178,12 @@
       <c r="K38" t="n">
         <v>6.168</v>
       </c>
+      <c r="L38" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>29.696</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3917,6 +4223,12 @@
       <c r="K39" t="n">
         <v>6.645</v>
       </c>
+      <c r="L39" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>30.932</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3956,6 +4268,12 @@
       <c r="K40" t="n">
         <v>5.984</v>
       </c>
+      <c r="L40" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>29.474</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3995,6 +4313,12 @@
       <c r="K41" t="n">
         <v>6.137</v>
       </c>
+      <c r="L41" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M41" t="n">
+        <v>29.748</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4034,6 +4358,12 @@
       <c r="K42" t="n">
         <v>6.333</v>
       </c>
+      <c r="L42" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M42" t="n">
+        <v>30.082</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4073,6 +4403,12 @@
       <c r="K43" t="n">
         <v>6.373</v>
       </c>
+      <c r="L43" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M43" t="n">
+        <v>28.16</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4112,6 +4448,12 @@
       <c r="K44" t="n">
         <v>6.738</v>
       </c>
+      <c r="L44" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>28.818</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4151,6 +4493,12 @@
       <c r="K45" t="n">
         <v>7.985</v>
       </c>
+      <c r="L45" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>31.578</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4190,6 +4538,12 @@
       <c r="K46" t="n">
         <v>6.068</v>
       </c>
+      <c r="L46" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M46" t="n">
+        <v>29.614</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4229,6 +4583,12 @@
       <c r="K47" t="n">
         <v>6.81</v>
       </c>
+      <c r="L47" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M47" t="n">
+        <v>28.898</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4268,6 +4628,12 @@
       <c r="K48" t="n">
         <v>6.805</v>
       </c>
+      <c r="L48" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M48" t="n">
+        <v>28.91</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4307,6 +4673,12 @@
       <c r="K49" t="n">
         <v>6.126</v>
       </c>
+      <c r="L49" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M49" t="n">
+        <v>29.796</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4346,6 +4718,12 @@
       <c r="K50" t="n">
         <v>7.234</v>
       </c>
+      <c r="L50" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M50" t="n">
+        <v>29.918</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4385,6 +4763,12 @@
       <c r="K51" t="n">
         <v>6.217</v>
       </c>
+      <c r="L51" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M51" t="n">
+        <v>29.902</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4424,6 +4808,12 @@
       <c r="K52" t="n">
         <v>7.227</v>
       </c>
+      <c r="L52" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M52" t="n">
+        <v>29.976</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4463,6 +4853,12 @@
       <c r="K53" t="n">
         <v>5.561</v>
       </c>
+      <c r="L53" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M53" t="n">
+        <v>29.11</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4502,6 +4898,12 @@
       <c r="K54" t="n">
         <v>5.603</v>
       </c>
+      <c r="L54" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M54" t="n">
+        <v>29.19</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4541,6 +4943,12 @@
       <c r="K55" t="n">
         <v>6.29</v>
       </c>
+      <c r="L55" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M55" t="n">
+        <v>30.764</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4580,6 +4988,12 @@
       <c r="K56" t="n">
         <v>6.438</v>
       </c>
+      <c r="L56" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M56" t="n">
+        <v>28.76</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4619,6 +5033,12 @@
       <c r="K57" t="n">
         <v>4.862</v>
       </c>
+      <c r="L57" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M57" t="n">
+        <v>27.692</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4658,6 +5078,12 @@
       <c r="K58" t="n">
         <v>5.468</v>
       </c>
+      <c r="L58" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M58" t="n">
+        <v>28.89</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4697,6 +5123,12 @@
       <c r="K59" t="n">
         <v>5.81</v>
       </c>
+      <c r="L59" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>29.504</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4736,6 +5168,12 @@
       <c r="K60" t="n">
         <v>5.212</v>
       </c>
+      <c r="L60" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M60" t="n">
+        <v>28.382</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4775,6 +5213,12 @@
       <c r="K61" t="n">
         <v>5.607</v>
       </c>
+      <c r="L61" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>29.368</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4814,6 +5258,12 @@
       <c r="K62" t="n">
         <v>5.462</v>
       </c>
+      <c r="L62" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M62" t="n">
+        <v>29.064</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4853,6 +5303,12 @@
       <c r="K63" t="n">
         <v>6.26</v>
       </c>
+      <c r="L63" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M63" t="n">
+        <v>28.45</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4892,6 +5348,12 @@
       <c r="K64" t="n">
         <v>5.343</v>
       </c>
+      <c r="L64" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M64" t="n">
+        <v>28.59</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4931,6 +5393,12 @@
       <c r="K65" t="n">
         <v>5.981</v>
       </c>
+      <c r="L65" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M65" t="n">
+        <v>30.354</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4970,6 +5438,12 @@
       <c r="K66" t="n">
         <v>5.615</v>
       </c>
+      <c r="L66" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M66" t="n">
+        <v>29.3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5009,6 +5483,12 @@
       <c r="K67" t="n">
         <v>5.881</v>
       </c>
+      <c r="L67" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M67" t="n">
+        <v>29.85</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5048,6 +5528,12 @@
       <c r="K68" t="n">
         <v>5.34</v>
       </c>
+      <c r="L68" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M68" t="n">
+        <v>28.834</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5087,6 +5573,12 @@
       <c r="K69" t="n">
         <v>6.765</v>
       </c>
+      <c r="L69" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M69" t="n">
+        <v>29.658</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5126,6 +5618,12 @@
       <c r="K70" t="n">
         <v>5.358</v>
       </c>
+      <c r="L70" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>29.45</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5165,6 +5663,12 @@
       <c r="K71" t="n">
         <v>5.315</v>
       </c>
+      <c r="L71" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M71" t="n">
+        <v>29.41</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5204,6 +5708,12 @@
       <c r="K72" t="n">
         <v>5.184</v>
       </c>
+      <c r="L72" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M72" t="n">
+        <v>29.056</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5243,6 +5753,12 @@
       <c r="K73" t="n">
         <v>5.229</v>
       </c>
+      <c r="L73" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M73" t="n">
+        <v>29.014</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5282,6 +5798,12 @@
       <c r="K74" t="n">
         <v>5.041</v>
       </c>
+      <c r="L74" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M74" t="n">
+        <v>28.698</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5321,6 +5843,12 @@
       <c r="K75" t="n">
         <v>5.282</v>
       </c>
+      <c r="L75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M75" t="n">
+        <v>29.166</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5360,6 +5888,12 @@
       <c r="K76" t="n">
         <v>4.818</v>
       </c>
+      <c r="L76" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>27.802</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5399,6 +5933,12 @@
       <c r="K77" t="n">
         <v>5.679</v>
       </c>
+      <c r="L77" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M77" t="n">
+        <v>30.086</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5438,6 +5978,12 @@
       <c r="K78" t="n">
         <v>5.593</v>
       </c>
+      <c r="L78" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M78" t="n">
+        <v>29.908</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5477,6 +6023,12 @@
       <c r="K79" t="n">
         <v>5.46</v>
       </c>
+      <c r="L79" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>29.424</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5516,6 +6068,12 @@
       <c r="K80" t="n">
         <v>5.102</v>
       </c>
+      <c r="L80" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M80" t="n">
+        <v>28.806</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5555,6 +6113,12 @@
       <c r="K81" t="n">
         <v>4.877</v>
       </c>
+      <c r="L81" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M81" t="n">
+        <v>28.292</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5594,6 +6158,12 @@
       <c r="K82" t="n">
         <v>5.781</v>
       </c>
+      <c r="L82" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M82" t="n">
+        <v>30.278</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5633,6 +6203,12 @@
       <c r="K83" t="n">
         <v>5.722</v>
       </c>
+      <c r="L83" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M83" t="n">
+        <v>30.198</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5672,6 +6248,12 @@
       <c r="K84" t="n">
         <v>5.473</v>
       </c>
+      <c r="L84" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M84" t="n">
+        <v>29.748</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5711,6 +6293,12 @@
       <c r="K85" t="n">
         <v>4.681</v>
       </c>
+      <c r="L85" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M85" t="n">
+        <v>27.826</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5750,6 +6338,12 @@
       <c r="K86" t="n">
         <v>5.434</v>
       </c>
+      <c r="L86" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M86" t="n">
+        <v>29.64</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5789,6 +6383,12 @@
       <c r="K87" t="n">
         <v>5.46</v>
       </c>
+      <c r="L87" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M87" t="n">
+        <v>28.894</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5828,6 +6428,12 @@
       <c r="K88" t="n">
         <v>5.182</v>
       </c>
+      <c r="L88" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M88" t="n">
+        <v>28.102</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5867,6 +6473,12 @@
       <c r="K89" t="n">
         <v>5.105</v>
       </c>
+      <c r="L89" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M89" t="n">
+        <v>27.936</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5906,6 +6518,12 @@
       <c r="K90" t="n">
         <v>5.761</v>
       </c>
+      <c r="L90" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M90" t="n">
+        <v>29.634</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5945,6 +6563,12 @@
       <c r="K91" t="n">
         <v>5.838</v>
       </c>
+      <c r="L91" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>29.918</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5984,6 +6608,12 @@
       <c r="K92" t="n">
         <v>5.595</v>
       </c>
+      <c r="L92" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M92" t="n">
+        <v>29.274</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6023,6 +6653,12 @@
       <c r="K93" t="n">
         <v>5.333</v>
       </c>
+      <c r="L93" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M93" t="n">
+        <v>28.37</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6062,6 +6698,12 @@
       <c r="K94" t="n">
         <v>4.758</v>
       </c>
+      <c r="L94" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M94" t="n">
+        <v>27.352</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6101,6 +6743,12 @@
       <c r="K95" t="n">
         <v>5.36</v>
       </c>
+      <c r="L95" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M95" t="n">
+        <v>28.53</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6140,6 +6788,12 @@
       <c r="K96" t="n">
         <v>6.121</v>
       </c>
+      <c r="L96" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M96" t="n">
+        <v>30.246</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6179,6 +6833,12 @@
       <c r="K97" t="n">
         <v>5.237</v>
       </c>
+      <c r="L97" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M97" t="n">
+        <v>28.264</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6218,6 +6878,12 @@
       <c r="K98" t="n">
         <v>5.279</v>
       </c>
+      <c r="L98" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M98" t="n">
+        <v>28.354</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6257,6 +6923,12 @@
       <c r="K99" t="n">
         <v>5.231</v>
       </c>
+      <c r="L99" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M99" t="n">
+        <v>28.46</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6296,6 +6968,12 @@
       <c r="K100" t="n">
         <v>4.764</v>
       </c>
+      <c r="L100" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M100" t="n">
+        <v>27.288</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6335,6 +7013,12 @@
       <c r="K101" t="n">
         <v>5.996</v>
       </c>
+      <c r="L101" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M101" t="n">
+        <v>30.208</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6374,6 +7058,12 @@
       <c r="K102" t="n">
         <v>5.444</v>
       </c>
+      <c r="L102" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M102" t="n">
+        <v>28.664</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6413,6 +7103,12 @@
       <c r="K103" t="n">
         <v>5.074</v>
       </c>
+      <c r="L103" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M103" t="n">
+        <v>27.922</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6452,6 +7148,12 @@
       <c r="K104" t="n">
         <v>5.126</v>
       </c>
+      <c r="L104" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M104" t="n">
+        <v>27.53</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6491,6 +7193,12 @@
       <c r="K105" t="n">
         <v>5.015</v>
       </c>
+      <c r="L105" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M105" t="n">
+        <v>23.272</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6530,6 +7238,12 @@
       <c r="K106" t="n">
         <v>5.331</v>
       </c>
+      <c r="L106" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M106" t="n">
+        <v>25.16</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6569,6 +7283,12 @@
       <c r="K107" t="n">
         <v>5.041</v>
       </c>
+      <c r="L107" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M107" t="n">
+        <v>24.41</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6608,6 +7328,12 @@
       <c r="K108" t="n">
         <v>4.886</v>
       </c>
+      <c r="L108" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M108" t="n">
+        <v>24.146</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6647,6 +7373,12 @@
       <c r="K109" t="n">
         <v>5.185</v>
       </c>
+      <c r="L109" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M109" t="n">
+        <v>24.588</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6686,6 +7418,12 @@
       <c r="K110" t="n">
         <v>5.765</v>
       </c>
+      <c r="L110" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M110" t="n">
+        <v>29.148</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6725,6 +7463,12 @@
       <c r="K111" t="n">
         <v>5.178</v>
       </c>
+      <c r="L111" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M111" t="n">
+        <v>27.666</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6764,6 +7508,12 @@
       <c r="K112" t="n">
         <v>5.425</v>
       </c>
+      <c r="L112" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>28.34</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6803,6 +7553,12 @@
       <c r="K113" t="n">
         <v>5.807</v>
       </c>
+      <c r="L113" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M113" t="n">
+        <v>29.302</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6842,6 +7598,12 @@
       <c r="K114" t="n">
         <v>5.692</v>
       </c>
+      <c r="L114" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M114" t="n">
+        <v>25.798</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6881,6 +7643,12 @@
       <c r="K115" t="n">
         <v>5.053</v>
       </c>
+      <c r="L115" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M115" t="n">
+        <v>26.486</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6920,6 +7688,12 @@
       <c r="K116" t="n">
         <v>4.824</v>
       </c>
+      <c r="L116" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M116" t="n">
+        <v>26.996</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6959,6 +7733,12 @@
       <c r="K117" t="n">
         <v>5.178</v>
       </c>
+      <c r="L117" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M117" t="n">
+        <v>27.706</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6998,6 +7778,12 @@
       <c r="K118" t="n">
         <v>5.794</v>
       </c>
+      <c r="L118" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M118" t="n">
+        <v>26.018</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7037,6 +7823,12 @@
       <c r="K119" t="n">
         <v>5.297</v>
       </c>
+      <c r="L119" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M119" t="n">
+        <v>27.788</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7076,6 +7868,12 @@
       <c r="K120" t="n">
         <v>5.143</v>
       </c>
+      <c r="L120" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M120" t="n">
+        <v>26.666</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7115,6 +7913,12 @@
       <c r="K121" t="n">
         <v>5.637</v>
       </c>
+      <c r="L121" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M121" t="n">
+        <v>29.822</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7154,6 +7958,12 @@
       <c r="K122" t="n">
         <v>5.348</v>
       </c>
+      <c r="L122" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M122" t="n">
+        <v>29.228</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7193,6 +8003,12 @@
       <c r="K123" t="n">
         <v>5.853</v>
       </c>
+      <c r="L123" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M123" t="n">
+        <v>30.312</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7232,6 +8048,12 @@
       <c r="K124" t="n">
         <v>5.891</v>
       </c>
+      <c r="L124" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M124" t="n">
+        <v>30.572</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7271,6 +8093,12 @@
       <c r="K125" t="n">
         <v>5.661</v>
       </c>
+      <c r="L125" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M125" t="n">
+        <v>30.08</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7310,6 +8138,12 @@
       <c r="K126" t="n">
         <v>5.767</v>
       </c>
+      <c r="L126" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M126" t="n">
+        <v>29.976</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7349,6 +8183,12 @@
       <c r="K127" t="n">
         <v>5.961</v>
       </c>
+      <c r="L127" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M127" t="n">
+        <v>30.908</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7388,6 +8228,12 @@
       <c r="K128" t="n">
         <v>5.78</v>
       </c>
+      <c r="L128" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M128" t="n">
+        <v>30.372</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7427,6 +8273,12 @@
       <c r="K129" t="n">
         <v>6.26</v>
       </c>
+      <c r="L129" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M129" t="n">
+        <v>31.264</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7466,6 +8318,12 @@
       <c r="K130" t="n">
         <v>5.836</v>
       </c>
+      <c r="L130" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M130" t="n">
+        <v>30.226</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7505,6 +8363,12 @@
       <c r="K131" t="n">
         <v>5.497</v>
       </c>
+      <c r="L131" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M131" t="n">
+        <v>29.314</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7544,6 +8408,12 @@
       <c r="K132" t="n">
         <v>6.11</v>
       </c>
+      <c r="L132" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M132" t="n">
+        <v>30.884</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7583,6 +8453,12 @@
       <c r="K133" t="n">
         <v>5.888</v>
       </c>
+      <c r="L133" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M133" t="n">
+        <v>30.464</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7622,6 +8498,12 @@
       <c r="K134" t="n">
         <v>5.22</v>
       </c>
+      <c r="L134" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>28.816</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7661,6 +8543,12 @@
       <c r="K135" t="n">
         <v>5.632</v>
       </c>
+      <c r="L135" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M135" t="n">
+        <v>29.736</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7700,6 +8588,12 @@
       <c r="K136" t="n">
         <v>6.383</v>
       </c>
+      <c r="L136" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M136" t="n">
+        <v>31.538</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7739,6 +8633,12 @@
       <c r="K137" t="n">
         <v>5.963</v>
       </c>
+      <c r="L137" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M137" t="n">
+        <v>30.624</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7778,6 +8678,12 @@
       <c r="K138" t="n">
         <v>4.317</v>
       </c>
+      <c r="L138" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M138" t="n">
+        <v>21.746</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7817,6 +8723,12 @@
       <c r="K139" t="n">
         <v>5.852</v>
       </c>
+      <c r="L139" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M139" t="n">
+        <v>29.902</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7856,6 +8768,12 @@
       <c r="K140" t="n">
         <v>5.13</v>
       </c>
+      <c r="L140" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M140" t="n">
+        <v>27.522</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7895,6 +8813,12 @@
       <c r="K141" t="n">
         <v>4.809</v>
       </c>
+      <c r="L141" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M141" t="n">
+        <v>22.924</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7934,6 +8858,12 @@
       <c r="K142" t="n">
         <v>4.693</v>
       </c>
+      <c r="L142" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M142" t="n">
+        <v>26.69</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7973,6 +8903,12 @@
       <c r="K143" t="n">
         <v>5.171</v>
       </c>
+      <c r="L143" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M143" t="n">
+        <v>28.018</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8012,6 +8948,12 @@
       <c r="K144" t="n">
         <v>4.532</v>
       </c>
+      <c r="L144" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M144" t="n">
+        <v>25.25</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8051,6 +8993,12 @@
       <c r="K145" t="n">
         <v>5.003</v>
       </c>
+      <c r="L145" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M145" t="n">
+        <v>27.308</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8090,6 +9038,12 @@
       <c r="K146" t="n">
         <v>5.488</v>
       </c>
+      <c r="L146" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M146" t="n">
+        <v>25.772</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8129,6 +9083,12 @@
       <c r="K147" t="n">
         <v>5.437</v>
       </c>
+      <c r="L147" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M147" t="n">
+        <v>28.878</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8168,6 +9128,12 @@
       <c r="K148" t="n">
         <v>5.422</v>
       </c>
+      <c r="L148" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M148" t="n">
+        <v>28.594</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8207,6 +9173,12 @@
       <c r="K149" t="n">
         <v>4.597</v>
       </c>
+      <c r="L149" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M149" t="n">
+        <v>25.37</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8246,6 +9218,12 @@
       <c r="K150" t="n">
         <v>4.144</v>
       </c>
+      <c r="L150" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M150" t="n">
+        <v>22.532</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8285,6 +9263,12 @@
       <c r="K151" t="n">
         <v>4.164</v>
       </c>
+      <c r="L151" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M151" t="n">
+        <v>21.594</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8324,6 +9308,12 @@
       <c r="K152" t="n">
         <v>4.826</v>
       </c>
+      <c r="L152" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M152" t="n">
+        <v>27.006</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8363,6 +9353,12 @@
       <c r="K153" t="n">
         <v>4.412</v>
       </c>
+      <c r="L153" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M153" t="n">
+        <v>21.916</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8402,6 +9398,12 @@
       <c r="K154" t="n">
         <v>5.716</v>
       </c>
+      <c r="L154" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M154" t="n">
+        <v>29.652</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8441,6 +9443,12 @@
       <c r="K155" t="n">
         <v>5.609</v>
       </c>
+      <c r="L155" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M155" t="n">
+        <v>29.102</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8480,6 +9488,12 @@
       <c r="K156" t="n">
         <v>6.952</v>
       </c>
+      <c r="L156" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M156" t="n">
+        <v>32.822</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8519,6 +9533,12 @@
       <c r="K157" t="n">
         <v>6.308</v>
       </c>
+      <c r="L157" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M157" t="n">
+        <v>31.488</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8558,6 +9578,12 @@
       <c r="K158" t="n">
         <v>5.938</v>
       </c>
+      <c r="L158" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M158" t="n">
+        <v>29.954</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8597,6 +9623,12 @@
       <c r="K159" t="n">
         <v>6.902</v>
       </c>
+      <c r="L159" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M159" t="n">
+        <v>32.226</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8636,6 +9668,12 @@
       <c r="K160" t="n">
         <v>5.626</v>
       </c>
+      <c r="L160" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M160" t="n">
+        <v>29.526</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8675,6 +9713,12 @@
       <c r="K161" t="n">
         <v>6.077</v>
       </c>
+      <c r="L161" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M161" t="n">
+        <v>30.044</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8714,6 +9758,12 @@
       <c r="K162" t="n">
         <v>6.685</v>
       </c>
+      <c r="L162" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M162" t="n">
+        <v>29.232</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8753,6 +9803,12 @@
       <c r="K163" t="n">
         <v>6.073</v>
       </c>
+      <c r="L163" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M163" t="n">
+        <v>30.152</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8792,6 +9848,12 @@
       <c r="K164" t="n">
         <v>5.741</v>
       </c>
+      <c r="L164" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M164" t="n">
+        <v>29.214</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8831,6 +9893,12 @@
       <c r="K165" t="n">
         <v>6.119</v>
       </c>
+      <c r="L165" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M165" t="n">
+        <v>30.462</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8870,6 +9938,12 @@
       <c r="K166" t="n">
         <v>6.681</v>
       </c>
+      <c r="L166" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M166" t="n">
+        <v>29.394</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8909,6 +9983,12 @@
       <c r="K167" t="n">
         <v>5.928</v>
       </c>
+      <c r="L167" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M167" t="n">
+        <v>29.97</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8948,6 +10028,12 @@
       <c r="K168" t="n">
         <v>5.626</v>
       </c>
+      <c r="L168" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M168" t="n">
+        <v>29.024</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8987,6 +10073,12 @@
       <c r="K169" t="n">
         <v>6.285</v>
       </c>
+      <c r="L169" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M169" t="n">
+        <v>31.42</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9026,6 +10118,12 @@
       <c r="K170" t="n">
         <v>6.89</v>
       </c>
+      <c r="L170" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M170" t="n">
+        <v>29.662</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9065,6 +10163,12 @@
       <c r="K171" t="n">
         <v>7.035</v>
       </c>
+      <c r="L171" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M171" t="n">
+        <v>32.446</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9104,6 +10208,12 @@
       <c r="K172" t="n">
         <v>6.409</v>
       </c>
+      <c r="L172" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M172" t="n">
+        <v>30.014</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9143,6 +10253,12 @@
       <c r="K173" t="n">
         <v>5.195</v>
       </c>
+      <c r="L173" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M173" t="n">
+        <v>27.52</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9182,6 +10298,12 @@
       <c r="K174" t="n">
         <v>6.04</v>
       </c>
+      <c r="L174" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M174" t="n">
+        <v>29.324</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9221,6 +10343,12 @@
       <c r="K175" t="n">
         <v>5.879</v>
       </c>
+      <c r="L175" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M175" t="n">
+        <v>28.97</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9260,6 +10388,12 @@
       <c r="K176" t="n">
         <v>5.798</v>
       </c>
+      <c r="L176" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M176" t="n">
+        <v>28.678</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9299,6 +10433,12 @@
       <c r="K177" t="n">
         <v>6.129</v>
       </c>
+      <c r="L177" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M177" t="n">
+        <v>29.512</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9338,6 +10478,12 @@
       <c r="K178" t="n">
         <v>5.615</v>
       </c>
+      <c r="L178" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M178" t="n">
+        <v>28.384</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9377,6 +10523,12 @@
       <c r="K179" t="n">
         <v>5.526</v>
       </c>
+      <c r="L179" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M179" t="n">
+        <v>28.272</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9416,6 +10568,12 @@
       <c r="K180" t="n">
         <v>5.767</v>
       </c>
+      <c r="L180" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M180" t="n">
+        <v>28.594</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9455,6 +10613,12 @@
       <c r="K181" t="n">
         <v>5.791</v>
       </c>
+      <c r="L181" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M181" t="n">
+        <v>28.704</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9494,6 +10658,12 @@
       <c r="K182" t="n">
         <v>6.137</v>
       </c>
+      <c r="L182" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M182" t="n">
+        <v>29.906</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9533,6 +10703,12 @@
       <c r="K183" t="n">
         <v>5.891</v>
       </c>
+      <c r="L183" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M183" t="n">
+        <v>28.99</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9572,6 +10748,12 @@
       <c r="K184" t="n">
         <v>6.265</v>
       </c>
+      <c r="L184" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M184" t="n">
+        <v>29.846</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9611,6 +10793,12 @@
       <c r="K185" t="n">
         <v>5.529</v>
       </c>
+      <c r="L185" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M185" t="n">
+        <v>28.244</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9650,6 +10838,12 @@
       <c r="K186" t="n">
         <v>5.448</v>
       </c>
+      <c r="L186" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M186" t="n">
+        <v>27.902</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9689,6 +10883,12 @@
       <c r="K187" t="n">
         <v>6.07</v>
       </c>
+      <c r="L187" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M187" t="n">
+        <v>28.796</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9728,6 +10928,12 @@
       <c r="K188" t="n">
         <v>6.029</v>
       </c>
+      <c r="L188" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M188" t="n">
+        <v>29.352</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9767,6 +10973,12 @@
       <c r="K189" t="n">
         <v>4.803</v>
       </c>
+      <c r="L189" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M189" t="n">
+        <v>27.324</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9806,6 +11018,12 @@
       <c r="K190" t="n">
         <v>5.227</v>
       </c>
+      <c r="L190" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M190" t="n">
+        <v>28.364</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9845,6 +11063,12 @@
       <c r="K191" t="n">
         <v>5.258</v>
       </c>
+      <c r="L191" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M191" t="n">
+        <v>28.32</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9884,6 +11108,12 @@
       <c r="K192" t="n">
         <v>4.962</v>
       </c>
+      <c r="L192" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M192" t="n">
+        <v>27.714</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9923,6 +11153,12 @@
       <c r="K193" t="n">
         <v>5.48</v>
       </c>
+      <c r="L193" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M193" t="n">
+        <v>29.236</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9962,6 +11198,12 @@
       <c r="K194" t="n">
         <v>5.206</v>
       </c>
+      <c r="L194" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M194" t="n">
+        <v>28.14</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10001,6 +11243,12 @@
       <c r="K195" t="n">
         <v>5.048</v>
       </c>
+      <c r="L195" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M195" t="n">
+        <v>27.832</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10040,6 +11288,12 @@
       <c r="K196" t="n">
         <v>5.289</v>
       </c>
+      <c r="L196" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M196" t="n">
+        <v>28.42</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10079,6 +11333,12 @@
       <c r="K197" t="n">
         <v>4.966</v>
       </c>
+      <c r="L197" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M197" t="n">
+        <v>27.604</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10118,6 +11378,12 @@
       <c r="K198" t="n">
         <v>4.914</v>
       </c>
+      <c r="L198" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M198" t="n">
+        <v>27.524</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10157,6 +11423,12 @@
       <c r="K199" t="n">
         <v>4.501</v>
       </c>
+      <c r="L199" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M199" t="n">
+        <v>26.692</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10196,6 +11468,12 @@
       <c r="K200" t="n">
         <v>5.484</v>
       </c>
+      <c r="L200" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M200" t="n">
+        <v>28.854</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10235,6 +11513,12 @@
       <c r="K201" t="n">
         <v>4.53</v>
       </c>
+      <c r="L201" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M201" t="n">
+        <v>26.67</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10274,6 +11558,12 @@
       <c r="K202" t="n">
         <v>4.992</v>
       </c>
+      <c r="L202" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M202" t="n">
+        <v>27.772</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10313,6 +11603,12 @@
       <c r="K203" t="n">
         <v>5.384</v>
       </c>
+      <c r="L203" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M203" t="n">
+        <v>29.066</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10352,6 +11648,12 @@
       <c r="K204" t="n">
         <v>5.247</v>
       </c>
+      <c r="L204" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M204" t="n">
+        <v>28.214</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10391,6 +11693,12 @@
       <c r="K205" t="n">
         <v>5.209</v>
       </c>
+      <c r="L205" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M205" t="n">
+        <v>28.122</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10430,6 +11738,12 @@
       <c r="K206" t="n">
         <v>6.626</v>
       </c>
+      <c r="L206" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M206" t="n">
+        <v>29.41</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10469,6 +11783,12 @@
       <c r="K207" t="n">
         <v>7.31</v>
       </c>
+      <c r="L207" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M207" t="n">
+        <v>30.706</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10508,6 +11828,12 @@
       <c r="K208" t="n">
         <v>6.498</v>
       </c>
+      <c r="L208" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M208" t="n">
+        <v>31.296</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10547,6 +11873,12 @@
       <c r="K209" t="n">
         <v>7.253</v>
       </c>
+      <c r="L209" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M209" t="n">
+        <v>30.67</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10586,6 +11918,12 @@
       <c r="K210" t="n">
         <v>6.386</v>
       </c>
+      <c r="L210" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M210" t="n">
+        <v>31.24</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10625,6 +11963,12 @@
       <c r="K211" t="n">
         <v>6.942</v>
       </c>
+      <c r="L211" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M211" t="n">
+        <v>30.068</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10664,6 +12008,12 @@
       <c r="K212" t="n">
         <v>5.681</v>
       </c>
+      <c r="L212" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M212" t="n">
+        <v>29.408</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10703,6 +12053,12 @@
       <c r="K213" t="n">
         <v>6.547</v>
       </c>
+      <c r="L213" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M213" t="n">
+        <v>31.426</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10742,6 +12098,12 @@
       <c r="K214" t="n">
         <v>5.819</v>
       </c>
+      <c r="L214" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M214" t="n">
+        <v>29.832</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10781,6 +12143,12 @@
       <c r="K215" t="n">
         <v>6.742</v>
       </c>
+      <c r="L215" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M215" t="n">
+        <v>31.776</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10820,6 +12188,12 @@
       <c r="K216" t="n">
         <v>6.342</v>
       </c>
+      <c r="L216" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M216" t="n">
+        <v>30.796</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10859,6 +12233,12 @@
       <c r="K217" t="n">
         <v>6.054</v>
       </c>
+      <c r="L217" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M217" t="n">
+        <v>30.35</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10898,6 +12278,12 @@
       <c r="K218" t="n">
         <v>6.32</v>
       </c>
+      <c r="L218" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M218" t="n">
+        <v>30.914</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10937,6 +12323,12 @@
       <c r="K219" t="n">
         <v>7.022</v>
       </c>
+      <c r="L219" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M219" t="n">
+        <v>30.198</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10976,6 +12368,12 @@
       <c r="K220" t="n">
         <v>5.731</v>
       </c>
+      <c r="L220" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M220" t="n">
+        <v>29.578</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11015,6 +12413,12 @@
       <c r="K221" t="n">
         <v>6.973</v>
       </c>
+      <c r="L221" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M221" t="n">
+        <v>32.99</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11054,6 +12458,12 @@
       <c r="K222" t="n">
         <v>6.563</v>
       </c>
+      <c r="L222" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M222" t="n">
+        <v>31.55</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11093,6 +12503,12 @@
       <c r="K223" t="n">
         <v>5.679</v>
       </c>
+      <c r="L223" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M223" t="n">
+        <v>29.03</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11132,6 +12548,12 @@
       <c r="K224" t="n">
         <v>5.02</v>
       </c>
+      <c r="L224" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M224" t="n">
+        <v>27.746</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11171,6 +12593,12 @@
       <c r="K225" t="n">
         <v>5.481</v>
       </c>
+      <c r="L225" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M225" t="n">
+        <v>28.664</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11210,6 +12638,12 @@
       <c r="K226" t="n">
         <v>6.089</v>
       </c>
+      <c r="L226" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M226" t="n">
+        <v>30.266</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11249,6 +12683,12 @@
       <c r="K227" t="n">
         <v>5.439</v>
       </c>
+      <c r="L227" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M227" t="n">
+        <v>28.696</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11288,6 +12728,12 @@
       <c r="K228" t="n">
         <v>5.979</v>
       </c>
+      <c r="L228" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M228" t="n">
+        <v>29.992</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11327,6 +12773,12 @@
       <c r="K229" t="n">
         <v>5.175</v>
       </c>
+      <c r="L229" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M229" t="n">
+        <v>28.104</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11366,6 +12818,12 @@
       <c r="K230" t="n">
         <v>5.16</v>
       </c>
+      <c r="L230" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M230" t="n">
+        <v>28.048</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11405,6 +12863,12 @@
       <c r="K231" t="n">
         <v>5.536</v>
       </c>
+      <c r="L231" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M231" t="n">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11444,6 +12908,12 @@
       <c r="K232" t="n">
         <v>5.322</v>
       </c>
+      <c r="L232" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M232" t="n">
+        <v>28.474</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11483,6 +12953,12 @@
       <c r="K233" t="n">
         <v>5.36</v>
       </c>
+      <c r="L233" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M233" t="n">
+        <v>28.444</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11522,6 +12998,12 @@
       <c r="K234" t="n">
         <v>5.187</v>
       </c>
+      <c r="L234" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M234" t="n">
+        <v>28.004</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11561,6 +13043,12 @@
       <c r="K235" t="n">
         <v>4.993</v>
       </c>
+      <c r="L235" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M235" t="n">
+        <v>26.56</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11600,6 +13088,12 @@
       <c r="K236" t="n">
         <v>5.818</v>
       </c>
+      <c r="L236" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M236" t="n">
+        <v>29.682</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11639,6 +13133,12 @@
       <c r="K237" t="n">
         <v>5.885</v>
       </c>
+      <c r="L237" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M237" t="n">
+        <v>29.656</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11678,6 +13178,12 @@
       <c r="K238" t="n">
         <v>5.321</v>
       </c>
+      <c r="L238" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M238" t="n">
+        <v>28.448</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11717,6 +13223,12 @@
       <c r="K239" t="n">
         <v>5.225</v>
       </c>
+      <c r="L239" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M239" t="n">
+        <v>28.178</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11756,6 +13268,12 @@
       <c r="K240" t="n">
         <v>5.923</v>
       </c>
+      <c r="L240" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M240" t="n">
+        <v>29.75</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11795,6 +13313,12 @@
       <c r="K241" t="n">
         <v>6.039</v>
       </c>
+      <c r="L241" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M241" t="n">
+        <v>29.964</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11834,6 +13358,12 @@
       <c r="K242" t="n">
         <v>5.909</v>
       </c>
+      <c r="L242" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M242" t="n">
+        <v>29.626</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11873,6 +13403,12 @@
       <c r="K243" t="n">
         <v>6.102</v>
       </c>
+      <c r="L243" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M243" t="n">
+        <v>30.208</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11912,6 +13448,12 @@
       <c r="K244" t="n">
         <v>5.664</v>
       </c>
+      <c r="L244" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M244" t="n">
+        <v>29.08</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11951,6 +13493,12 @@
       <c r="K245" t="n">
         <v>5.858</v>
       </c>
+      <c r="L245" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M245" t="n">
+        <v>29.494</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11990,6 +13538,12 @@
       <c r="K246" t="n">
         <v>6.754</v>
       </c>
+      <c r="L246" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M246" t="n">
+        <v>31.576</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12029,6 +13583,12 @@
       <c r="K247" t="n">
         <v>5.971</v>
       </c>
+      <c r="L247" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M247" t="n">
+        <v>29.768</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12068,6 +13628,12 @@
       <c r="K248" t="n">
         <v>6.268</v>
       </c>
+      <c r="L248" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M248" t="n">
+        <v>30.758</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12107,6 +13673,12 @@
       <c r="K249" t="n">
         <v>5.518</v>
       </c>
+      <c r="L249" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M249" t="n">
+        <v>28.81</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12146,6 +13718,12 @@
       <c r="K250" t="n">
         <v>6.518</v>
       </c>
+      <c r="L250" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M250" t="n">
+        <v>31.228</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12185,6 +13763,12 @@
       <c r="K251" t="n">
         <v>5.928</v>
       </c>
+      <c r="L251" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M251" t="n">
+        <v>29.944</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12224,6 +13808,12 @@
       <c r="K252" t="n">
         <v>6.056</v>
       </c>
+      <c r="L252" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M252" t="n">
+        <v>30.1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12263,6 +13853,12 @@
       <c r="K253" t="n">
         <v>5.686</v>
       </c>
+      <c r="L253" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M253" t="n">
+        <v>29.174</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12302,6 +13898,12 @@
       <c r="K254" t="n">
         <v>5.927</v>
       </c>
+      <c r="L254" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M254" t="n">
+        <v>29.716</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12341,6 +13943,12 @@
       <c r="K255" t="n">
         <v>6.598</v>
       </c>
+      <c r="L255" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M255" t="n">
+        <v>31.432</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12380,6 +13988,12 @@
       <c r="K256" t="n">
         <v>6.459</v>
       </c>
+      <c r="L256" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M256" t="n">
+        <v>31.016</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12419,6 +14033,12 @@
       <c r="K257" t="n">
         <v>5.987</v>
       </c>
+      <c r="L257" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M257" t="n">
+        <v>29.744</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12458,6 +14078,12 @@
       <c r="K258" t="n">
         <v>6.271</v>
       </c>
+      <c r="L258" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M258" t="n">
+        <v>30.54</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12497,6 +14123,12 @@
       <c r="K259" t="n">
         <v>4.961</v>
       </c>
+      <c r="L259" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M259" t="n">
+        <v>27.658</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12536,6 +14168,12 @@
       <c r="K260" t="n">
         <v>5.262</v>
       </c>
+      <c r="L260" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M260" t="n">
+        <v>28.046</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12575,6 +14213,12 @@
       <c r="K261" t="n">
         <v>6.345</v>
       </c>
+      <c r="L261" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M261" t="n">
+        <v>30.842</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12614,6 +14258,12 @@
       <c r="K262" t="n">
         <v>4.675</v>
       </c>
+      <c r="L262" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M262" t="n">
+        <v>27.022</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12653,6 +14303,12 @@
       <c r="K263" t="n">
         <v>5.811</v>
       </c>
+      <c r="L263" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M263" t="n">
+        <v>29.424</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12692,6 +14348,12 @@
       <c r="K264" t="n">
         <v>5.581</v>
       </c>
+      <c r="L264" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M264" t="n">
+        <v>28.988</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12731,6 +14393,12 @@
       <c r="K265" t="n">
         <v>5.484</v>
       </c>
+      <c r="L265" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M265" t="n">
+        <v>28.746</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12770,6 +14438,12 @@
       <c r="K266" t="n">
         <v>5.515</v>
       </c>
+      <c r="L266" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M266" t="n">
+        <v>28.588</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12809,6 +14483,12 @@
       <c r="K267" t="n">
         <v>5.528</v>
       </c>
+      <c r="L267" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M267" t="n">
+        <v>26.518</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12848,6 +14528,12 @@
       <c r="K268" t="n">
         <v>5.589</v>
       </c>
+      <c r="L268" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M268" t="n">
+        <v>29.708</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12887,6 +14573,12 @@
       <c r="K269" t="n">
         <v>5.624</v>
       </c>
+      <c r="L269" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M269" t="n">
+        <v>29.088</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12926,6 +14618,12 @@
       <c r="K270" t="n">
         <v>5.297</v>
       </c>
+      <c r="L270" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M270" t="n">
+        <v>28.096</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12965,6 +14663,12 @@
       <c r="K271" t="n">
         <v>6.86</v>
       </c>
+      <c r="L271" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M271" t="n">
+        <v>29.866</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13004,6 +14708,12 @@
       <c r="K272" t="n">
         <v>6.206</v>
       </c>
+      <c r="L272" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M272" t="n">
+        <v>30.612</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13043,6 +14753,12 @@
       <c r="K273" t="n">
         <v>5.379</v>
       </c>
+      <c r="L273" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M273" t="n">
+        <v>28.246</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13082,6 +14798,12 @@
       <c r="K274" t="n">
         <v>7.123</v>
       </c>
+      <c r="L274" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M274" t="n">
+        <v>29.548</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13121,6 +14843,12 @@
       <c r="K275" t="n">
         <v>5.378</v>
       </c>
+      <c r="L275" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M275" t="n">
+        <v>27.802</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13160,6 +14888,12 @@
       <c r="K276" t="n">
         <v>6.177</v>
       </c>
+      <c r="L276" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M276" t="n">
+        <v>29.52</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13199,6 +14933,12 @@
       <c r="K277" t="n">
         <v>5.549</v>
       </c>
+      <c r="L277" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M277" t="n">
+        <v>28.188</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13238,6 +14978,12 @@
       <c r="K278" t="n">
         <v>5.24</v>
       </c>
+      <c r="L278" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M278" t="n">
+        <v>27.642</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -13277,6 +15023,12 @@
       <c r="K279" t="n">
         <v>6</v>
       </c>
+      <c r="L279" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M279" t="n">
+        <v>29.132</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13316,6 +15068,12 @@
       <c r="K280" t="n">
         <v>5.701</v>
       </c>
+      <c r="L280" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M280" t="n">
+        <v>28.462</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13355,6 +15113,12 @@
       <c r="K281" t="n">
         <v>6.643</v>
       </c>
+      <c r="L281" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M281" t="n">
+        <v>30.654</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13394,6 +15158,12 @@
       <c r="K282" t="n">
         <v>6.369</v>
       </c>
+      <c r="L282" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M282" t="n">
+        <v>30.168</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13433,6 +15203,12 @@
       <c r="K283" t="n">
         <v>5.882</v>
       </c>
+      <c r="L283" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M283" t="n">
+        <v>28.922</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13472,6 +15248,12 @@
       <c r="K284" t="n">
         <v>6.148</v>
       </c>
+      <c r="L284" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M284" t="n">
+        <v>29.598</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13511,6 +15293,12 @@
       <c r="K285" t="n">
         <v>5.445</v>
       </c>
+      <c r="L285" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M285" t="n">
+        <v>28.05</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13550,6 +15338,12 @@
       <c r="K286" t="n">
         <v>6.011</v>
       </c>
+      <c r="L286" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M286" t="n">
+        <v>29.378</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13589,6 +15383,12 @@
       <c r="K287" t="n">
         <v>6.018</v>
       </c>
+      <c r="L287" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M287" t="n">
+        <v>29.184</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13628,6 +15428,12 @@
       <c r="K288" t="n">
         <v>5.144</v>
       </c>
+      <c r="L288" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M288" t="n">
+        <v>27.548</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13667,6 +15473,12 @@
       <c r="K289" t="n">
         <v>5.667</v>
       </c>
+      <c r="L289" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M289" t="n">
+        <v>28.588</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13706,6 +15518,12 @@
       <c r="K290" t="n">
         <v>5.268</v>
       </c>
+      <c r="L290" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M290" t="n">
+        <v>27.758</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13745,6 +15563,12 @@
       <c r="K291" t="n">
         <v>6.65</v>
       </c>
+      <c r="L291" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M291" t="n">
+        <v>28.906</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13784,6 +15608,12 @@
       <c r="K292" t="n">
         <v>5.72</v>
       </c>
+      <c r="L292" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M292" t="n">
+        <v>29.044</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13823,6 +15653,12 @@
       <c r="K293" t="n">
         <v>4.837</v>
       </c>
+      <c r="L293" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M293" t="n">
+        <v>27.286</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13862,6 +15698,12 @@
       <c r="K294" t="n">
         <v>4.901</v>
       </c>
+      <c r="L294" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M294" t="n">
+        <v>27.596</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13901,6 +15743,12 @@
       <c r="K295" t="n">
         <v>7.061</v>
       </c>
+      <c r="L295" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M295" t="n">
+        <v>29.978</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13940,6 +15788,12 @@
       <c r="K296" t="n">
         <v>5.129</v>
       </c>
+      <c r="L296" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M296" t="n">
+        <v>27.902</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13979,6 +15833,12 @@
       <c r="K297" t="n">
         <v>4.867</v>
       </c>
+      <c r="L297" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M297" t="n">
+        <v>27.376</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14018,6 +15878,12 @@
       <c r="K298" t="n">
         <v>5.532</v>
       </c>
+      <c r="L298" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M298" t="n">
+        <v>28.688</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14057,6 +15923,12 @@
       <c r="K299" t="n">
         <v>5.672</v>
       </c>
+      <c r="L299" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M299" t="n">
+        <v>29.044</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14096,6 +15968,12 @@
       <c r="K300" t="n">
         <v>5.78</v>
       </c>
+      <c r="L300" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M300" t="n">
+        <v>29.512</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14135,6 +16013,12 @@
       <c r="K301" t="n">
         <v>6.491</v>
       </c>
+      <c r="L301" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M301" t="n">
+        <v>31.59</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14174,6 +16058,12 @@
       <c r="K302" t="n">
         <v>5.285</v>
       </c>
+      <c r="L302" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M302" t="n">
+        <v>28.29</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14213,6 +16103,12 @@
       <c r="K303" t="n">
         <v>5.535</v>
       </c>
+      <c r="L303" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M303" t="n">
+        <v>28.704</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14252,6 +16148,12 @@
       <c r="K304" t="n">
         <v>6.111</v>
       </c>
+      <c r="L304" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M304" t="n">
+        <v>30.574</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14291,6 +16193,12 @@
       <c r="K305" t="n">
         <v>5.222</v>
       </c>
+      <c r="L305" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M305" t="n">
+        <v>28.26</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14330,6 +16238,12 @@
       <c r="K306" t="n">
         <v>6.212</v>
       </c>
+      <c r="L306" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M306" t="n">
+        <v>28.042</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14369,6 +16283,12 @@
       <c r="K307" t="n">
         <v>5.828</v>
       </c>
+      <c r="L307" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M307" t="n">
+        <v>29.528</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14408,6 +16328,12 @@
       <c r="K308" t="n">
         <v>5.061</v>
       </c>
+      <c r="L308" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M308" t="n">
+        <v>27.892</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14447,6 +16373,12 @@
       <c r="K309" t="n">
         <v>5.867</v>
       </c>
+      <c r="L309" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M309" t="n">
+        <v>29.706</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14486,6 +16418,12 @@
       <c r="K310" t="n">
         <v>5.626</v>
       </c>
+      <c r="L310" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M310" t="n">
+        <v>29.104</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14525,6 +16463,12 @@
       <c r="K311" t="n">
         <v>4.929</v>
       </c>
+      <c r="L311" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M311" t="n">
+        <v>27.466</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14564,6 +16508,12 @@
       <c r="K312" t="n">
         <v>5.019</v>
       </c>
+      <c r="L312" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M312" t="n">
+        <v>27.634</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14603,6 +16553,12 @@
       <c r="K313" t="n">
         <v>4.636</v>
       </c>
+      <c r="L313" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M313" t="n">
+        <v>26.85</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14642,6 +16598,12 @@
       <c r="K314" t="n">
         <v>4.639</v>
       </c>
+      <c r="L314" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M314" t="n">
+        <v>26.912</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14681,6 +16643,12 @@
       <c r="K315" t="n">
         <v>5.316</v>
       </c>
+      <c r="L315" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M315" t="n">
+        <v>28.514</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14720,6 +16688,12 @@
       <c r="K316" t="n">
         <v>5.46</v>
       </c>
+      <c r="L316" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M316" t="n">
+        <v>25.77</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14759,6 +16733,12 @@
       <c r="K317" t="n">
         <v>4.596</v>
       </c>
+      <c r="L317" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M317" t="n">
+        <v>26.846</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14798,6 +16778,12 @@
       <c r="K318" t="n">
         <v>5.449</v>
       </c>
+      <c r="L318" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M318" t="n">
+        <v>25.606</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14837,6 +16823,12 @@
       <c r="K319" t="n">
         <v>4.938</v>
       </c>
+      <c r="L319" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M319" t="n">
+        <v>27.576</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14876,6 +16868,12 @@
       <c r="K320" t="n">
         <v>5.983</v>
       </c>
+      <c r="L320" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M320" t="n">
+        <v>29.906</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14915,6 +16913,12 @@
       <c r="K321" t="n">
         <v>5.574</v>
       </c>
+      <c r="L321" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M321" t="n">
+        <v>28.816</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14954,6 +16958,12 @@
       <c r="K322" t="n">
         <v>5.709</v>
       </c>
+      <c r="L322" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M322" t="n">
+        <v>29.346</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14993,6 +17003,12 @@
       <c r="K323" t="n">
         <v>5.093</v>
       </c>
+      <c r="L323" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M323" t="n">
+        <v>27.798</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15032,6 +17048,12 @@
       <c r="K324" t="n">
         <v>4.876</v>
       </c>
+      <c r="L324" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M324" t="n">
+        <v>27.376</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15071,6 +17093,12 @@
       <c r="K325" t="n">
         <v>5.247</v>
       </c>
+      <c r="L325" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M325" t="n">
+        <v>28.616</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15110,6 +17138,12 @@
       <c r="K326" t="n">
         <v>5.421</v>
       </c>
+      <c r="L326" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M326" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15149,6 +17183,12 @@
       <c r="K327" t="n">
         <v>4.985</v>
       </c>
+      <c r="L327" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M327" t="n">
+        <v>28.152</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15188,6 +17228,12 @@
       <c r="K328" t="n">
         <v>4.959</v>
       </c>
+      <c r="L328" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M328" t="n">
+        <v>28.112</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15227,6 +17273,12 @@
       <c r="K329" t="n">
         <v>5.619</v>
       </c>
+      <c r="L329" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M329" t="n">
+        <v>29.566</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15266,6 +17318,12 @@
       <c r="K330" t="n">
         <v>5.294</v>
       </c>
+      <c r="L330" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M330" t="n">
+        <v>28.97</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15305,6 +17363,12 @@
       <c r="K331" t="n">
         <v>5.189</v>
       </c>
+      <c r="L331" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M331" t="n">
+        <v>28.504</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15344,6 +17408,12 @@
       <c r="K332" t="n">
         <v>5.288</v>
       </c>
+      <c r="L332" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M332" t="n">
+        <v>28.752</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15383,6 +17453,12 @@
       <c r="K333" t="n">
         <v>5.696</v>
       </c>
+      <c r="L333" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M333" t="n">
+        <v>29.756</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15422,6 +17498,12 @@
       <c r="K334" t="n">
         <v>4.782</v>
       </c>
+      <c r="L334" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M334" t="n">
+        <v>27.704</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15461,6 +17543,12 @@
       <c r="K335" t="n">
         <v>5.455</v>
       </c>
+      <c r="L335" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M335" t="n">
+        <v>29.3</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15500,6 +17588,12 @@
       <c r="K336" t="n">
         <v>5.518</v>
       </c>
+      <c r="L336" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M336" t="n">
+        <v>29.308</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15539,6 +17633,12 @@
       <c r="K337" t="n">
         <v>5.578</v>
       </c>
+      <c r="L337" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M337" t="n">
+        <v>29.956</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15578,6 +17678,12 @@
       <c r="K338" t="n">
         <v>5.526</v>
       </c>
+      <c r="L338" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M338" t="n">
+        <v>29.474</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15617,6 +17723,12 @@
       <c r="K339" t="n">
         <v>5.935</v>
       </c>
+      <c r="L339" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M339" t="n">
+        <v>30.388</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15656,6 +17768,12 @@
       <c r="K340" t="n">
         <v>4.861</v>
       </c>
+      <c r="L340" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M340" t="n">
+        <v>27.864</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15695,6 +17813,12 @@
       <c r="K341" t="n">
         <v>5.1</v>
       </c>
+      <c r="L341" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M341" t="n">
+        <v>28.334</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -15734,6 +17858,12 @@
       <c r="K342" t="n">
         <v>6.017</v>
       </c>
+      <c r="L342" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M342" t="n">
+        <v>30.612</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15773,6 +17903,12 @@
       <c r="K343" t="n">
         <v>5.901</v>
       </c>
+      <c r="L343" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M343" t="n">
+        <v>30.446</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -15812,6 +17948,12 @@
       <c r="K344" t="n">
         <v>5.513</v>
       </c>
+      <c r="L344" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M344" t="n">
+        <v>29.628</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15851,6 +17993,12 @@
       <c r="K345" t="n">
         <v>5.554</v>
       </c>
+      <c r="L345" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M345" t="n">
+        <v>29.558</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -15890,6 +18038,12 @@
       <c r="K346" t="n">
         <v>6.294</v>
       </c>
+      <c r="L346" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M346" t="n">
+        <v>31.29</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -15929,6 +18083,12 @@
       <c r="K347" t="n">
         <v>6.403</v>
       </c>
+      <c r="L347" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M347" t="n">
+        <v>31.33</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -15968,6 +18128,12 @@
       <c r="K348" t="n">
         <v>5.619</v>
       </c>
+      <c r="L348" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M348" t="n">
+        <v>29.666</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16007,6 +18173,12 @@
       <c r="K349" t="n">
         <v>5.3</v>
       </c>
+      <c r="L349" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M349" t="n">
+        <v>29.09</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16046,6 +18218,12 @@
       <c r="K350" t="n">
         <v>5.888</v>
       </c>
+      <c r="L350" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M350" t="n">
+        <v>30.362</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16085,6 +18263,12 @@
       <c r="K351" t="n">
         <v>5.742</v>
       </c>
+      <c r="L351" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M351" t="n">
+        <v>29.998</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16124,6 +18308,12 @@
       <c r="K352" t="n">
         <v>5.844</v>
       </c>
+      <c r="L352" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M352" t="n">
+        <v>30.12</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16163,6 +18353,12 @@
       <c r="K353" t="n">
         <v>5.87</v>
       </c>
+      <c r="L353" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M353" t="n">
+        <v>30.304</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16202,6 +18398,12 @@
       <c r="K354" t="n">
         <v>5.708</v>
       </c>
+      <c r="L354" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M354" t="n">
+        <v>29.91</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16241,6 +18443,12 @@
       <c r="K355" t="n">
         <v>5.795</v>
       </c>
+      <c r="L355" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M355" t="n">
+        <v>29.996</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16280,6 +18488,12 @@
       <c r="K356" t="n">
         <v>6.316</v>
       </c>
+      <c r="L356" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M356" t="n">
+        <v>31.286</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16319,6 +18533,12 @@
       <c r="K357" t="n">
         <v>5.807</v>
       </c>
+      <c r="L357" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M357" t="n">
+        <v>30.202</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16358,6 +18578,12 @@
       <c r="K358" t="n">
         <v>5.987</v>
       </c>
+      <c r="L358" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M358" t="n">
+        <v>30.596</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16397,6 +18623,12 @@
       <c r="K359" t="n">
         <v>4.669</v>
       </c>
+      <c r="L359" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M359" t="n">
+        <v>27.116</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16436,6 +18668,12 @@
       <c r="K360" t="n">
         <v>5.747</v>
       </c>
+      <c r="L360" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M360" t="n">
+        <v>29.56</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -16475,6 +18713,12 @@
       <c r="K361" t="n">
         <v>5.081</v>
       </c>
+      <c r="L361" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M361" t="n">
+        <v>27.958</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16514,6 +18758,12 @@
       <c r="K362" t="n">
         <v>4.855</v>
       </c>
+      <c r="L362" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M362" t="n">
+        <v>27.542</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16553,6 +18803,12 @@
       <c r="K363" t="n">
         <v>5.386</v>
       </c>
+      <c r="L363" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M363" t="n">
+        <v>28.516</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16592,6 +18848,12 @@
       <c r="K364" t="n">
         <v>5.745</v>
       </c>
+      <c r="L364" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M364" t="n">
+        <v>29.596</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16631,6 +18893,12 @@
       <c r="K365" t="n">
         <v>5.443</v>
       </c>
+      <c r="L365" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M365" t="n">
+        <v>28.974</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -16670,6 +18938,12 @@
       <c r="K366" t="n">
         <v>5.154</v>
       </c>
+      <c r="L366" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M366" t="n">
+        <v>28.276</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16709,6 +18983,12 @@
       <c r="K367" t="n">
         <v>5.689</v>
       </c>
+      <c r="L367" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M367" t="n">
+        <v>29.456</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -16748,6 +19028,12 @@
       <c r="K368" t="n">
         <v>5.349</v>
       </c>
+      <c r="L368" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M368" t="n">
+        <v>28.562</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16787,6 +19073,12 @@
       <c r="K369" t="n">
         <v>6.165</v>
       </c>
+      <c r="L369" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M369" t="n">
+        <v>30.596</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16826,6 +19118,12 @@
       <c r="K370" t="n">
         <v>4.932</v>
       </c>
+      <c r="L370" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M370" t="n">
+        <v>27.682</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16865,6 +19163,12 @@
       <c r="K371" t="n">
         <v>5.173</v>
       </c>
+      <c r="L371" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M371" t="n">
+        <v>28.13</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16904,6 +19208,12 @@
       <c r="K372" t="n">
         <v>4.885</v>
       </c>
+      <c r="L372" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M372" t="n">
+        <v>27.488</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -16943,6 +19253,12 @@
       <c r="K373" t="n">
         <v>5.609</v>
       </c>
+      <c r="L373" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M373" t="n">
+        <v>29.356</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -16982,6 +19298,12 @@
       <c r="K374" t="n">
         <v>5.863</v>
       </c>
+      <c r="L374" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M374" t="n">
+        <v>29.61</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17021,6 +19343,12 @@
       <c r="K375" t="n">
         <v>5.257</v>
       </c>
+      <c r="L375" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M375" t="n">
+        <v>28.456</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17060,6 +19388,12 @@
       <c r="K376" t="n">
         <v>5.781</v>
       </c>
+      <c r="L376" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M376" t="n">
+        <v>29.724</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17099,6 +19433,12 @@
       <c r="K377" t="n">
         <v>5.97</v>
       </c>
+      <c r="L377" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M377" t="n">
+        <v>30.042</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17138,6 +19478,12 @@
       <c r="K378" t="n">
         <v>5.918</v>
       </c>
+      <c r="L378" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M378" t="n">
+        <v>29.92</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17177,6 +19523,12 @@
       <c r="K379" t="n">
         <v>5.997</v>
       </c>
+      <c r="L379" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M379" t="n">
+        <v>30.182</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17216,6 +19568,12 @@
       <c r="K380" t="n">
         <v>5.614</v>
       </c>
+      <c r="L380" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M380" t="n">
+        <v>29.336</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -17255,6 +19613,12 @@
       <c r="K381" t="n">
         <v>5.769</v>
       </c>
+      <c r="L381" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M381" t="n">
+        <v>29.634</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -17294,6 +19658,12 @@
       <c r="K382" t="n">
         <v>6.11</v>
       </c>
+      <c r="L382" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M382" t="n">
+        <v>30.522</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -17333,6 +19703,12 @@
       <c r="K383" t="n">
         <v>6.09</v>
       </c>
+      <c r="L383" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M383" t="n">
+        <v>30.432</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -17372,6 +19748,12 @@
       <c r="K384" t="n">
         <v>6.004</v>
       </c>
+      <c r="L384" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M384" t="n">
+        <v>30.166</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -17411,6 +19793,12 @@
       <c r="K385" t="n">
         <v>5.874</v>
       </c>
+      <c r="L385" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M385" t="n">
+        <v>30.004</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -17450,6 +19838,12 @@
       <c r="K386" t="n">
         <v>5.945</v>
       </c>
+      <c r="L386" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M386" t="n">
+        <v>29.996</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -17489,6 +19883,12 @@
       <c r="K387" t="n">
         <v>6.751</v>
       </c>
+      <c r="L387" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M387" t="n">
+        <v>32.398</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -17528,6 +19928,12 @@
       <c r="K388" t="n">
         <v>5.915</v>
       </c>
+      <c r="L388" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M388" t="n">
+        <v>30.016</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -17567,6 +19973,12 @@
       <c r="K389" t="n">
         <v>5.539</v>
       </c>
+      <c r="L389" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M389" t="n">
+        <v>29.19</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -17606,6 +20018,12 @@
       <c r="K390" t="n">
         <v>5.968</v>
       </c>
+      <c r="L390" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M390" t="n">
+        <v>30.016</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -17645,6 +20063,12 @@
       <c r="K391" t="n">
         <v>5.914</v>
       </c>
+      <c r="L391" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M391" t="n">
+        <v>30.042</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -17684,6 +20108,12 @@
       <c r="K392" t="n">
         <v>5.685</v>
       </c>
+      <c r="L392" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M392" t="n">
+        <v>29.46</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -17723,6 +20153,12 @@
       <c r="K393" t="n">
         <v>5.739</v>
       </c>
+      <c r="L393" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M393" t="n">
+        <v>29.184</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -17762,6 +20198,12 @@
       <c r="K394" t="n">
         <v>5.001</v>
       </c>
+      <c r="L394" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M394" t="n">
+        <v>27.712</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17801,6 +20243,12 @@
       <c r="K395" t="n">
         <v>6.087</v>
       </c>
+      <c r="L395" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M395" t="n">
+        <v>30.084</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -17840,6 +20288,12 @@
       <c r="K396" t="n">
         <v>5.798</v>
       </c>
+      <c r="L396" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M396" t="n">
+        <v>29.258</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17879,6 +20333,12 @@
       <c r="K397" t="n">
         <v>6.02</v>
       </c>
+      <c r="L397" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M397" t="n">
+        <v>29.952</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -17918,6 +20378,12 @@
       <c r="K398" t="n">
         <v>6.115</v>
       </c>
+      <c r="L398" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M398" t="n">
+        <v>30.078</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -17957,6 +20423,12 @@
       <c r="K399" t="n">
         <v>5.6</v>
       </c>
+      <c r="L399" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M399" t="n">
+        <v>28.932</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17996,6 +20468,12 @@
       <c r="K400" t="n">
         <v>5.295</v>
       </c>
+      <c r="L400" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M400" t="n">
+        <v>28.178</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18035,6 +20513,12 @@
       <c r="K401" t="n">
         <v>6.182</v>
       </c>
+      <c r="L401" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M401" t="n">
+        <v>30.242</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18074,6 +20558,12 @@
       <c r="K402" t="n">
         <v>5.556</v>
       </c>
+      <c r="L402" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M402" t="n">
+        <v>28.852</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -18113,6 +20603,12 @@
       <c r="K403" t="n">
         <v>6.068</v>
       </c>
+      <c r="L403" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M403" t="n">
+        <v>29.926</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -18152,6 +20648,12 @@
       <c r="K404" t="n">
         <v>5.938</v>
       </c>
+      <c r="L404" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M404" t="n">
+        <v>29.68</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18191,6 +20693,12 @@
       <c r="K405" t="n">
         <v>4.965</v>
       </c>
+      <c r="L405" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M405" t="n">
+        <v>27.66</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -18230,6 +20738,12 @@
       <c r="K406" t="n">
         <v>5.603</v>
       </c>
+      <c r="L406" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M406" t="n">
+        <v>28.968</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -18269,6 +20783,12 @@
       <c r="K407" t="n">
         <v>5.547</v>
       </c>
+      <c r="L407" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M407" t="n">
+        <v>28.82</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -18308,6 +20828,12 @@
       <c r="K408" t="n">
         <v>5.646</v>
       </c>
+      <c r="L408" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M408" t="n">
+        <v>29.004</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -18347,6 +20873,12 @@
       <c r="K409" t="n">
         <v>5.364</v>
       </c>
+      <c r="L409" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M409" t="n">
+        <v>28.308</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -18386,6 +20918,12 @@
       <c r="K410" t="n">
         <v>5.391</v>
       </c>
+      <c r="L410" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M410" t="n">
+        <v>24.942</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -18425,6 +20963,12 @@
       <c r="K411" t="n">
         <v>5.48</v>
       </c>
+      <c r="L411" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M411" t="n">
+        <v>28.038</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -18464,6 +21008,12 @@
       <c r="K412" t="n">
         <v>4.797</v>
       </c>
+      <c r="L412" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M412" t="n">
+        <v>26.394</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -18503,6 +21053,12 @@
       <c r="K413" t="n">
         <v>5.177</v>
       </c>
+      <c r="L413" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24.62</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -18542,6 +21098,12 @@
       <c r="K414" t="n">
         <v>4.897</v>
       </c>
+      <c r="L414" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M414" t="n">
+        <v>26.684</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18581,6 +21143,12 @@
       <c r="K415" t="n">
         <v>4.837</v>
       </c>
+      <c r="L415" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M415" t="n">
+        <v>23.46</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -18620,6 +21188,12 @@
       <c r="K416" t="n">
         <v>4.944</v>
       </c>
+      <c r="L416" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M416" t="n">
+        <v>26.934</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -18659,6 +21233,12 @@
       <c r="K417" t="n">
         <v>5.106</v>
       </c>
+      <c r="L417" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M417" t="n">
+        <v>26.948</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -18698,6 +21278,12 @@
       <c r="K418" t="n">
         <v>4.631</v>
       </c>
+      <c r="L418" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M418" t="n">
+        <v>23.072</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -18737,6 +21323,12 @@
       <c r="K419" t="n">
         <v>4.499</v>
       </c>
+      <c r="L419" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M419" t="n">
+        <v>25.794</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18776,6 +21368,12 @@
       <c r="K420" t="n">
         <v>5.854</v>
       </c>
+      <c r="L420" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M420" t="n">
+        <v>26.028</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -18815,6 +21413,12 @@
       <c r="K421" t="n">
         <v>4.815</v>
       </c>
+      <c r="L421" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M421" t="n">
+        <v>23.714</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -18854,6 +21458,12 @@
       <c r="K422" t="n">
         <v>5.489</v>
       </c>
+      <c r="L422" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M422" t="n">
+        <v>27.882</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -18893,6 +21503,12 @@
       <c r="K423" t="n">
         <v>4.885</v>
       </c>
+      <c r="L423" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M423" t="n">
+        <v>23.576</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -18932,6 +21548,12 @@
       <c r="K424" t="n">
         <v>4.957</v>
       </c>
+      <c r="L424" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M424" t="n">
+        <v>23.67</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -18971,6 +21593,12 @@
       <c r="K425" t="n">
         <v>4.754</v>
       </c>
+      <c r="L425" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M425" t="n">
+        <v>23.276</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -19010,6 +21638,12 @@
       <c r="K426" t="n">
         <v>4.399</v>
       </c>
+      <c r="L426" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M426" t="n">
+        <v>22.624</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -19049,6 +21683,12 @@
       <c r="K427" t="n">
         <v>9.242000000000001</v>
       </c>
+      <c r="L427" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M427" t="n">
+        <v>30.406</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -19088,6 +21728,12 @@
       <c r="K428" t="n">
         <v>5.986</v>
       </c>
+      <c r="L428" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M428" t="n">
+        <v>29.948</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -19127,6 +21773,12 @@
       <c r="K429" t="n">
         <v>5.659</v>
       </c>
+      <c r="L429" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M429" t="n">
+        <v>29.132</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -19166,6 +21818,12 @@
       <c r="K430" t="n">
         <v>6.129</v>
       </c>
+      <c r="L430" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M430" t="n">
+        <v>30.898</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -19205,6 +21863,12 @@
       <c r="K431" t="n">
         <v>5.474</v>
       </c>
+      <c r="L431" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M431" t="n">
+        <v>28.616</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -19244,6 +21908,12 @@
       <c r="K432" t="n">
         <v>6.784</v>
       </c>
+      <c r="L432" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M432" t="n">
+        <v>32.29</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -19283,6 +21953,12 @@
       <c r="K433" t="n">
         <v>6.834</v>
       </c>
+      <c r="L433" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M433" t="n">
+        <v>32.308</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -19322,6 +21998,12 @@
       <c r="K434" t="n">
         <v>6.099</v>
       </c>
+      <c r="L434" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M434" t="n">
+        <v>30.166</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -19361,6 +22043,12 @@
       <c r="K435" t="n">
         <v>5.347</v>
       </c>
+      <c r="L435" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M435" t="n">
+        <v>28.24</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -19400,6 +22088,12 @@
       <c r="K436" t="n">
         <v>5.795</v>
       </c>
+      <c r="L436" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M436" t="n">
+        <v>29.32</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -19439,6 +22133,12 @@
       <c r="K437" t="n">
         <v>5.736</v>
       </c>
+      <c r="L437" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M437" t="n">
+        <v>29.148</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -19478,6 +22178,12 @@
       <c r="K438" t="n">
         <v>5.643</v>
       </c>
+      <c r="L438" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M438" t="n">
+        <v>28.896</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -19517,6 +22223,12 @@
       <c r="K439" t="n">
         <v>6.355</v>
       </c>
+      <c r="L439" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M439" t="n">
+        <v>30.524</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -19556,6 +22268,12 @@
       <c r="K440" t="n">
         <v>6.243</v>
       </c>
+      <c r="L440" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M440" t="n">
+        <v>28.282</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -19595,6 +22313,12 @@
       <c r="K441" t="n">
         <v>5.736</v>
       </c>
+      <c r="L441" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M441" t="n">
+        <v>29.102</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -19634,6 +22358,12 @@
       <c r="K442" t="n">
         <v>5.71</v>
       </c>
+      <c r="L442" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M442" t="n">
+        <v>29.252</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -19673,6 +22403,12 @@
       <c r="K443" t="n">
         <v>5.247</v>
       </c>
+      <c r="L443" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M443" t="n">
+        <v>28.06</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -19712,6 +22448,12 @@
       <c r="K444" t="n">
         <v>7.112</v>
       </c>
+      <c r="L444" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M444" t="n">
+        <v>29.746</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -19751,6 +22493,12 @@
       <c r="K445" t="n">
         <v>5.782</v>
       </c>
+      <c r="L445" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M445" t="n">
+        <v>28.842</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -19790,6 +22538,12 @@
       <c r="K446" t="n">
         <v>6.208</v>
       </c>
+      <c r="L446" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M446" t="n">
+        <v>29.79</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -19829,6 +22583,12 @@
       <c r="K447" t="n">
         <v>5.889</v>
       </c>
+      <c r="L447" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M447" t="n">
+        <v>29.244</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -19868,6 +22628,12 @@
       <c r="K448" t="n">
         <v>7.727</v>
       </c>
+      <c r="L448" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M448" t="n">
+        <v>30.98</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -19907,6 +22673,12 @@
       <c r="K449" t="n">
         <v>5.733</v>
       </c>
+      <c r="L449" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M449" t="n">
+        <v>28.85</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -19946,6 +22718,12 @@
       <c r="K450" t="n">
         <v>6.379</v>
       </c>
+      <c r="L450" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M450" t="n">
+        <v>30.16</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -19985,6 +22763,12 @@
       <c r="K451" t="n">
         <v>5.983</v>
       </c>
+      <c r="L451" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M451" t="n">
+        <v>29.404</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -20024,6 +22808,12 @@
       <c r="K452" t="n">
         <v>6.105</v>
       </c>
+      <c r="L452" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M452" t="n">
+        <v>29.62</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -20063,6 +22853,12 @@
       <c r="K453" t="n">
         <v>5.596</v>
       </c>
+      <c r="L453" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M453" t="n">
+        <v>28.576</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -20102,6 +22898,12 @@
       <c r="K454" t="n">
         <v>6.454</v>
       </c>
+      <c r="L454" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M454" t="n">
+        <v>30.358</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -20141,6 +22943,12 @@
       <c r="K455" t="n">
         <v>7.053</v>
       </c>
+      <c r="L455" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M455" t="n">
+        <v>29.442</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -20180,6 +22988,12 @@
       <c r="K456" t="n">
         <v>5.742</v>
       </c>
+      <c r="L456" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M456" t="n">
+        <v>28.888</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -20219,6 +23033,12 @@
       <c r="K457" t="n">
         <v>6.227</v>
       </c>
+      <c r="L457" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M457" t="n">
+        <v>29.742</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -20258,6 +23078,12 @@
       <c r="K458" t="n">
         <v>7.109</v>
       </c>
+      <c r="L458" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M458" t="n">
+        <v>29.68</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -20297,6 +23123,12 @@
       <c r="K459" t="n">
         <v>6.329</v>
       </c>
+      <c r="L459" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M459" t="n">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -20336,6 +23168,12 @@
       <c r="K460" t="n">
         <v>6.112</v>
       </c>
+      <c r="L460" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M460" t="n">
+        <v>29.542</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -20375,6 +23213,12 @@
       <c r="K461" t="n">
         <v>7.047</v>
       </c>
+      <c r="L461" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M461" t="n">
+        <v>29.668</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -20414,6 +23258,12 @@
       <c r="K462" t="n">
         <v>6.932</v>
       </c>
+      <c r="L462" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M462" t="n">
+        <v>29.45</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -20453,6 +23303,12 @@
       <c r="K463" t="n">
         <v>6.686</v>
       </c>
+      <c r="L463" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M463" t="n">
+        <v>31.152</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -20492,6 +23348,12 @@
       <c r="K464" t="n">
         <v>10.379</v>
       </c>
+      <c r="L464" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M464" t="n">
+        <v>32.558</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -20531,6 +23393,12 @@
       <c r="K465" t="n">
         <v>9.254</v>
       </c>
+      <c r="L465" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M465" t="n">
+        <v>30.184</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -20570,6 +23438,12 @@
       <c r="K466" t="n">
         <v>6.351</v>
       </c>
+      <c r="L466" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M466" t="n">
+        <v>30.386</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -20609,6 +23483,12 @@
       <c r="K467" t="n">
         <v>6.592</v>
       </c>
+      <c r="L467" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M467" t="n">
+        <v>28.798</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -20648,6 +23528,12 @@
       <c r="K468" t="n">
         <v>7.164</v>
       </c>
+      <c r="L468" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M468" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -20687,6 +23573,12 @@
       <c r="K469" t="n">
         <v>7.083</v>
       </c>
+      <c r="L469" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M469" t="n">
+        <v>29.73</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -20726,6 +23618,12 @@
       <c r="K470" t="n">
         <v>5.895</v>
       </c>
+      <c r="L470" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M470" t="n">
+        <v>29.358</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -20765,6 +23663,12 @@
       <c r="K471" t="n">
         <v>6.119</v>
       </c>
+      <c r="L471" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M471" t="n">
+        <v>29.954</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -20804,6 +23708,12 @@
       <c r="K472" t="n">
         <v>7.462</v>
       </c>
+      <c r="L472" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M472" t="n">
+        <v>30.53</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -20843,6 +23753,12 @@
       <c r="K473" t="n">
         <v>7.045</v>
       </c>
+      <c r="L473" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M473" t="n">
+        <v>29.674</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -20882,6 +23798,12 @@
       <c r="K474" t="n">
         <v>6.614</v>
       </c>
+      <c r="L474" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M474" t="n">
+        <v>28.816</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -20921,6 +23843,12 @@
       <c r="K475" t="n">
         <v>6.466</v>
       </c>
+      <c r="L475" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M475" t="n">
+        <v>28.538</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -20960,6 +23888,12 @@
       <c r="K476" t="n">
         <v>7.297</v>
       </c>
+      <c r="L476" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M476" t="n">
+        <v>30.27</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -20999,6 +23933,12 @@
       <c r="K477" t="n">
         <v>6.374</v>
       </c>
+      <c r="L477" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M477" t="n">
+        <v>28.378</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -21038,6 +23978,12 @@
       <c r="K478" t="n">
         <v>4.606</v>
       </c>
+      <c r="L478" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M478" t="n">
+        <v>27.03</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -21077,6 +24023,12 @@
       <c r="K479" t="n">
         <v>5.061</v>
       </c>
+      <c r="L479" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M479" t="n">
+        <v>28.03</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -21116,6 +24068,12 @@
       <c r="K480" t="n">
         <v>5.319</v>
       </c>
+      <c r="L480" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M480" t="n">
+        <v>28.432</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -21155,6 +24113,12 @@
       <c r="K481" t="n">
         <v>5.541</v>
       </c>
+      <c r="L481" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M481" t="n">
+        <v>28.91</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -21194,6 +24158,12 @@
       <c r="K482" t="n">
         <v>4.566</v>
       </c>
+      <c r="L482" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M482" t="n">
+        <v>26.974</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -21233,6 +24203,12 @@
       <c r="K483" t="n">
         <v>5.946</v>
       </c>
+      <c r="L483" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M483" t="n">
+        <v>30.03</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -21272,6 +24248,12 @@
       <c r="K484" t="n">
         <v>5.248</v>
       </c>
+      <c r="L484" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M484" t="n">
+        <v>28.458</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -21311,6 +24293,12 @@
       <c r="K485" t="n">
         <v>5.098</v>
       </c>
+      <c r="L485" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M485" t="n">
+        <v>27.868</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -21350,6 +24338,12 @@
       <c r="K486" t="n">
         <v>5.235</v>
       </c>
+      <c r="L486" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M486" t="n">
+        <v>28.31</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -21389,6 +24383,12 @@
       <c r="K487" t="n">
         <v>4.936</v>
       </c>
+      <c r="L487" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M487" t="n">
+        <v>27.654</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -21428,6 +24428,12 @@
       <c r="K488" t="n">
         <v>4.695</v>
       </c>
+      <c r="L488" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M488" t="n">
+        <v>27.214</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -21467,6 +24473,12 @@
       <c r="K489" t="n">
         <v>4.563</v>
       </c>
+      <c r="L489" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M489" t="n">
+        <v>26.748</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -21506,6 +24518,12 @@
       <c r="K490" t="n">
         <v>4.694</v>
       </c>
+      <c r="L490" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M490" t="n">
+        <v>27.19</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -21545,6 +24563,12 @@
       <c r="K491" t="n">
         <v>5.91</v>
       </c>
+      <c r="L491" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M491" t="n">
+        <v>30.006</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -21584,6 +24608,12 @@
       <c r="K492" t="n">
         <v>4.757</v>
       </c>
+      <c r="L492" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M492" t="n">
+        <v>27.306</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -21623,6 +24653,12 @@
       <c r="K493" t="n">
         <v>4.917</v>
       </c>
+      <c r="L493" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M493" t="n">
+        <v>27.518</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -21662,6 +24698,12 @@
       <c r="K494" t="n">
         <v>5.187</v>
       </c>
+      <c r="L494" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M494" t="n">
+        <v>28.192</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -21701,6 +24743,12 @@
       <c r="K495" t="n">
         <v>5.562</v>
       </c>
+      <c r="L495" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M495" t="n">
+        <v>28.982</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -21740,6 +24788,12 @@
       <c r="K496" t="n">
         <v>5.302</v>
       </c>
+      <c r="L496" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M496" t="n">
+        <v>28.398</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -21779,6 +24833,12 @@
       <c r="K497" t="n">
         <v>5.055</v>
       </c>
+      <c r="L497" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M497" t="n">
+        <v>27.794</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -21818,6 +24878,12 @@
       <c r="K498" t="n">
         <v>5.672</v>
       </c>
+      <c r="L498" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M498" t="n">
+        <v>29.248</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -21857,6 +24923,12 @@
       <c r="K499" t="n">
         <v>5.345</v>
       </c>
+      <c r="L499" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M499" t="n">
+        <v>28.424</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -21896,6 +24968,12 @@
       <c r="K500" t="n">
         <v>5.508</v>
       </c>
+      <c r="L500" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M500" t="n">
+        <v>28.832</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -21935,6 +25013,12 @@
       <c r="K501" t="n">
         <v>5.404</v>
       </c>
+      <c r="L501" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M501" t="n">
+        <v>28.682</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -21974,6 +25058,12 @@
       <c r="K502" t="n">
         <v>5.464</v>
       </c>
+      <c r="L502" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M502" t="n">
+        <v>28.742</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -22013,6 +25103,12 @@
       <c r="K503" t="n">
         <v>5.308</v>
       </c>
+      <c r="L503" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M503" t="n">
+        <v>28.504</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -22052,6 +25148,12 @@
       <c r="K504" t="n">
         <v>5.2</v>
       </c>
+      <c r="L504" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M504" t="n">
+        <v>28.1</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -22091,6 +25193,12 @@
       <c r="K505" t="n">
         <v>5.49</v>
       </c>
+      <c r="L505" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M505" t="n">
+        <v>28.822</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -22130,6 +25238,12 @@
       <c r="K506" t="n">
         <v>6.043</v>
       </c>
+      <c r="L506" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M506" t="n">
+        <v>30.034</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -22169,6 +25283,12 @@
       <c r="K507" t="n">
         <v>5.409</v>
       </c>
+      <c r="L507" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M507" t="n">
+        <v>28.48</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -22208,6 +25328,12 @@
       <c r="K508" t="n">
         <v>5.84</v>
       </c>
+      <c r="L508" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M508" t="n">
+        <v>29.536</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -22247,6 +25373,12 @@
       <c r="K509" t="n">
         <v>5.392</v>
       </c>
+      <c r="L509" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M509" t="n">
+        <v>28.622</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -22286,6 +25418,12 @@
       <c r="K510" t="n">
         <v>4.823</v>
       </c>
+      <c r="L510" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M510" t="n">
+        <v>27.364</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -22325,6 +25463,12 @@
       <c r="K511" t="n">
         <v>5.686</v>
       </c>
+      <c r="L511" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M511" t="n">
+        <v>29.256</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -22364,6 +25508,12 @@
       <c r="K512" t="n">
         <v>5.466</v>
       </c>
+      <c r="L512" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M512" t="n">
+        <v>28.402</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -22403,6 +25553,12 @@
       <c r="K513" t="n">
         <v>4.947</v>
       </c>
+      <c r="L513" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M513" t="n">
+        <v>27.13</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -22442,6 +25598,12 @@
       <c r="K514" t="n">
         <v>4.982</v>
       </c>
+      <c r="L514" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M514" t="n">
+        <v>23.34</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -22481,6 +25643,12 @@
       <c r="K515" t="n">
         <v>5.343</v>
       </c>
+      <c r="L515" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M515" t="n">
+        <v>24.98</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -22520,6 +25688,12 @@
       <c r="K516" t="n">
         <v>5.207</v>
       </c>
+      <c r="L516" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M516" t="n">
+        <v>27.704</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -22559,6 +25733,12 @@
       <c r="K517" t="n">
         <v>5.854</v>
       </c>
+      <c r="L517" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M517" t="n">
+        <v>29.148</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -22598,6 +25778,12 @@
       <c r="K518" t="n">
         <v>5.201</v>
       </c>
+      <c r="L518" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M518" t="n">
+        <v>27.838</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -22637,6 +25823,12 @@
       <c r="K519" t="n">
         <v>5.595</v>
       </c>
+      <c r="L519" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M519" t="n">
+        <v>25.61</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -22676,6 +25868,12 @@
       <c r="K520" t="n">
         <v>5.141</v>
       </c>
+      <c r="L520" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M520" t="n">
+        <v>27.668</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -22715,6 +25913,12 @@
       <c r="K521" t="n">
         <v>5.275</v>
       </c>
+      <c r="L521" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M521" t="n">
+        <v>27.918</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -22754,6 +25958,12 @@
       <c r="K522" t="n">
         <v>5.082</v>
       </c>
+      <c r="L522" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M522" t="n">
+        <v>24.568</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -22793,6 +26003,12 @@
       <c r="K523" t="n">
         <v>6.089</v>
       </c>
+      <c r="L523" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M523" t="n">
+        <v>29.872</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -22832,6 +26048,12 @@
       <c r="K524" t="n">
         <v>5.14</v>
       </c>
+      <c r="L524" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M524" t="n">
+        <v>27.696</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -22871,6 +26093,12 @@
       <c r="K525" t="n">
         <v>6.003</v>
       </c>
+      <c r="L525" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M525" t="n">
+        <v>29.428</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -22910,6 +26138,12 @@
       <c r="K526" t="n">
         <v>5.271</v>
       </c>
+      <c r="L526" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M526" t="n">
+        <v>24.818</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -22949,6 +26183,12 @@
       <c r="K527" t="n">
         <v>5.445</v>
       </c>
+      <c r="L527" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M527" t="n">
+        <v>28.398</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -22988,6 +26228,12 @@
       <c r="K528" t="n">
         <v>5.105</v>
       </c>
+      <c r="L528" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M528" t="n">
+        <v>26.524</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -23027,6 +26273,12 @@
       <c r="K529" t="n">
         <v>4.996</v>
       </c>
+      <c r="L529" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M529" t="n">
+        <v>26.19</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -23066,6 +26318,12 @@
       <c r="K530" t="n">
         <v>5.235</v>
       </c>
+      <c r="L530" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M530" t="n">
+        <v>27.786</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -23105,6 +26363,12 @@
       <c r="K531" t="n">
         <v>4.645</v>
       </c>
+      <c r="L531" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M531" t="n">
+        <v>23.524</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -23144,6 +26408,12 @@
       <c r="K532" t="n">
         <v>6</v>
       </c>
+      <c r="L532" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M532" t="n">
+        <v>29.738</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -23183,6 +26453,12 @@
       <c r="K533" t="n">
         <v>4.697</v>
       </c>
+      <c r="L533" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M533" t="n">
+        <v>22.476</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -23222,6 +26498,12 @@
       <c r="K534" t="n">
         <v>5.562</v>
       </c>
+      <c r="L534" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M534" t="n">
+        <v>29.098</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -23261,6 +26543,12 @@
       <c r="K535" t="n">
         <v>5.039</v>
       </c>
+      <c r="L535" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M535" t="n">
+        <v>26.27</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -23300,6 +26588,12 @@
       <c r="K536" t="n">
         <v>4.677</v>
       </c>
+      <c r="L536" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M536" t="n">
+        <v>22.654</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -23339,6 +26633,12 @@
       <c r="K537" t="n">
         <v>4.623</v>
       </c>
+      <c r="L537" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M537" t="n">
+        <v>22.336</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -23378,6 +26678,12 @@
       <c r="K538" t="n">
         <v>5.659</v>
       </c>
+      <c r="L538" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M538" t="n">
+        <v>28.918</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -23417,6 +26723,12 @@
       <c r="K539" t="n">
         <v>5.263</v>
       </c>
+      <c r="L539" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M539" t="n">
+        <v>27.81</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -23456,6 +26768,12 @@
       <c r="K540" t="n">
         <v>5.544</v>
       </c>
+      <c r="L540" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M540" t="n">
+        <v>28.784</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -23495,6 +26813,12 @@
       <c r="K541" t="n">
         <v>5.254</v>
       </c>
+      <c r="L541" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M541" t="n">
+        <v>26.796</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -23534,6 +26858,12 @@
       <c r="K542" t="n">
         <v>5.446</v>
       </c>
+      <c r="L542" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M542" t="n">
+        <v>28.484</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -23573,6 +26903,12 @@
       <c r="K543" t="n">
         <v>4.762</v>
       </c>
+      <c r="L543" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M543" t="n">
+        <v>26.742</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -23612,6 +26948,12 @@
       <c r="K544" t="n">
         <v>5.051</v>
       </c>
+      <c r="L544" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M544" t="n">
+        <v>24.428</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -23650,6 +26992,12 @@
       </c>
       <c r="K545" t="n">
         <v>5.299</v>
+      </c>
+      <c r="L545" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M545" t="n">
+        <v>27.926</v>
       </c>
     </row>
   </sheetData>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -550,10 +550,10 @@
         <v>120.76</v>
       </c>
       <c r="J2" t="n">
-        <v>47.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>214.1</v>
+        <v>181.79</v>
       </c>
       <c r="L2" t="n">
         <v>42</v>
@@ -610,10 +610,10 @@
         <v>112.98</v>
       </c>
       <c r="J3" t="n">
-        <v>49.5</v>
+        <v>71.47</v>
       </c>
       <c r="K3" t="n">
-        <v>214.86</v>
+        <v>179.6</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
@@ -670,10 +670,10 @@
         <v>110.81</v>
       </c>
       <c r="J4" t="n">
-        <v>48.4</v>
+        <v>70</v>
       </c>
       <c r="K4" t="n">
-        <v>216.6</v>
+        <v>179.98</v>
       </c>
       <c r="L4" t="n">
         <v>42</v>
@@ -730,10 +730,10 @@
         <v>107.54</v>
       </c>
       <c r="J5" t="n">
-        <v>48.6</v>
+        <v>69</v>
       </c>
       <c r="K5" t="n">
-        <v>212.84</v>
+        <v>176.39</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
@@ -790,10 +790,10 @@
         <v>106.48</v>
       </c>
       <c r="J6" t="n">
-        <v>46.7</v>
+        <v>67.39</v>
       </c>
       <c r="K6" t="n">
-        <v>208.88</v>
+        <v>173.44</v>
       </c>
       <c r="L6" t="n">
         <v>45</v>
@@ -850,10 +850,10 @@
         <v>104.02</v>
       </c>
       <c r="J7" t="n">
-        <v>45.9</v>
+        <v>66.02</v>
       </c>
       <c r="K7" t="n">
-        <v>203.64</v>
+        <v>169.16</v>
       </c>
       <c r="L7" t="n">
         <v>39</v>
@@ -910,10 +910,10 @@
         <v>103.18</v>
       </c>
       <c r="J8" t="n">
-        <v>49.2</v>
+        <v>67.88</v>
       </c>
       <c r="K8" t="n">
-        <v>211.92</v>
+        <v>174.28</v>
       </c>
       <c r="L8" t="n">
         <v>41</v>
@@ -970,10 +970,10 @@
         <v>103</v>
       </c>
       <c r="J9" t="n">
-        <v>31.3</v>
+        <v>56.12</v>
       </c>
       <c r="K9" t="n">
-        <v>178.16</v>
+        <v>152.14</v>
       </c>
       <c r="L9" t="n">
         <v>39</v>
@@ -1030,10 +1030,10 @@
         <v>100.84</v>
       </c>
       <c r="J10" t="n">
-        <v>28.4</v>
+        <v>53.47</v>
       </c>
       <c r="K10" t="n">
-        <v>210.34</v>
+        <v>172.44</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
@@ -1090,10 +1090,10 @@
         <v>99.76000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>46.7</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>205.98</v>
+        <v>169.21</v>
       </c>
       <c r="L11" t="n">
         <v>44</v>
@@ -1150,10 +1150,10 @@
         <v>99.56</v>
       </c>
       <c r="J12" t="n">
-        <v>30.2</v>
+        <v>54.21</v>
       </c>
       <c r="K12" t="n">
-        <v>173.18</v>
+        <v>147.7</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
@@ -1210,10 +1210,10 @@
         <v>99.52</v>
       </c>
       <c r="J13" t="n">
-        <v>47</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>207.06</v>
+        <v>169.84</v>
       </c>
       <c r="L13" t="n">
         <v>39</v>
@@ -1270,10 +1270,10 @@
         <v>98.69</v>
       </c>
       <c r="J14" t="n">
-        <v>28.6</v>
+        <v>52.86</v>
       </c>
       <c r="K14" t="n">
-        <v>172.48</v>
+        <v>146.94</v>
       </c>
       <c r="L14" t="n">
         <v>41</v>
@@ -1330,10 +1330,10 @@
         <v>97.5</v>
       </c>
       <c r="J15" t="n">
-        <v>41.9</v>
+        <v>61.15</v>
       </c>
       <c r="K15" t="n">
-        <v>201.42</v>
+        <v>165.45</v>
       </c>
       <c r="L15" t="n">
         <v>41</v>
@@ -1390,10 +1390,10 @@
         <v>96.83</v>
       </c>
       <c r="J16" t="n">
-        <v>42.7</v>
+        <v>61.44</v>
       </c>
       <c r="K16" t="n">
-        <v>198.32</v>
+        <v>163.19</v>
       </c>
       <c r="L16" t="n">
         <v>40</v>
@@ -1450,10 +1450,10 @@
         <v>96.52</v>
       </c>
       <c r="J17" t="n">
-        <v>28.7</v>
+        <v>52.17</v>
       </c>
       <c r="K17" t="n">
-        <v>168.92</v>
+        <v>143.86</v>
       </c>
       <c r="L17" t="n">
         <v>40</v>
@@ -1510,10 +1510,10 @@
         <v>96.38</v>
       </c>
       <c r="J18" t="n">
-        <v>43.1</v>
+        <v>61.54</v>
       </c>
       <c r="K18" t="n">
-        <v>199.22</v>
+        <v>163.62</v>
       </c>
       <c r="L18" t="n">
         <v>41</v>
@@ -1570,10 +1570,10 @@
         <v>92.67</v>
       </c>
       <c r="J19" t="n">
-        <v>25.6</v>
+        <v>48.82</v>
       </c>
       <c r="K19" t="n">
-        <v>164.26</v>
+        <v>139.48</v>
       </c>
       <c r="L19" t="n">
         <v>39</v>
@@ -1630,10 +1630,10 @@
         <v>92.5</v>
       </c>
       <c r="J20" t="n">
-        <v>25.2</v>
+        <v>48.49</v>
       </c>
       <c r="K20" t="n">
-        <v>164.12</v>
+        <v>139.33</v>
       </c>
       <c r="L20" t="n">
         <v>42</v>
@@ -1690,10 +1690,10 @@
         <v>91.54000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>23.7</v>
+        <v>47.18</v>
       </c>
       <c r="K21" t="n">
-        <v>163.5</v>
+        <v>138.59</v>
       </c>
       <c r="L21" t="n">
         <v>39</v>
@@ -1750,10 +1750,10 @@
         <v>91.15000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>26.6</v>
+        <v>48.94</v>
       </c>
       <c r="K22" t="n">
-        <v>143.76</v>
+        <v>125.55</v>
       </c>
       <c r="L22" t="n">
         <v>41</v>
@@ -1810,10 +1810,10 @@
         <v>91</v>
       </c>
       <c r="J23" t="n">
-        <v>40.2</v>
+        <v>57.78</v>
       </c>
       <c r="K23" t="n">
-        <v>196.86</v>
+        <v>160.22</v>
       </c>
       <c r="L23" t="n">
         <v>41</v>
@@ -1870,10 +1870,10 @@
         <v>90.45</v>
       </c>
       <c r="J24" t="n">
-        <v>24.3</v>
+        <v>47.2</v>
       </c>
       <c r="K24" t="n">
-        <v>161</v>
+        <v>136.58</v>
       </c>
       <c r="L24" t="n">
         <v>37</v>
@@ -1930,10 +1930,10 @@
         <v>90.03</v>
       </c>
       <c r="J25" t="n">
-        <v>5.4</v>
+        <v>34.69</v>
       </c>
       <c r="K25" t="n">
-        <v>146.48</v>
+        <v>126.94</v>
       </c>
       <c r="L25" t="n">
         <v>37</v>
@@ -1990,10 +1990,10 @@
         <v>89.73999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>25.7</v>
+        <v>47.87</v>
       </c>
       <c r="K26" t="n">
-        <v>142.16</v>
+        <v>124.02</v>
       </c>
       <c r="L26" t="n">
         <v>39</v>
@@ -2050,10 +2050,10 @@
         <v>88.77</v>
       </c>
       <c r="J27" t="n">
-        <v>22.7</v>
+        <v>45.57</v>
       </c>
       <c r="K27" t="n">
-        <v>193.32</v>
+        <v>157.13</v>
       </c>
       <c r="L27" t="n">
         <v>38</v>
@@ -2110,10 +2110,10 @@
         <v>87.75</v>
       </c>
       <c r="J28" t="n">
-        <v>24.2</v>
+        <v>46.2</v>
       </c>
       <c r="K28" t="n">
-        <v>139.44</v>
+        <v>121.55</v>
       </c>
       <c r="L28" t="n">
         <v>42</v>
@@ -2170,10 +2170,10 @@
         <v>86.5</v>
       </c>
       <c r="J29" t="n">
-        <v>37.6</v>
+        <v>54.53</v>
       </c>
       <c r="K29" t="n">
-        <v>190.7</v>
+        <v>154.63</v>
       </c>
       <c r="L29" t="n">
         <v>41</v>
@@ -2230,10 +2230,10 @@
         <v>86.28</v>
       </c>
       <c r="J30" t="n">
-        <v>20.3</v>
+        <v>43.14</v>
       </c>
       <c r="K30" t="n">
-        <v>156.62</v>
+        <v>132.27</v>
       </c>
       <c r="L30" t="n">
         <v>39</v>
@@ -2290,10 +2290,10 @@
         <v>84.91</v>
       </c>
       <c r="J31" t="n">
-        <v>21.4</v>
+        <v>43.38</v>
       </c>
       <c r="K31" t="n">
-        <v>187.58</v>
+        <v>152.04</v>
       </c>
       <c r="L31" t="n">
         <v>39</v>
@@ -2350,10 +2350,10 @@
         <v>83.70999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>20.3</v>
+        <v>42.25</v>
       </c>
       <c r="K32" t="n">
-        <v>135</v>
+        <v>117.25</v>
       </c>
       <c r="L32" t="n">
         <v>38</v>
@@ -2410,10 +2410,10 @@
         <v>83.02</v>
       </c>
       <c r="J33" t="n">
-        <v>19</v>
+        <v>41.16</v>
       </c>
       <c r="K33" t="n">
-        <v>134.72</v>
+        <v>116.82</v>
       </c>
       <c r="L33" t="n">
         <v>36</v>
@@ -2559,10 +2559,10 @@
         <v>5.541</v>
       </c>
       <c r="L2" t="n">
-        <v>-9</v>
+        <v>-3.967</v>
       </c>
       <c r="M2" t="n">
-        <v>26.066</v>
+        <v>18.962</v>
       </c>
     </row>
     <row r="3">
@@ -2604,10 +2604,10 @@
         <v>4.497</v>
       </c>
       <c r="L3" t="n">
-        <v>-9</v>
+        <v>-4.328</v>
       </c>
       <c r="M3" t="n">
-        <v>26.56</v>
+        <v>18.923</v>
       </c>
     </row>
     <row r="4">
@@ -2649,10 +2649,10 @@
         <v>5.087</v>
       </c>
       <c r="L4" t="n">
-        <v>-9</v>
+        <v>-4.124</v>
       </c>
       <c r="M4" t="n">
-        <v>24.972</v>
+        <v>18.089</v>
       </c>
     </row>
     <row r="5">
@@ -2694,10 +2694,10 @@
         <v>4.416</v>
       </c>
       <c r="L5" t="n">
-        <v>-9</v>
+        <v>-4.356</v>
       </c>
       <c r="M5" t="n">
-        <v>22.224</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="6">
@@ -2739,10 +2739,10 @@
         <v>4.862</v>
       </c>
       <c r="L6" t="n">
-        <v>-9</v>
+        <v>-4.202</v>
       </c>
       <c r="M6" t="n">
-        <v>24.208</v>
+        <v>17.512</v>
       </c>
     </row>
     <row r="7">
@@ -2784,10 +2784,10 @@
         <v>4.395</v>
       </c>
       <c r="L7" t="n">
-        <v>-9</v>
+        <v>-4.364</v>
       </c>
       <c r="M7" t="n">
-        <v>22.386</v>
+        <v>16.159</v>
       </c>
     </row>
     <row r="8">
@@ -2829,10 +2829,10 @@
         <v>5.343</v>
       </c>
       <c r="L8" t="n">
-        <v>-7</v>
+        <v>-2.728</v>
       </c>
       <c r="M8" t="n">
-        <v>28.268</v>
+        <v>20.333</v>
       </c>
     </row>
     <row r="9">
@@ -2874,10 +2874,10 @@
         <v>4.959</v>
       </c>
       <c r="L9" t="n">
-        <v>-9</v>
+        <v>-4.168</v>
       </c>
       <c r="M9" t="n">
-        <v>27.542</v>
+        <v>19.725</v>
       </c>
     </row>
     <row r="10">
@@ -2919,10 +2919,10 @@
         <v>4.367</v>
       </c>
       <c r="L10" t="n">
-        <v>-9</v>
+        <v>-4.373</v>
       </c>
       <c r="M10" t="n">
-        <v>23.32</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="11">
@@ -2964,10 +2964,10 @@
         <v>4.493</v>
       </c>
       <c r="L11" t="n">
-        <v>-9</v>
+        <v>-4.33</v>
       </c>
       <c r="M11" t="n">
-        <v>25.566</v>
+        <v>18.272</v>
       </c>
     </row>
     <row r="12">
@@ -3009,10 +3009,10 @@
         <v>4.444</v>
       </c>
       <c r="L12" t="n">
-        <v>-9</v>
+        <v>-4.347</v>
       </c>
       <c r="M12" t="n">
-        <v>26.39</v>
+        <v>18.794</v>
       </c>
     </row>
     <row r="13">
@@ -3054,10 +3054,10 @@
         <v>5.651</v>
       </c>
       <c r="L13" t="n">
-        <v>-7</v>
+        <v>-2.621</v>
       </c>
       <c r="M13" t="n">
-        <v>29.298</v>
+        <v>21.113</v>
       </c>
     </row>
     <row r="14">
@@ -3099,10 +3099,10 @@
         <v>4.641</v>
       </c>
       <c r="L14" t="n">
-        <v>-9</v>
+        <v>-4.278</v>
       </c>
       <c r="M14" t="n">
-        <v>25.692</v>
+        <v>18.406</v>
       </c>
     </row>
     <row r="15">
@@ -3144,10 +3144,10 @@
         <v>5.083</v>
       </c>
       <c r="L15" t="n">
-        <v>-7</v>
+        <v>-2.818</v>
       </c>
       <c r="M15" t="n">
-        <v>27.946</v>
+        <v>20.032</v>
       </c>
     </row>
     <row r="16">
@@ -3189,10 +3189,10 @@
         <v>5.215</v>
       </c>
       <c r="L16" t="n">
-        <v>-9</v>
+        <v>-4.08</v>
       </c>
       <c r="M16" t="n">
-        <v>25.156</v>
+        <v>18.254</v>
       </c>
     </row>
     <row r="17">
@@ -3234,10 +3234,10 @@
         <v>4.816</v>
       </c>
       <c r="L17" t="n">
-        <v>-7</v>
+        <v>-2.91</v>
       </c>
       <c r="M17" t="n">
-        <v>27.022</v>
+        <v>19.336</v>
       </c>
     </row>
     <row r="18">
@@ -3279,10 +3279,10 @@
         <v>5.208</v>
       </c>
       <c r="L18" t="n">
-        <v>-7</v>
+        <v>-2.774</v>
       </c>
       <c r="M18" t="n">
-        <v>28.192</v>
+        <v>20.236</v>
       </c>
     </row>
     <row r="19">
@@ -3324,10 +3324,10 @@
         <v>6.011</v>
       </c>
       <c r="L19" t="n">
-        <v>-9</v>
+        <v>-3.804</v>
       </c>
       <c r="M19" t="n">
-        <v>30.14</v>
+        <v>21.788</v>
       </c>
     </row>
     <row r="20">
@@ -3369,10 +3369,10 @@
         <v>6.154</v>
       </c>
       <c r="L20" t="n">
-        <v>-9</v>
+        <v>-3.755</v>
       </c>
       <c r="M20" t="n">
-        <v>30.404</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="21">
@@ -3414,10 +3414,10 @@
         <v>6.293</v>
       </c>
       <c r="L21" t="n">
-        <v>-7</v>
+        <v>-2.399</v>
       </c>
       <c r="M21" t="n">
-        <v>27.974</v>
+        <v>20.469</v>
       </c>
     </row>
     <row r="22">
@@ -3459,10 +3459,10 @@
         <v>6.256</v>
       </c>
       <c r="L22" t="n">
-        <v>-9</v>
+        <v>-3.719</v>
       </c>
       <c r="M22" t="n">
-        <v>30.552</v>
+        <v>22.142</v>
       </c>
     </row>
     <row r="23">
@@ -3504,10 +3504,10 @@
         <v>6.377</v>
       </c>
       <c r="L23" t="n">
-        <v>-9</v>
+        <v>-3.677</v>
       </c>
       <c r="M23" t="n">
-        <v>30.66</v>
+        <v>22.255</v>
       </c>
     </row>
     <row r="24">
@@ -3549,10 +3549,10 @@
         <v>5.929</v>
       </c>
       <c r="L24" t="n">
-        <v>-9</v>
+        <v>-3.833</v>
       </c>
       <c r="M24" t="n">
-        <v>29.938</v>
+        <v>21.628</v>
       </c>
     </row>
     <row r="25">
@@ -3594,10 +3594,10 @@
         <v>6.24</v>
       </c>
       <c r="L25" t="n">
-        <v>-7</v>
+        <v>-2.417</v>
       </c>
       <c r="M25" t="n">
-        <v>30.572</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="26">
@@ -3639,10 +3639,10 @@
         <v>5.729</v>
       </c>
       <c r="L26" t="n">
-        <v>-9</v>
+        <v>-3.902</v>
       </c>
       <c r="M26" t="n">
-        <v>29.418</v>
+        <v>21.218</v>
       </c>
     </row>
     <row r="27">
@@ -3684,10 +3684,10 @@
         <v>6.121</v>
       </c>
       <c r="L27" t="n">
-        <v>-7</v>
+        <v>-2.458</v>
       </c>
       <c r="M27" t="n">
-        <v>30.214</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="28">
@@ -3729,10 +3729,10 @@
         <v>5.72</v>
       </c>
       <c r="L28" t="n">
-        <v>-7</v>
+        <v>-2.597</v>
       </c>
       <c r="M28" t="n">
-        <v>29.392</v>
+        <v>21.198</v>
       </c>
     </row>
     <row r="29">
@@ -3774,10 +3774,10 @@
         <v>5.635</v>
       </c>
       <c r="L29" t="n">
-        <v>-9</v>
+        <v>-3.934</v>
       </c>
       <c r="M29" t="n">
-        <v>29.25</v>
+        <v>21.076</v>
       </c>
     </row>
     <row r="30">
@@ -3819,10 +3819,10 @@
         <v>6.016</v>
       </c>
       <c r="L30" t="n">
-        <v>-9</v>
+        <v>-3.802</v>
       </c>
       <c r="M30" t="n">
-        <v>29.954</v>
+        <v>21.668</v>
       </c>
     </row>
     <row r="31">
@@ -3864,10 +3864,10 @@
         <v>5.82</v>
       </c>
       <c r="L31" t="n">
-        <v>-9</v>
+        <v>-3.87</v>
       </c>
       <c r="M31" t="n">
-        <v>29.692</v>
+        <v>21.429</v>
       </c>
     </row>
     <row r="32">
@@ -3909,10 +3909,10 @@
         <v>6.17</v>
       </c>
       <c r="L32" t="n">
-        <v>-7</v>
+        <v>-2.441</v>
       </c>
       <c r="M32" t="n">
-        <v>30.492</v>
+        <v>22.073</v>
       </c>
     </row>
     <row r="33">
@@ -3954,10 +3954,10 @@
         <v>5.943</v>
       </c>
       <c r="L33" t="n">
-        <v>-9</v>
+        <v>-3.828</v>
       </c>
       <c r="M33" t="n">
-        <v>29.828</v>
+        <v>21.561</v>
       </c>
     </row>
     <row r="34">
@@ -3999,10 +3999,10 @@
         <v>6.531</v>
       </c>
       <c r="L34" t="n">
-        <v>-9</v>
+        <v>-3.624</v>
       </c>
       <c r="M34" t="n">
-        <v>31.082</v>
+        <v>22.584</v>
       </c>
     </row>
     <row r="35">
@@ -4044,10 +4044,10 @@
         <v>6.054</v>
       </c>
       <c r="L35" t="n">
-        <v>-9</v>
+        <v>-3.789</v>
       </c>
       <c r="M35" t="n">
-        <v>30.214</v>
+        <v>21.851</v>
       </c>
     </row>
     <row r="36">
@@ -4089,10 +4089,10 @@
         <v>6.613</v>
       </c>
       <c r="L36" t="n">
-        <v>-7</v>
+        <v>-2.288</v>
       </c>
       <c r="M36" t="n">
-        <v>30.776</v>
+        <v>22.412</v>
       </c>
     </row>
     <row r="37">
@@ -4134,10 +4134,10 @@
         <v>7.516</v>
       </c>
       <c r="L37" t="n">
-        <v>-7</v>
+        <v>-1.976</v>
       </c>
       <c r="M37" t="n">
-        <v>30.418</v>
+        <v>22.491</v>
       </c>
     </row>
     <row r="38">
@@ -4179,10 +4179,10 @@
         <v>6.168</v>
       </c>
       <c r="L38" t="n">
-        <v>-9</v>
+        <v>-3.75</v>
       </c>
       <c r="M38" t="n">
-        <v>29.696</v>
+        <v>21.552</v>
       </c>
     </row>
     <row r="39">
@@ -4224,10 +4224,10 @@
         <v>6.645</v>
       </c>
       <c r="L39" t="n">
-        <v>-7</v>
+        <v>-2.277</v>
       </c>
       <c r="M39" t="n">
-        <v>30.932</v>
+        <v>22.525</v>
       </c>
     </row>
     <row r="40">
@@ -4269,10 +4269,10 @@
         <v>5.984</v>
       </c>
       <c r="L40" t="n">
-        <v>-9</v>
+        <v>-3.814</v>
       </c>
       <c r="M40" t="n">
-        <v>29.474</v>
+        <v>21.343</v>
       </c>
     </row>
     <row r="41">
@@ -4314,10 +4314,10 @@
         <v>6.137</v>
       </c>
       <c r="L41" t="n">
-        <v>-9</v>
+        <v>-3.761</v>
       </c>
       <c r="M41" t="n">
-        <v>29.748</v>
+        <v>21.575</v>
       </c>
     </row>
     <row r="42">
@@ -4359,10 +4359,10 @@
         <v>6.333</v>
       </c>
       <c r="L42" t="n">
-        <v>-7</v>
+        <v>-2.385</v>
       </c>
       <c r="M42" t="n">
-        <v>30.082</v>
+        <v>21.862</v>
       </c>
     </row>
     <row r="43">
@@ -4404,10 +4404,10 @@
         <v>6.373</v>
       </c>
       <c r="L43" t="n">
-        <v>-9</v>
+        <v>-3.679</v>
       </c>
       <c r="M43" t="n">
-        <v>28.16</v>
+        <v>20.619</v>
       </c>
     </row>
     <row r="44">
@@ -4449,10 +4449,10 @@
         <v>6.738</v>
       </c>
       <c r="L44" t="n">
-        <v>-7</v>
+        <v>-2.245</v>
       </c>
       <c r="M44" t="n">
-        <v>28.818</v>
+        <v>21.175</v>
       </c>
     </row>
     <row r="45">
@@ -4494,10 +4494,10 @@
         <v>7.985</v>
       </c>
       <c r="L45" t="n">
-        <v>-7</v>
+        <v>-1.813</v>
       </c>
       <c r="M45" t="n">
-        <v>31.578</v>
+        <v>23.412</v>
       </c>
     </row>
     <row r="46">
@@ -4539,10 +4539,10 @@
         <v>6.068</v>
       </c>
       <c r="L46" t="n">
-        <v>-9</v>
+        <v>-3.784</v>
       </c>
       <c r="M46" t="n">
-        <v>29.614</v>
+        <v>21.464</v>
       </c>
     </row>
     <row r="47">
@@ -4584,10 +4584,10 @@
         <v>6.81</v>
       </c>
       <c r="L47" t="n">
-        <v>-9</v>
+        <v>-3.528</v>
       </c>
       <c r="M47" t="n">
-        <v>28.898</v>
+        <v>21.253</v>
       </c>
     </row>
     <row r="48">
@@ -4629,10 +4629,10 @@
         <v>6.805</v>
       </c>
       <c r="L48" t="n">
-        <v>-7</v>
+        <v>-2.222</v>
       </c>
       <c r="M48" t="n">
-        <v>28.91</v>
+        <v>21.259</v>
       </c>
     </row>
     <row r="49">
@@ -4674,10 +4674,10 @@
         <v>6.126</v>
       </c>
       <c r="L49" t="n">
-        <v>-9</v>
+        <v>-3.764</v>
       </c>
       <c r="M49" t="n">
-        <v>29.796</v>
+        <v>21.603</v>
       </c>
     </row>
     <row r="50">
@@ -4719,10 +4719,10 @@
         <v>7.234</v>
       </c>
       <c r="L50" t="n">
-        <v>-9</v>
+        <v>-3.381</v>
       </c>
       <c r="M50" t="n">
-        <v>29.918</v>
+        <v>22.066</v>
       </c>
     </row>
     <row r="51">
@@ -4764,10 +4764,10 @@
         <v>6.217</v>
       </c>
       <c r="L51" t="n">
-        <v>-7</v>
+        <v>-2.425</v>
       </c>
       <c r="M51" t="n">
-        <v>29.902</v>
+        <v>21.704</v>
       </c>
     </row>
     <row r="52">
@@ -4809,10 +4809,10 @@
         <v>7.227</v>
       </c>
       <c r="L52" t="n">
-        <v>-7</v>
+        <v>-2.076</v>
       </c>
       <c r="M52" t="n">
-        <v>29.976</v>
+        <v>22.102</v>
       </c>
     </row>
     <row r="53">
@@ -4854,10 +4854,10 @@
         <v>5.561</v>
       </c>
       <c r="L53" t="n">
-        <v>-9</v>
+        <v>-3.96</v>
       </c>
       <c r="M53" t="n">
-        <v>29.11</v>
+        <v>20.959</v>
       </c>
     </row>
     <row r="54">
@@ -4899,10 +4899,10 @@
         <v>5.603</v>
       </c>
       <c r="L54" t="n">
-        <v>-9</v>
+        <v>-3.945</v>
       </c>
       <c r="M54" t="n">
-        <v>29.19</v>
+        <v>21.026</v>
       </c>
     </row>
     <row r="55">
@@ -4944,10 +4944,10 @@
         <v>6.29</v>
       </c>
       <c r="L55" t="n">
-        <v>-7</v>
+        <v>-2.4</v>
       </c>
       <c r="M55" t="n">
-        <v>30.764</v>
+        <v>22.293</v>
       </c>
     </row>
     <row r="56">
@@ -4989,10 +4989,10 @@
         <v>6.438</v>
       </c>
       <c r="L56" t="n">
-        <v>-7</v>
+        <v>-2.349</v>
       </c>
       <c r="M56" t="n">
-        <v>28.76</v>
+        <v>21.034</v>
       </c>
     </row>
     <row r="57">
@@ -5034,10 +5034,10 @@
         <v>4.862</v>
       </c>
       <c r="L57" t="n">
-        <v>-9</v>
+        <v>-4.202</v>
       </c>
       <c r="M57" t="n">
-        <v>27.692</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="58">
@@ -5079,10 +5079,10 @@
         <v>5.468</v>
       </c>
       <c r="L58" t="n">
-        <v>-7</v>
+        <v>-2.684</v>
       </c>
       <c r="M58" t="n">
-        <v>28.89</v>
+        <v>20.783</v>
       </c>
     </row>
     <row r="59">
@@ -5124,10 +5124,10 @@
         <v>5.81</v>
       </c>
       <c r="L59" t="n">
-        <v>-7</v>
+        <v>-2.566</v>
       </c>
       <c r="M59" t="n">
-        <v>29.504</v>
+        <v>21.303</v>
       </c>
     </row>
     <row r="60">
@@ -5169,10 +5169,10 @@
         <v>5.212</v>
       </c>
       <c r="L60" t="n">
-        <v>-7</v>
+        <v>-2.773</v>
       </c>
       <c r="M60" t="n">
-        <v>28.382</v>
+        <v>20.362</v>
       </c>
     </row>
     <row r="61">
@@ -5214,10 +5214,10 @@
         <v>5.607</v>
       </c>
       <c r="L61" t="n">
-        <v>-7</v>
+        <v>-2.636</v>
       </c>
       <c r="M61" t="n">
-        <v>29.368</v>
+        <v>21.143</v>
       </c>
     </row>
     <row r="62">
@@ -5259,10 +5259,10 @@
         <v>5.462</v>
       </c>
       <c r="L62" t="n">
-        <v>-7</v>
+        <v>-2.686</v>
       </c>
       <c r="M62" t="n">
-        <v>29.064</v>
+        <v>20.895</v>
       </c>
     </row>
     <row r="63">
@@ -5304,10 +5304,10 @@
         <v>6.26</v>
       </c>
       <c r="L63" t="n">
-        <v>-7</v>
+        <v>-2.41</v>
       </c>
       <c r="M63" t="n">
-        <v>28.45</v>
+        <v>20.769</v>
       </c>
     </row>
     <row r="64">
@@ -5349,10 +5349,10 @@
         <v>5.343</v>
       </c>
       <c r="L64" t="n">
-        <v>-9</v>
+        <v>-4.035</v>
       </c>
       <c r="M64" t="n">
-        <v>28.59</v>
+        <v>20.543</v>
       </c>
     </row>
     <row r="65">
@@ -5394,10 +5394,10 @@
         <v>5.981</v>
       </c>
       <c r="L65" t="n">
-        <v>-7</v>
+        <v>-2.507</v>
       </c>
       <c r="M65" t="n">
-        <v>30.354</v>
+        <v>21.918</v>
       </c>
     </row>
     <row r="66">
@@ -5439,10 +5439,10 @@
         <v>5.615</v>
       </c>
       <c r="L66" t="n">
-        <v>-9</v>
+        <v>-3.941</v>
       </c>
       <c r="M66" t="n">
-        <v>29.3</v>
+        <v>21.102</v>
       </c>
     </row>
     <row r="67">
@@ -5484,10 +5484,10 @@
         <v>5.881</v>
       </c>
       <c r="L67" t="n">
-        <v>-7</v>
+        <v>-2.541</v>
       </c>
       <c r="M67" t="n">
-        <v>29.85</v>
+        <v>21.553</v>
       </c>
     </row>
     <row r="68">
@@ -5529,10 +5529,10 @@
         <v>5.34</v>
       </c>
       <c r="L68" t="n">
-        <v>-7</v>
+        <v>-2.729</v>
       </c>
       <c r="M68" t="n">
-        <v>28.834</v>
+        <v>20.702</v>
       </c>
     </row>
     <row r="69">
@@ -5574,10 +5574,10 @@
         <v>6.765</v>
       </c>
       <c r="L69" t="n">
-        <v>-7</v>
+        <v>-2.235</v>
       </c>
       <c r="M69" t="n">
-        <v>29.658</v>
+        <v>21.734</v>
       </c>
     </row>
     <row r="70">
@@ -5619,10 +5619,10 @@
         <v>5.358</v>
       </c>
       <c r="L70" t="n">
-        <v>-9</v>
+        <v>-4.03</v>
       </c>
       <c r="M70" t="n">
-        <v>29.45</v>
+        <v>21.111</v>
       </c>
     </row>
     <row r="71">
@@ -5664,10 +5664,10 @@
         <v>5.315</v>
       </c>
       <c r="L71" t="n">
-        <v>-9</v>
+        <v>-4.045</v>
       </c>
       <c r="M71" t="n">
-        <v>29.41</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="72">
@@ -5709,10 +5709,10 @@
         <v>5.184</v>
       </c>
       <c r="L72" t="n">
-        <v>-9</v>
+        <v>-4.09</v>
       </c>
       <c r="M72" t="n">
-        <v>29.056</v>
+        <v>20.793</v>
       </c>
     </row>
     <row r="73">
@@ -5754,10 +5754,10 @@
         <v>5.229</v>
       </c>
       <c r="L73" t="n">
-        <v>-9</v>
+        <v>-4.075</v>
       </c>
       <c r="M73" t="n">
-        <v>29.014</v>
+        <v>20.781</v>
       </c>
     </row>
     <row r="74">
@@ -5799,10 +5799,10 @@
         <v>5.041</v>
       </c>
       <c r="L74" t="n">
-        <v>-9</v>
+        <v>-4.14</v>
       </c>
       <c r="M74" t="n">
-        <v>28.698</v>
+        <v>20.509</v>
       </c>
     </row>
     <row r="75">
@@ -5844,10 +5844,10 @@
         <v>5.282</v>
       </c>
       <c r="L75" t="n">
-        <v>-9</v>
+        <v>-4.056</v>
       </c>
       <c r="M75" t="n">
-        <v>29.166</v>
+        <v>20.899</v>
       </c>
     </row>
     <row r="76">
@@ -5889,10 +5889,10 @@
         <v>4.818</v>
       </c>
       <c r="L76" t="n">
-        <v>-7</v>
+        <v>-2.909</v>
       </c>
       <c r="M76" t="n">
-        <v>27.802</v>
+        <v>19.846</v>
       </c>
     </row>
     <row r="77">
@@ -5934,10 +5934,10 @@
         <v>5.679</v>
       </c>
       <c r="L77" t="n">
-        <v>-7</v>
+        <v>-2.611</v>
       </c>
       <c r="M77" t="n">
-        <v>30.086</v>
+        <v>21.638</v>
       </c>
     </row>
     <row r="78">
@@ -5979,10 +5979,10 @@
         <v>5.593</v>
       </c>
       <c r="L78" t="n">
-        <v>-9</v>
+        <v>-3.949</v>
       </c>
       <c r="M78" t="n">
-        <v>29.908</v>
+        <v>21.492</v>
       </c>
     </row>
     <row r="79">
@@ -6024,10 +6024,10 @@
         <v>5.46</v>
       </c>
       <c r="L79" t="n">
-        <v>-9</v>
+        <v>-3.995</v>
       </c>
       <c r="M79" t="n">
-        <v>29.424</v>
+        <v>21.129</v>
       </c>
     </row>
     <row r="80">
@@ -6069,10 +6069,10 @@
         <v>5.102</v>
       </c>
       <c r="L80" t="n">
-        <v>-9</v>
+        <v>-4.119</v>
       </c>
       <c r="M80" t="n">
-        <v>28.806</v>
+        <v>20.601</v>
       </c>
     </row>
     <row r="81">
@@ -6114,10 +6114,10 @@
         <v>4.877</v>
       </c>
       <c r="L81" t="n">
-        <v>-9</v>
+        <v>-4.197</v>
       </c>
       <c r="M81" t="n">
-        <v>28.292</v>
+        <v>20.187</v>
       </c>
     </row>
     <row r="82">
@@ -6159,10 +6159,10 @@
         <v>5.781</v>
       </c>
       <c r="L82" t="n">
-        <v>-9</v>
+        <v>-3.884</v>
       </c>
       <c r="M82" t="n">
-        <v>30.278</v>
+        <v>21.799</v>
       </c>
     </row>
     <row r="83">
@@ -6204,10 +6204,10 @@
         <v>5.722</v>
       </c>
       <c r="L83" t="n">
-        <v>-7</v>
+        <v>-2.596</v>
       </c>
       <c r="M83" t="n">
-        <v>30.198</v>
+        <v>21.726</v>
       </c>
     </row>
     <row r="84">
@@ -6249,10 +6249,10 @@
         <v>5.473</v>
       </c>
       <c r="L84" t="n">
-        <v>-9</v>
+        <v>-3.99</v>
       </c>
       <c r="M84" t="n">
-        <v>29.748</v>
+        <v>21.346</v>
       </c>
     </row>
     <row r="85">
@@ -6294,10 +6294,10 @@
         <v>4.681</v>
       </c>
       <c r="L85" t="n">
-        <v>-9</v>
+        <v>-4.265</v>
       </c>
       <c r="M85" t="n">
-        <v>27.826</v>
+        <v>19.815</v>
       </c>
     </row>
     <row r="86">
@@ -6339,10 +6339,10 @@
         <v>5.434</v>
       </c>
       <c r="L86" t="n">
-        <v>-7</v>
+        <v>-2.696</v>
       </c>
       <c r="M86" t="n">
-        <v>29.64</v>
+        <v>21.261</v>
       </c>
     </row>
     <row r="87">
@@ -6384,10 +6384,10 @@
         <v>5.46</v>
       </c>
       <c r="L87" t="n">
-        <v>-9</v>
+        <v>-3.995</v>
       </c>
       <c r="M87" t="n">
-        <v>28.894</v>
+        <v>20.783</v>
       </c>
     </row>
     <row r="88">
@@ -6429,10 +6429,10 @@
         <v>5.182</v>
       </c>
       <c r="L88" t="n">
-        <v>-9</v>
+        <v>-4.091</v>
       </c>
       <c r="M88" t="n">
-        <v>28.102</v>
+        <v>20.169</v>
       </c>
     </row>
     <row r="89">
@@ -6474,10 +6474,10 @@
         <v>5.105</v>
       </c>
       <c r="L89" t="n">
-        <v>-9</v>
+        <v>-4.118</v>
       </c>
       <c r="M89" t="n">
-        <v>27.936</v>
+        <v>20.033</v>
       </c>
     </row>
     <row r="90">
@@ -6519,10 +6519,10 @@
         <v>5.761</v>
       </c>
       <c r="L90" t="n">
-        <v>-7</v>
+        <v>-2.583</v>
       </c>
       <c r="M90" t="n">
-        <v>29.634</v>
+        <v>21.371</v>
       </c>
     </row>
     <row r="91">
@@ -6564,10 +6564,10 @@
         <v>5.838</v>
       </c>
       <c r="L91" t="n">
-        <v>-9</v>
+        <v>-3.864</v>
       </c>
       <c r="M91" t="n">
-        <v>29.918</v>
+        <v>21.583</v>
       </c>
     </row>
     <row r="92">
@@ -6609,10 +6609,10 @@
         <v>5.595</v>
       </c>
       <c r="L92" t="n">
-        <v>-9</v>
+        <v>-3.948</v>
       </c>
       <c r="M92" t="n">
-        <v>29.274</v>
+        <v>21.078</v>
       </c>
     </row>
     <row r="93">
@@ -6654,10 +6654,10 @@
         <v>5.333</v>
       </c>
       <c r="L93" t="n">
-        <v>-9</v>
+        <v>-4.039</v>
       </c>
       <c r="M93" t="n">
-        <v>28.37</v>
+        <v>20.396</v>
       </c>
     </row>
     <row r="94">
@@ -6699,10 +6699,10 @@
         <v>4.758</v>
       </c>
       <c r="L94" t="n">
-        <v>-9</v>
+        <v>-4.238</v>
       </c>
       <c r="M94" t="n">
-        <v>27.352</v>
+        <v>19.531</v>
       </c>
     </row>
     <row r="95">
@@ -6744,10 +6744,10 @@
         <v>5.36</v>
       </c>
       <c r="L95" t="n">
-        <v>-9</v>
+        <v>-4.029</v>
       </c>
       <c r="M95" t="n">
-        <v>28.53</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="96">
@@ -6789,10 +6789,10 @@
         <v>6.121</v>
       </c>
       <c r="L96" t="n">
-        <v>-9</v>
+        <v>-3.766</v>
       </c>
       <c r="M96" t="n">
-        <v>30.246</v>
+        <v>21.895</v>
       </c>
     </row>
     <row r="97">
@@ -6834,10 +6834,10 @@
         <v>5.237</v>
       </c>
       <c r="L97" t="n">
-        <v>-9</v>
+        <v>-4.072</v>
       </c>
       <c r="M97" t="n">
-        <v>28.264</v>
+        <v>20.294</v>
       </c>
     </row>
     <row r="98">
@@ -6879,10 +6879,10 @@
         <v>5.279</v>
       </c>
       <c r="L98" t="n">
-        <v>-9</v>
+        <v>-4.058</v>
       </c>
       <c r="M98" t="n">
-        <v>28.354</v>
+        <v>20.367</v>
       </c>
     </row>
     <row r="99">
@@ -6924,10 +6924,10 @@
         <v>5.231</v>
       </c>
       <c r="L99" t="n">
-        <v>-9</v>
+        <v>-4.074</v>
       </c>
       <c r="M99" t="n">
-        <v>28.46</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="100">
@@ -6969,10 +6969,10 @@
         <v>4.764</v>
       </c>
       <c r="L100" t="n">
-        <v>-9</v>
+        <v>-4.236</v>
       </c>
       <c r="M100" t="n">
-        <v>27.288</v>
+        <v>19.492</v>
       </c>
     </row>
     <row r="101">
@@ -7014,10 +7014,10 @@
         <v>5.996</v>
       </c>
       <c r="L101" t="n">
-        <v>-7</v>
+        <v>-2.502</v>
       </c>
       <c r="M101" t="n">
-        <v>30.208</v>
+        <v>21.827</v>
       </c>
     </row>
     <row r="102">
@@ -7059,10 +7059,10 @@
         <v>5.444</v>
       </c>
       <c r="L102" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="M102" t="n">
-        <v>28.664</v>
+        <v>20.627</v>
       </c>
     </row>
     <row r="103">
@@ -7104,10 +7104,10 @@
         <v>5.074</v>
       </c>
       <c r="L103" t="n">
-        <v>-9</v>
+        <v>-4.128</v>
       </c>
       <c r="M103" t="n">
-        <v>27.922</v>
+        <v>20.014</v>
       </c>
     </row>
     <row r="104">
@@ -7149,10 +7149,10 @@
         <v>5.126</v>
       </c>
       <c r="L104" t="n">
-        <v>-9</v>
+        <v>-4.11</v>
       </c>
       <c r="M104" t="n">
-        <v>27.53</v>
+        <v>19.775</v>
       </c>
     </row>
     <row r="105">
@@ -7194,10 +7194,10 @@
         <v>5.015</v>
       </c>
       <c r="L105" t="n">
-        <v>-9</v>
+        <v>-4.149</v>
       </c>
       <c r="M105" t="n">
-        <v>23.272</v>
+        <v>16.953</v>
       </c>
     </row>
     <row r="106">
@@ -7239,10 +7239,10 @@
         <v>5.331</v>
       </c>
       <c r="L106" t="n">
-        <v>-9</v>
+        <v>-4.04</v>
       </c>
       <c r="M106" t="n">
-        <v>25.16</v>
+        <v>18.296</v>
       </c>
     </row>
     <row r="107">
@@ -7284,10 +7284,10 @@
         <v>5.041</v>
       </c>
       <c r="L107" t="n">
-        <v>-9</v>
+        <v>-4.14</v>
       </c>
       <c r="M107" t="n">
-        <v>24.41</v>
+        <v>17.706</v>
       </c>
     </row>
     <row r="108">
@@ -7329,10 +7329,10 @@
         <v>4.886</v>
       </c>
       <c r="L108" t="n">
-        <v>-9</v>
+        <v>-4.194</v>
       </c>
       <c r="M108" t="n">
-        <v>24.146</v>
+        <v>17.479</v>
       </c>
     </row>
     <row r="109">
@@ -7374,10 +7374,10 @@
         <v>5.185</v>
       </c>
       <c r="L109" t="n">
-        <v>-9</v>
+        <v>-4.09</v>
       </c>
       <c r="M109" t="n">
-        <v>24.588</v>
+        <v>17.872</v>
       </c>
     </row>
     <row r="110">
@@ -7419,10 +7419,10 @@
         <v>5.765</v>
       </c>
       <c r="L110" t="n">
-        <v>-7</v>
+        <v>-2.582</v>
       </c>
       <c r="M110" t="n">
-        <v>29.148</v>
+        <v>21.054</v>
       </c>
     </row>
     <row r="111">
@@ -7464,10 +7464,10 @@
         <v>5.178</v>
       </c>
       <c r="L111" t="n">
-        <v>-9</v>
+        <v>-4.092</v>
       </c>
       <c r="M111" t="n">
-        <v>27.666</v>
+        <v>19.882</v>
       </c>
     </row>
     <row r="112">
@@ -7509,10 +7509,10 @@
         <v>5.425</v>
       </c>
       <c r="L112" t="n">
-        <v>-9</v>
+        <v>-4.007</v>
       </c>
       <c r="M112" t="n">
-        <v>28.34</v>
+        <v>20.408</v>
       </c>
     </row>
     <row r="113">
@@ -7554,10 +7554,10 @@
         <v>5.807</v>
       </c>
       <c r="L113" t="n">
-        <v>-9</v>
+        <v>-3.875</v>
       </c>
       <c r="M113" t="n">
-        <v>29.302</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="114">
@@ -7599,10 +7599,10 @@
         <v>5.692</v>
       </c>
       <c r="L114" t="n">
-        <v>-9</v>
+        <v>-3.915</v>
       </c>
       <c r="M114" t="n">
-        <v>25.798</v>
+        <v>18.839</v>
       </c>
     </row>
     <row r="115">
@@ -7644,10 +7644,10 @@
         <v>5.053</v>
       </c>
       <c r="L115" t="n">
-        <v>-9</v>
+        <v>-4.136</v>
       </c>
       <c r="M115" t="n">
-        <v>26.486</v>
+        <v>19.067</v>
       </c>
     </row>
     <row r="116">
@@ -7689,10 +7689,10 @@
         <v>4.824</v>
       </c>
       <c r="L116" t="n">
-        <v>-9</v>
+        <v>-4.215</v>
       </c>
       <c r="M116" t="n">
-        <v>26.996</v>
+        <v>19.321</v>
       </c>
     </row>
     <row r="117">
@@ -7734,10 +7734,10 @@
         <v>5.178</v>
       </c>
       <c r="L117" t="n">
-        <v>-9</v>
+        <v>-4.092</v>
       </c>
       <c r="M117" t="n">
-        <v>27.706</v>
+        <v>19.908</v>
       </c>
     </row>
     <row r="118">
@@ -7779,10 +7779,10 @@
         <v>5.794</v>
       </c>
       <c r="L118" t="n">
-        <v>-9</v>
+        <v>-3.879</v>
       </c>
       <c r="M118" t="n">
-        <v>26.018</v>
+        <v>19.018</v>
       </c>
     </row>
     <row r="119">
@@ -7824,10 +7824,10 @@
         <v>5.297</v>
       </c>
       <c r="L119" t="n">
-        <v>-9</v>
+        <v>-4.051</v>
       </c>
       <c r="M119" t="n">
-        <v>27.788</v>
+        <v>20.003</v>
       </c>
     </row>
     <row r="120">
@@ -7869,10 +7869,10 @@
         <v>5.143</v>
       </c>
       <c r="L120" t="n">
-        <v>-9</v>
+        <v>-4.105</v>
       </c>
       <c r="M120" t="n">
-        <v>26.666</v>
+        <v>19.216</v>
       </c>
     </row>
     <row r="121">
@@ -7914,10 +7914,10 @@
         <v>5.637</v>
       </c>
       <c r="L121" t="n">
-        <v>-9</v>
+        <v>-3.934</v>
       </c>
       <c r="M121" t="n">
-        <v>29.822</v>
+        <v>21.451</v>
       </c>
     </row>
     <row r="122">
@@ -7959,10 +7959,10 @@
         <v>5.348</v>
       </c>
       <c r="L122" t="n">
-        <v>-9</v>
+        <v>-4.034</v>
       </c>
       <c r="M122" t="n">
-        <v>29.228</v>
+        <v>20.962</v>
       </c>
     </row>
     <row r="123">
@@ -8004,10 +8004,10 @@
         <v>5.853</v>
       </c>
       <c r="L123" t="n">
-        <v>-7</v>
+        <v>-2.551</v>
       </c>
       <c r="M123" t="n">
-        <v>30.312</v>
+        <v>21.846</v>
       </c>
     </row>
     <row r="124">
@@ -8049,10 +8049,10 @@
         <v>5.891</v>
       </c>
       <c r="L124" t="n">
-        <v>-9</v>
+        <v>-3.846</v>
       </c>
       <c r="M124" t="n">
-        <v>30.572</v>
+        <v>22.029</v>
       </c>
     </row>
     <row r="125">
@@ -8094,10 +8094,10 @@
         <v>5.661</v>
       </c>
       <c r="L125" t="n">
-        <v>-7</v>
+        <v>-2.618</v>
       </c>
       <c r="M125" t="n">
-        <v>30.08</v>
+        <v>21.628</v>
       </c>
     </row>
     <row r="126">
@@ -8139,10 +8139,10 @@
         <v>5.767</v>
       </c>
       <c r="L126" t="n">
-        <v>-7</v>
+        <v>-2.581</v>
       </c>
       <c r="M126" t="n">
-        <v>29.976</v>
+        <v>21.596</v>
       </c>
     </row>
     <row r="127">
@@ -8184,10 +8184,10 @@
         <v>5.961</v>
       </c>
       <c r="L127" t="n">
-        <v>-7</v>
+        <v>-2.514</v>
       </c>
       <c r="M127" t="n">
-        <v>30.908</v>
+        <v>22.273</v>
       </c>
     </row>
     <row r="128">
@@ -8229,10 +8229,10 @@
         <v>5.78</v>
       </c>
       <c r="L128" t="n">
-        <v>-9</v>
+        <v>-3.884</v>
       </c>
       <c r="M128" t="n">
-        <v>30.372</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="129">
@@ -8274,10 +8274,10 @@
         <v>6.26</v>
       </c>
       <c r="L129" t="n">
-        <v>-9</v>
+        <v>-3.718</v>
       </c>
       <c r="M129" t="n">
-        <v>31.264</v>
+        <v>22.609</v>
       </c>
     </row>
     <row r="130">
@@ -8319,10 +8319,10 @@
         <v>5.836</v>
       </c>
       <c r="L130" t="n">
-        <v>-9</v>
+        <v>-3.865</v>
       </c>
       <c r="M130" t="n">
-        <v>30.226</v>
+        <v>21.784</v>
       </c>
     </row>
     <row r="131">
@@ -8364,10 +8364,10 @@
         <v>5.497</v>
       </c>
       <c r="L131" t="n">
-        <v>-7</v>
+        <v>-2.674</v>
       </c>
       <c r="M131" t="n">
-        <v>29.314</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="132">
@@ -8409,10 +8409,10 @@
         <v>6.11</v>
       </c>
       <c r="L132" t="n">
-        <v>-7</v>
+        <v>-2.462</v>
       </c>
       <c r="M132" t="n">
-        <v>30.884</v>
+        <v>22.309</v>
       </c>
     </row>
     <row r="133">
@@ -8454,10 +8454,10 @@
         <v>5.888</v>
       </c>
       <c r="L133" t="n">
-        <v>-7</v>
+        <v>-2.539</v>
       </c>
       <c r="M133" t="n">
-        <v>30.464</v>
+        <v>21.957</v>
       </c>
     </row>
     <row r="134">
@@ -8499,10 +8499,10 @@
         <v>5.22</v>
       </c>
       <c r="L134" t="n">
-        <v>-9</v>
+        <v>-4.078</v>
       </c>
       <c r="M134" t="n">
-        <v>28.816</v>
+        <v>20.649</v>
       </c>
     </row>
     <row r="135">
@@ -8544,10 +8544,10 @@
         <v>5.632</v>
       </c>
       <c r="L135" t="n">
-        <v>-9</v>
+        <v>-3.935</v>
       </c>
       <c r="M135" t="n">
-        <v>29.736</v>
+        <v>21.393</v>
       </c>
     </row>
     <row r="136">
@@ -8589,10 +8589,10 @@
         <v>6.383</v>
       </c>
       <c r="L136" t="n">
-        <v>-7</v>
+        <v>-2.368</v>
       </c>
       <c r="M136" t="n">
-        <v>31.538</v>
+        <v>22.831</v>
       </c>
     </row>
     <row r="137">
@@ -8634,10 +8634,10 @@
         <v>5.963</v>
       </c>
       <c r="L137" t="n">
-        <v>-7</v>
+        <v>-2.513</v>
       </c>
       <c r="M137" t="n">
-        <v>30.624</v>
+        <v>22.088</v>
       </c>
     </row>
     <row r="138">
@@ -8679,10 +8679,10 @@
         <v>4.317</v>
       </c>
       <c r="L138" t="n">
-        <v>-9</v>
+        <v>-4.391</v>
       </c>
       <c r="M138" t="n">
-        <v>21.746</v>
+        <v>15.713</v>
       </c>
     </row>
     <row r="139">
@@ -8724,10 +8724,10 @@
         <v>5.852</v>
       </c>
       <c r="L139" t="n">
-        <v>-7</v>
+        <v>-2.551</v>
       </c>
       <c r="M139" t="n">
-        <v>29.902</v>
+        <v>21.577</v>
       </c>
     </row>
     <row r="140">
@@ -8769,10 +8769,10 @@
         <v>5.13</v>
       </c>
       <c r="L140" t="n">
-        <v>-9</v>
+        <v>-4.109</v>
       </c>
       <c r="M140" t="n">
-        <v>27.522</v>
+        <v>19.771</v>
       </c>
     </row>
     <row r="141">
@@ -8814,10 +8814,10 @@
         <v>4.809</v>
       </c>
       <c r="L141" t="n">
-        <v>-9</v>
+        <v>-4.22</v>
       </c>
       <c r="M141" t="n">
-        <v>22.924</v>
+        <v>16.654</v>
       </c>
     </row>
     <row r="142">
@@ -8859,10 +8859,10 @@
         <v>4.693</v>
       </c>
       <c r="L142" t="n">
-        <v>-9</v>
+        <v>-4.26</v>
       </c>
       <c r="M142" t="n">
-        <v>26.69</v>
+        <v>19.076</v>
       </c>
     </row>
     <row r="143">
@@ -8904,10 +8904,10 @@
         <v>5.171</v>
       </c>
       <c r="L143" t="n">
-        <v>-9</v>
+        <v>-4.095</v>
       </c>
       <c r="M143" t="n">
-        <v>28.018</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="144">
@@ -8949,10 +8949,10 @@
         <v>4.532</v>
       </c>
       <c r="L144" t="n">
-        <v>-9</v>
+        <v>-4.316</v>
       </c>
       <c r="M144" t="n">
-        <v>25.25</v>
+        <v>18.079</v>
       </c>
     </row>
     <row r="145">
@@ -8994,10 +8994,10 @@
         <v>5.003</v>
       </c>
       <c r="L145" t="n">
-        <v>-9</v>
+        <v>-4.153</v>
       </c>
       <c r="M145" t="n">
-        <v>27.308</v>
+        <v>19.587</v>
       </c>
     </row>
     <row r="146">
@@ -9039,10 +9039,10 @@
         <v>5.488</v>
       </c>
       <c r="L146" t="n">
-        <v>-9</v>
+        <v>-3.985</v>
       </c>
       <c r="M146" t="n">
-        <v>25.772</v>
+        <v>18.751</v>
       </c>
     </row>
     <row r="147">
@@ -9084,10 +9084,10 @@
         <v>5.437</v>
       </c>
       <c r="L147" t="n">
-        <v>-7</v>
+        <v>-2.695</v>
       </c>
       <c r="M147" t="n">
-        <v>28.878</v>
+        <v>20.764</v>
       </c>
     </row>
     <row r="148">
@@ -9129,10 +9129,10 @@
         <v>5.422</v>
       </c>
       <c r="L148" t="n">
-        <v>-7</v>
+        <v>-2.7</v>
       </c>
       <c r="M148" t="n">
-        <v>28.594</v>
+        <v>20.573</v>
       </c>
     </row>
     <row r="149">
@@ -9174,10 +9174,10 @@
         <v>4.597</v>
       </c>
       <c r="L149" t="n">
-        <v>-9</v>
+        <v>-4.294</v>
       </c>
       <c r="M149" t="n">
-        <v>25.37</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="150">
@@ -9219,10 +9219,10 @@
         <v>4.144</v>
       </c>
       <c r="L150" t="n">
-        <v>-9</v>
+        <v>-4.45</v>
       </c>
       <c r="M150" t="n">
-        <v>22.532</v>
+        <v>16.167</v>
       </c>
     </row>
     <row r="151">
@@ -9264,10 +9264,10 @@
         <v>4.164</v>
       </c>
       <c r="L151" t="n">
-        <v>-9</v>
+        <v>-4.443</v>
       </c>
       <c r="M151" t="n">
-        <v>21.594</v>
+        <v>15.561</v>
       </c>
     </row>
     <row r="152">
@@ -9309,10 +9309,10 @@
         <v>4.826</v>
       </c>
       <c r="L152" t="n">
-        <v>-9</v>
+        <v>-4.214</v>
       </c>
       <c r="M152" t="n">
-        <v>27.006</v>
+        <v>19.329</v>
       </c>
     </row>
     <row r="153">
@@ -9354,10 +9354,10 @@
         <v>4.412</v>
       </c>
       <c r="L153" t="n">
-        <v>-9</v>
+        <v>-4.358</v>
       </c>
       <c r="M153" t="n">
-        <v>21.916</v>
+        <v>15.857</v>
       </c>
     </row>
     <row r="154">
@@ -9399,10 +9399,10 @@
         <v>5.716</v>
       </c>
       <c r="L154" t="n">
-        <v>-9</v>
+        <v>-3.906</v>
       </c>
       <c r="M154" t="n">
-        <v>29.652</v>
+        <v>21.367</v>
       </c>
     </row>
     <row r="155">
@@ -9444,10 +9444,10 @@
         <v>5.609</v>
       </c>
       <c r="L155" t="n">
-        <v>-7</v>
+        <v>-2.636</v>
       </c>
       <c r="M155" t="n">
-        <v>29.102</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="156">
@@ -9489,10 +9489,10 @@
         <v>6.952</v>
       </c>
       <c r="L156" t="n">
-        <v>-7</v>
+        <v>-2.171</v>
       </c>
       <c r="M156" t="n">
-        <v>32.822</v>
+        <v>23.867</v>
       </c>
     </row>
     <row r="157">
@@ -9534,10 +9534,10 @@
         <v>6.308</v>
       </c>
       <c r="L157" t="n">
-        <v>-7</v>
+        <v>-2.394</v>
       </c>
       <c r="M157" t="n">
-        <v>31.488</v>
+        <v>22.772</v>
       </c>
     </row>
     <row r="158">
@@ -9579,10 +9579,10 @@
         <v>5.938</v>
       </c>
       <c r="L158" t="n">
-        <v>-7</v>
+        <v>-2.522</v>
       </c>
       <c r="M158" t="n">
-        <v>29.954</v>
+        <v>21.641</v>
       </c>
     </row>
     <row r="159">
@@ -9624,10 +9624,10 @@
         <v>6.902</v>
       </c>
       <c r="L159" t="n">
-        <v>-7</v>
+        <v>-2.188</v>
       </c>
       <c r="M159" t="n">
-        <v>32.226</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>5.626</v>
       </c>
       <c r="L160" t="n">
-        <v>-7</v>
+        <v>-2.63</v>
       </c>
       <c r="M160" t="n">
-        <v>29.526</v>
+        <v>21.253</v>
       </c>
     </row>
     <row r="161">
@@ -9714,10 +9714,10 @@
         <v>6.077</v>
       </c>
       <c r="L161" t="n">
-        <v>-9</v>
+        <v>-3.781</v>
       </c>
       <c r="M161" t="n">
-        <v>30.044</v>
+        <v>21.748</v>
       </c>
     </row>
     <row r="162">
@@ -9759,10 +9759,10 @@
         <v>6.685</v>
       </c>
       <c r="L162" t="n">
-        <v>-7</v>
+        <v>-2.263</v>
       </c>
       <c r="M162" t="n">
-        <v>29.232</v>
+        <v>21.428</v>
       </c>
     </row>
     <row r="163">
@@ -9804,10 +9804,10 @@
         <v>6.073</v>
       </c>
       <c r="L163" t="n">
-        <v>-9</v>
+        <v>-3.783</v>
       </c>
       <c r="M163" t="n">
-        <v>30.152</v>
+        <v>21.817</v>
       </c>
     </row>
     <row r="164">
@@ -9849,10 +9849,10 @@
         <v>5.741</v>
       </c>
       <c r="L164" t="n">
-        <v>-7</v>
+        <v>-2.59</v>
       </c>
       <c r="M164" t="n">
-        <v>29.214</v>
+        <v>21.089</v>
       </c>
     </row>
     <row r="165">
@@ -9894,10 +9894,10 @@
         <v>6.119</v>
       </c>
       <c r="L165" t="n">
-        <v>-9</v>
+        <v>-3.767</v>
       </c>
       <c r="M165" t="n">
-        <v>30.462</v>
+        <v>22.036</v>
       </c>
     </row>
     <row r="166">
@@ -9939,10 +9939,10 @@
         <v>6.681</v>
       </c>
       <c r="L166" t="n">
-        <v>-7</v>
+        <v>-2.265</v>
       </c>
       <c r="M166" t="n">
-        <v>29.394</v>
+        <v>21.532</v>
       </c>
     </row>
     <row r="167">
@@ -9984,10 +9984,10 @@
         <v>5.928</v>
       </c>
       <c r="L167" t="n">
-        <v>-7</v>
+        <v>-2.525</v>
       </c>
       <c r="M167" t="n">
-        <v>29.97</v>
+        <v>21.648</v>
       </c>
     </row>
     <row r="168">
@@ -10029,10 +10029,10 @@
         <v>5.626</v>
       </c>
       <c r="L168" t="n">
-        <v>-7</v>
+        <v>-2.63</v>
       </c>
       <c r="M168" t="n">
-        <v>29.024</v>
+        <v>20.925</v>
       </c>
     </row>
     <row r="169">
@@ -10074,10 +10074,10 @@
         <v>6.285</v>
       </c>
       <c r="L169" t="n">
-        <v>-7</v>
+        <v>-2.402</v>
       </c>
       <c r="M169" t="n">
-        <v>31.42</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="170">
@@ -10119,10 +10119,10 @@
         <v>6.89</v>
       </c>
       <c r="L170" t="n">
-        <v>-9</v>
+        <v>-3.5</v>
       </c>
       <c r="M170" t="n">
-        <v>29.662</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="171">
@@ -10164,10 +10164,10 @@
         <v>7.035</v>
       </c>
       <c r="L171" t="n">
-        <v>-7</v>
+        <v>-2.142</v>
       </c>
       <c r="M171" t="n">
-        <v>32.446</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="172">
@@ -10209,10 +10209,10 @@
         <v>6.409</v>
       </c>
       <c r="L172" t="n">
-        <v>-9</v>
+        <v>-3.666</v>
       </c>
       <c r="M172" t="n">
-        <v>30.014</v>
+        <v>21.843</v>
       </c>
     </row>
     <row r="173">
@@ -10254,10 +10254,10 @@
         <v>5.195</v>
       </c>
       <c r="L173" t="n">
-        <v>-9</v>
+        <v>-4.087</v>
       </c>
       <c r="M173" t="n">
-        <v>27.52</v>
+        <v>19.793</v>
       </c>
     </row>
     <row r="174">
@@ -10299,10 +10299,10 @@
         <v>6.04</v>
       </c>
       <c r="L174" t="n">
-        <v>-7</v>
+        <v>-2.486</v>
       </c>
       <c r="M174" t="n">
-        <v>29.324</v>
+        <v>21.265</v>
       </c>
     </row>
     <row r="175">
@@ -10344,10 +10344,10 @@
         <v>5.879</v>
       </c>
       <c r="L175" t="n">
-        <v>-9</v>
+        <v>-3.85</v>
       </c>
       <c r="M175" t="n">
-        <v>28.97</v>
+        <v>20.977</v>
       </c>
     </row>
     <row r="176">
@@ -10389,10 +10389,10 @@
         <v>5.798</v>
       </c>
       <c r="L176" t="n">
-        <v>-9</v>
+        <v>-3.878</v>
       </c>
       <c r="M176" t="n">
-        <v>28.678</v>
+        <v>20.758</v>
       </c>
     </row>
     <row r="177">
@@ -10434,10 +10434,10 @@
         <v>6.129</v>
       </c>
       <c r="L177" t="n">
-        <v>-7</v>
+        <v>-2.456</v>
       </c>
       <c r="M177" t="n">
-        <v>29.512</v>
+        <v>21.418</v>
       </c>
     </row>
     <row r="178">
@@ -10479,10 +10479,10 @@
         <v>5.615</v>
       </c>
       <c r="L178" t="n">
-        <v>-9</v>
+        <v>-3.941</v>
       </c>
       <c r="M178" t="n">
-        <v>28.384</v>
+        <v>20.503</v>
       </c>
     </row>
     <row r="179">
@@ -10524,10 +10524,10 @@
         <v>5.526</v>
       </c>
       <c r="L179" t="n">
-        <v>-9</v>
+        <v>-3.972</v>
       </c>
       <c r="M179" t="n">
-        <v>28.272</v>
+        <v>20.399</v>
       </c>
     </row>
     <row r="180">
@@ -10569,10 +10569,10 @@
         <v>5.767</v>
       </c>
       <c r="L180" t="n">
-        <v>-9</v>
+        <v>-3.889</v>
       </c>
       <c r="M180" t="n">
-        <v>28.594</v>
+        <v>20.693</v>
       </c>
     </row>
     <row r="181">
@@ -10614,10 +10614,10 @@
         <v>5.791</v>
       </c>
       <c r="L181" t="n">
-        <v>-9</v>
+        <v>-3.88</v>
       </c>
       <c r="M181" t="n">
-        <v>28.704</v>
+        <v>20.773</v>
       </c>
     </row>
     <row r="182">
@@ -10659,10 +10659,10 @@
         <v>6.137</v>
       </c>
       <c r="L182" t="n">
-        <v>-9</v>
+        <v>-3.761</v>
       </c>
       <c r="M182" t="n">
-        <v>29.906</v>
+        <v>21.679</v>
       </c>
     </row>
     <row r="183">
@@ -10704,10 +10704,10 @@
         <v>5.891</v>
       </c>
       <c r="L183" t="n">
-        <v>-9</v>
+        <v>-3.846</v>
       </c>
       <c r="M183" t="n">
-        <v>28.99</v>
+        <v>20.995</v>
       </c>
     </row>
     <row r="184">
@@ -10749,10 +10749,10 @@
         <v>6.265</v>
       </c>
       <c r="L184" t="n">
-        <v>-7</v>
+        <v>-2.409</v>
       </c>
       <c r="M184" t="n">
-        <v>29.846</v>
+        <v>21.684</v>
       </c>
     </row>
     <row r="185">
@@ -10794,10 +10794,10 @@
         <v>5.529</v>
       </c>
       <c r="L185" t="n">
-        <v>-9</v>
+        <v>-3.971</v>
       </c>
       <c r="M185" t="n">
-        <v>28.244</v>
+        <v>20.382</v>
       </c>
     </row>
     <row r="186">
@@ -10839,10 +10839,10 @@
         <v>5.448</v>
       </c>
       <c r="L186" t="n">
-        <v>-9</v>
+        <v>-3.999</v>
       </c>
       <c r="M186" t="n">
-        <v>27.902</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="187">
@@ -10884,10 +10884,10 @@
         <v>6.07</v>
       </c>
       <c r="L187" t="n">
-        <v>-9</v>
+        <v>-3.784</v>
       </c>
       <c r="M187" t="n">
-        <v>28.796</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="188">
@@ -10929,10 +10929,10 @@
         <v>6.029</v>
       </c>
       <c r="L188" t="n">
-        <v>-9</v>
+        <v>-3.798</v>
       </c>
       <c r="M188" t="n">
-        <v>29.352</v>
+        <v>21.279</v>
       </c>
     </row>
     <row r="189">
@@ -10974,10 +10974,10 @@
         <v>4.803</v>
       </c>
       <c r="L189" t="n">
-        <v>-7</v>
+        <v>-2.915</v>
       </c>
       <c r="M189" t="n">
-        <v>27.324</v>
+        <v>19.529</v>
       </c>
     </row>
     <row r="190">
@@ -11019,10 +11019,10 @@
         <v>5.227</v>
       </c>
       <c r="L190" t="n">
-        <v>-7</v>
+        <v>-2.768</v>
       </c>
       <c r="M190" t="n">
-        <v>28.364</v>
+        <v>20.355</v>
       </c>
     </row>
     <row r="191">
@@ -11064,10 +11064,10 @@
         <v>5.258</v>
       </c>
       <c r="L191" t="n">
-        <v>-7</v>
+        <v>-2.757</v>
       </c>
       <c r="M191" t="n">
-        <v>28.32</v>
+        <v>20.337</v>
       </c>
     </row>
     <row r="192">
@@ -11109,10 +11109,10 @@
         <v>4.962</v>
       </c>
       <c r="L192" t="n">
-        <v>-9</v>
+        <v>-4.167</v>
       </c>
       <c r="M192" t="n">
-        <v>27.714</v>
+        <v>19.839</v>
       </c>
     </row>
     <row r="193">
@@ -11154,10 +11154,10 @@
         <v>5.48</v>
       </c>
       <c r="L193" t="n">
-        <v>-9</v>
+        <v>-3.988</v>
       </c>
       <c r="M193" t="n">
-        <v>29.236</v>
+        <v>21.013</v>
       </c>
     </row>
     <row r="194">
@@ -11199,10 +11199,10 @@
         <v>5.206</v>
       </c>
       <c r="L194" t="n">
-        <v>-7</v>
+        <v>-2.775</v>
       </c>
       <c r="M194" t="n">
-        <v>28.14</v>
+        <v>20.202</v>
       </c>
     </row>
     <row r="195">
@@ -11244,10 +11244,10 @@
         <v>5.048</v>
       </c>
       <c r="L195" t="n">
-        <v>-9</v>
+        <v>-4.137</v>
       </c>
       <c r="M195" t="n">
-        <v>27.832</v>
+        <v>19.946</v>
       </c>
     </row>
     <row r="196">
@@ -11289,10 +11289,10 @@
         <v>5.289</v>
       </c>
       <c r="L196" t="n">
-        <v>-7</v>
+        <v>-2.746</v>
       </c>
       <c r="M196" t="n">
-        <v>28.42</v>
+        <v>20.414</v>
       </c>
     </row>
     <row r="197">
@@ -11334,10 +11334,10 @@
         <v>4.966</v>
       </c>
       <c r="L197" t="n">
-        <v>-9</v>
+        <v>-4.166</v>
       </c>
       <c r="M197" t="n">
-        <v>27.604</v>
+        <v>19.768</v>
       </c>
     </row>
     <row r="198">
@@ -11379,10 +11379,10 @@
         <v>4.914</v>
       </c>
       <c r="L198" t="n">
-        <v>-7</v>
+        <v>-2.876</v>
       </c>
       <c r="M198" t="n">
-        <v>27.524</v>
+        <v>19.698</v>
       </c>
     </row>
     <row r="199">
@@ -11424,10 +11424,10 @@
         <v>4.501</v>
       </c>
       <c r="L199" t="n">
-        <v>-9</v>
+        <v>-4.327</v>
       </c>
       <c r="M199" t="n">
-        <v>26.692</v>
+        <v>19.011</v>
       </c>
     </row>
     <row r="200">
@@ -11469,10 +11469,10 @@
         <v>5.484</v>
       </c>
       <c r="L200" t="n">
-        <v>-9</v>
+        <v>-3.987</v>
       </c>
       <c r="M200" t="n">
-        <v>28.854</v>
+        <v>20.765</v>
       </c>
     </row>
     <row r="201">
@@ -11514,10 +11514,10 @@
         <v>4.53</v>
       </c>
       <c r="L201" t="n">
-        <v>-9</v>
+        <v>-4.317</v>
       </c>
       <c r="M201" t="n">
-        <v>26.67</v>
+        <v>19.007</v>
       </c>
     </row>
     <row r="202">
@@ -11559,10 +11559,10 @@
         <v>4.992</v>
       </c>
       <c r="L202" t="n">
-        <v>-7</v>
+        <v>-2.849</v>
       </c>
       <c r="M202" t="n">
-        <v>27.772</v>
+        <v>19.887</v>
       </c>
     </row>
     <row r="203">
@@ -11604,10 +11604,10 @@
         <v>5.384</v>
       </c>
       <c r="L203" t="n">
-        <v>-9</v>
+        <v>-4.021</v>
       </c>
       <c r="M203" t="n">
-        <v>29.066</v>
+        <v>20.869</v>
       </c>
     </row>
     <row r="204">
@@ -11649,10 +11649,10 @@
         <v>5.247</v>
       </c>
       <c r="L204" t="n">
-        <v>-9</v>
+        <v>-4.069</v>
       </c>
       <c r="M204" t="n">
-        <v>28.214</v>
+        <v>20.264</v>
       </c>
     </row>
     <row r="205">
@@ -11694,10 +11694,10 @@
         <v>5.209</v>
       </c>
       <c r="L205" t="n">
-        <v>-9</v>
+        <v>-4.082</v>
       </c>
       <c r="M205" t="n">
-        <v>28.122</v>
+        <v>20.191</v>
       </c>
     </row>
     <row r="206">
@@ -11739,10 +11739,10 @@
         <v>6.626</v>
       </c>
       <c r="L206" t="n">
-        <v>-7</v>
+        <v>-2.284</v>
       </c>
       <c r="M206" t="n">
-        <v>29.41</v>
+        <v>21.524</v>
       </c>
     </row>
     <row r="207">
@@ -11784,10 +11784,10 @@
         <v>7.31</v>
       </c>
       <c r="L207" t="n">
-        <v>-7</v>
+        <v>-2.047</v>
       </c>
       <c r="M207" t="n">
-        <v>30.706</v>
+        <v>22.608</v>
       </c>
     </row>
     <row r="208">
@@ -11829,10 +11829,10 @@
         <v>6.498</v>
       </c>
       <c r="L208" t="n">
-        <v>-7</v>
+        <v>-2.328</v>
       </c>
       <c r="M208" t="n">
-        <v>31.296</v>
+        <v>22.713</v>
       </c>
     </row>
     <row r="209">
@@ -11874,10 +11874,10 @@
         <v>7.253</v>
       </c>
       <c r="L209" t="n">
-        <v>-7</v>
+        <v>-2.067</v>
       </c>
       <c r="M209" t="n">
-        <v>30.67</v>
+        <v>22.565</v>
       </c>
     </row>
     <row r="210">
@@ -11919,10 +11919,10 @@
         <v>6.386</v>
       </c>
       <c r="L210" t="n">
-        <v>-7</v>
+        <v>-2.367</v>
       </c>
       <c r="M210" t="n">
-        <v>31.24</v>
+        <v>22.637</v>
       </c>
     </row>
     <row r="211">
@@ -11964,10 +11964,10 @@
         <v>6.942</v>
       </c>
       <c r="L211" t="n">
-        <v>-9</v>
+        <v>-3.482</v>
       </c>
       <c r="M211" t="n">
-        <v>30.068</v>
+        <v>22.063</v>
       </c>
     </row>
     <row r="212">
@@ -12009,10 +12009,10 @@
         <v>5.681</v>
       </c>
       <c r="L212" t="n">
-        <v>-7</v>
+        <v>-2.611</v>
       </c>
       <c r="M212" t="n">
-        <v>29.408</v>
+        <v>21.195</v>
       </c>
     </row>
     <row r="213">
@@ -12054,10 +12054,10 @@
         <v>6.547</v>
       </c>
       <c r="L213" t="n">
-        <v>-7</v>
+        <v>-2.311</v>
       </c>
       <c r="M213" t="n">
-        <v>31.426</v>
+        <v>22.815</v>
       </c>
     </row>
     <row r="214">
@@ -12099,10 +12099,10 @@
         <v>5.819</v>
       </c>
       <c r="L214" t="n">
-        <v>-9</v>
+        <v>-3.871</v>
       </c>
       <c r="M214" t="n">
-        <v>29.832</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="215">
@@ -12144,10 +12144,10 @@
         <v>6.742</v>
       </c>
       <c r="L215" t="n">
-        <v>-7</v>
+        <v>-2.243</v>
       </c>
       <c r="M215" t="n">
-        <v>31.776</v>
+        <v>23.111</v>
       </c>
     </row>
     <row r="216">
@@ -12189,10 +12189,10 @@
         <v>6.342</v>
       </c>
       <c r="L216" t="n">
-        <v>-7</v>
+        <v>-2.382</v>
       </c>
       <c r="M216" t="n">
-        <v>30.796</v>
+        <v>22.332</v>
       </c>
     </row>
     <row r="217">
@@ -12234,10 +12234,10 @@
         <v>6.054</v>
       </c>
       <c r="L217" t="n">
-        <v>-9</v>
+        <v>-3.789</v>
       </c>
       <c r="M217" t="n">
-        <v>30.35</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="218">
@@ -12279,10 +12279,10 @@
         <v>6.32</v>
       </c>
       <c r="L218" t="n">
-        <v>-7</v>
+        <v>-2.389</v>
       </c>
       <c r="M218" t="n">
-        <v>30.914</v>
+        <v>22.401</v>
       </c>
     </row>
     <row r="219">
@@ -12324,10 +12324,10 @@
         <v>7.022</v>
       </c>
       <c r="L219" t="n">
-        <v>-7</v>
+        <v>-2.146</v>
       </c>
       <c r="M219" t="n">
-        <v>30.198</v>
+        <v>22.176</v>
       </c>
     </row>
     <row r="220">
@@ -12369,10 +12369,10 @@
         <v>5.731</v>
       </c>
       <c r="L220" t="n">
-        <v>-9</v>
+        <v>-3.901</v>
       </c>
       <c r="M220" t="n">
-        <v>29.578</v>
+        <v>21.324</v>
       </c>
     </row>
     <row r="221">
@@ -12414,10 +12414,10 @@
         <v>6.973</v>
       </c>
       <c r="L221" t="n">
-        <v>-7</v>
+        <v>-2.163</v>
       </c>
       <c r="M221" t="n">
-        <v>32.99</v>
+        <v>23.985</v>
       </c>
     </row>
     <row r="222">
@@ -12459,10 +12459,10 @@
         <v>6.563</v>
       </c>
       <c r="L222" t="n">
-        <v>-7</v>
+        <v>-2.305</v>
       </c>
       <c r="M222" t="n">
-        <v>31.55</v>
+        <v>22.901</v>
       </c>
     </row>
     <row r="223">
@@ -12504,10 +12504,10 @@
         <v>5.679</v>
       </c>
       <c r="L223" t="n">
-        <v>-9</v>
+        <v>-3.919</v>
       </c>
       <c r="M223" t="n">
-        <v>29.03</v>
+        <v>20.947</v>
       </c>
     </row>
     <row r="224">
@@ -12549,10 +12549,10 @@
         <v>5.02</v>
       </c>
       <c r="L224" t="n">
-        <v>-9</v>
+        <v>-4.147</v>
       </c>
       <c r="M224" t="n">
-        <v>27.746</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="225">
@@ -12594,10 +12594,10 @@
         <v>5.481</v>
       </c>
       <c r="L225" t="n">
-        <v>-9</v>
+        <v>-3.988</v>
       </c>
       <c r="M225" t="n">
-        <v>28.664</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="226">
@@ -12639,10 +12639,10 @@
         <v>6.089</v>
       </c>
       <c r="L226" t="n">
-        <v>-7</v>
+        <v>-2.469</v>
       </c>
       <c r="M226" t="n">
-        <v>30.266</v>
+        <v>21.897</v>
       </c>
     </row>
     <row r="227">
@@ -12684,10 +12684,10 @@
         <v>5.439</v>
       </c>
       <c r="L227" t="n">
-        <v>-9</v>
+        <v>-4.002</v>
       </c>
       <c r="M227" t="n">
-        <v>28.696</v>
+        <v>20.646</v>
       </c>
     </row>
     <row r="228">
@@ -12729,10 +12729,10 @@
         <v>5.979</v>
       </c>
       <c r="L228" t="n">
-        <v>-7</v>
+        <v>-2.508</v>
       </c>
       <c r="M228" t="n">
-        <v>29.992</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="229">
@@ -12774,10 +12774,10 @@
         <v>5.175</v>
       </c>
       <c r="L229" t="n">
-        <v>-9</v>
+        <v>-4.094</v>
       </c>
       <c r="M229" t="n">
-        <v>28.104</v>
+        <v>20.167</v>
       </c>
     </row>
     <row r="230">
@@ -12819,10 +12819,10 @@
         <v>5.16</v>
       </c>
       <c r="L230" t="n">
-        <v>-9</v>
+        <v>-4.099</v>
       </c>
       <c r="M230" t="n">
-        <v>28.048</v>
+        <v>20.126</v>
       </c>
     </row>
     <row r="231">
@@ -12864,10 +12864,10 @@
         <v>5.536</v>
       </c>
       <c r="L231" t="n">
-        <v>-9</v>
+        <v>-3.969</v>
       </c>
       <c r="M231" t="n">
-        <v>28.8</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="232">
@@ -12909,10 +12909,10 @@
         <v>5.322</v>
       </c>
       <c r="L232" t="n">
-        <v>-7</v>
+        <v>-2.735</v>
       </c>
       <c r="M232" t="n">
-        <v>28.474</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="233">
@@ -12954,10 +12954,10 @@
         <v>5.36</v>
       </c>
       <c r="L233" t="n">
-        <v>-9</v>
+        <v>-4.029</v>
       </c>
       <c r="M233" t="n">
-        <v>28.444</v>
+        <v>20.454</v>
       </c>
     </row>
     <row r="234">
@@ -12999,10 +12999,10 @@
         <v>5.187</v>
       </c>
       <c r="L234" t="n">
-        <v>-9</v>
+        <v>-4.089</v>
       </c>
       <c r="M234" t="n">
-        <v>28.004</v>
+        <v>20.106</v>
       </c>
     </row>
     <row r="235">
@@ -13044,10 +13044,10 @@
         <v>4.993</v>
       </c>
       <c r="L235" t="n">
-        <v>-9</v>
+        <v>-4.157</v>
       </c>
       <c r="M235" t="n">
-        <v>26.56</v>
+        <v>19.095</v>
       </c>
     </row>
     <row r="236">
@@ -13089,10 +13089,10 @@
         <v>5.818</v>
       </c>
       <c r="L236" t="n">
-        <v>-7</v>
+        <v>-2.563</v>
       </c>
       <c r="M236" t="n">
-        <v>29.682</v>
+        <v>21.422</v>
       </c>
     </row>
     <row r="237">
@@ -13134,10 +13134,10 @@
         <v>5.885</v>
       </c>
       <c r="L237" t="n">
-        <v>-7</v>
+        <v>-2.54</v>
       </c>
       <c r="M237" t="n">
-        <v>29.656</v>
+        <v>21.428</v>
       </c>
     </row>
     <row r="238">
@@ -13179,10 +13179,10 @@
         <v>5.321</v>
       </c>
       <c r="L238" t="n">
-        <v>-9</v>
+        <v>-4.043</v>
       </c>
       <c r="M238" t="n">
-        <v>28.448</v>
+        <v>20.443</v>
       </c>
     </row>
     <row r="239">
@@ -13224,10 +13224,10 @@
         <v>5.225</v>
       </c>
       <c r="L239" t="n">
-        <v>-9</v>
+        <v>-4.076</v>
       </c>
       <c r="M239" t="n">
-        <v>28.178</v>
+        <v>20.233</v>
       </c>
     </row>
     <row r="240">
@@ -13269,10 +13269,10 @@
         <v>5.923</v>
       </c>
       <c r="L240" t="n">
-        <v>-7</v>
+        <v>-2.527</v>
       </c>
       <c r="M240" t="n">
-        <v>29.75</v>
+        <v>21.503</v>
       </c>
     </row>
     <row r="241">
@@ -13314,10 +13314,10 @@
         <v>6.039</v>
       </c>
       <c r="L241" t="n">
-        <v>-7</v>
+        <v>-2.487</v>
       </c>
       <c r="M241" t="n">
-        <v>29.964</v>
+        <v>21.683</v>
       </c>
     </row>
     <row r="242">
@@ -13359,10 +13359,10 @@
         <v>5.909</v>
       </c>
       <c r="L242" t="n">
-        <v>-7</v>
+        <v>-2.532</v>
       </c>
       <c r="M242" t="n">
-        <v>29.626</v>
+        <v>21.417</v>
       </c>
     </row>
     <row r="243">
@@ -13404,10 +13404,10 @@
         <v>6.102</v>
       </c>
       <c r="L243" t="n">
-        <v>-7</v>
+        <v>-2.465</v>
       </c>
       <c r="M243" t="n">
-        <v>30.208</v>
+        <v>21.864</v>
       </c>
     </row>
     <row r="244">
@@ -13449,10 +13449,10 @@
         <v>5.664</v>
       </c>
       <c r="L244" t="n">
-        <v>-7</v>
+        <v>-2.617</v>
       </c>
       <c r="M244" t="n">
-        <v>29.08</v>
+        <v>20.975</v>
       </c>
     </row>
     <row r="245">
@@ -13494,10 +13494,10 @@
         <v>5.858</v>
       </c>
       <c r="L245" t="n">
-        <v>-7</v>
+        <v>-2.549</v>
       </c>
       <c r="M245" t="n">
-        <v>29.494</v>
+        <v>21.313</v>
       </c>
     </row>
     <row r="246">
@@ -13539,10 +13539,10 @@
         <v>6.754</v>
       </c>
       <c r="L246" t="n">
-        <v>-7</v>
+        <v>-2.239</v>
       </c>
       <c r="M246" t="n">
-        <v>31.576</v>
+        <v>22.984</v>
       </c>
     </row>
     <row r="247">
@@ -13584,10 +13584,10 @@
         <v>5.971</v>
       </c>
       <c r="L247" t="n">
-        <v>-9</v>
+        <v>-3.818</v>
       </c>
       <c r="M247" t="n">
-        <v>29.768</v>
+        <v>21.531</v>
       </c>
     </row>
     <row r="248">
@@ -13629,10 +13629,10 @@
         <v>6.268</v>
       </c>
       <c r="L248" t="n">
-        <v>-7</v>
+        <v>-2.407</v>
       </c>
       <c r="M248" t="n">
-        <v>30.758</v>
+        <v>22.281</v>
       </c>
     </row>
     <row r="249">
@@ -13674,10 +13674,10 @@
         <v>5.518</v>
       </c>
       <c r="L249" t="n">
-        <v>-9</v>
+        <v>-3.975</v>
       </c>
       <c r="M249" t="n">
-        <v>28.81</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="250">
@@ -13719,10 +13719,10 @@
         <v>6.518</v>
       </c>
       <c r="L250" t="n">
-        <v>-7</v>
+        <v>-2.321</v>
       </c>
       <c r="M250" t="n">
-        <v>31.228</v>
+        <v>22.675</v>
       </c>
     </row>
     <row r="251">
@@ -13764,10 +13764,10 @@
         <v>5.928</v>
       </c>
       <c r="L251" t="n">
-        <v>-9</v>
+        <v>-3.833</v>
       </c>
       <c r="M251" t="n">
-        <v>29.944</v>
+        <v>21.631</v>
       </c>
     </row>
     <row r="252">
@@ -13809,10 +13809,10 @@
         <v>6.056</v>
       </c>
       <c r="L252" t="n">
-        <v>-7</v>
+        <v>-2.481</v>
       </c>
       <c r="M252" t="n">
-        <v>30.1</v>
+        <v>21.778</v>
       </c>
     </row>
     <row r="253">
@@ -13854,10 +13854,10 @@
         <v>5.686</v>
       </c>
       <c r="L253" t="n">
-        <v>-9</v>
+        <v>-3.917</v>
       </c>
       <c r="M253" t="n">
-        <v>29.174</v>
+        <v>21.044</v>
       </c>
     </row>
     <row r="254">
@@ -13899,10 +13899,10 @@
         <v>5.927</v>
       </c>
       <c r="L254" t="n">
-        <v>-9</v>
+        <v>-3.833</v>
       </c>
       <c r="M254" t="n">
-        <v>29.716</v>
+        <v>21.482</v>
       </c>
     </row>
     <row r="255">
@@ -13944,10 +13944,10 @@
         <v>6.598</v>
       </c>
       <c r="L255" t="n">
-        <v>-7</v>
+        <v>-2.293</v>
       </c>
       <c r="M255" t="n">
-        <v>31.432</v>
+        <v>22.836</v>
       </c>
     </row>
     <row r="256">
@@ -13989,10 +13989,10 @@
         <v>6.459</v>
       </c>
       <c r="L256" t="n">
-        <v>-7</v>
+        <v>-2.341</v>
       </c>
       <c r="M256" t="n">
-        <v>31.016</v>
+        <v>22.516</v>
       </c>
     </row>
     <row r="257">
@@ -14034,10 +14034,10 @@
         <v>5.987</v>
       </c>
       <c r="L257" t="n">
-        <v>-7</v>
+        <v>-2.505</v>
       </c>
       <c r="M257" t="n">
-        <v>29.744</v>
+        <v>21.521</v>
       </c>
     </row>
     <row r="258">
@@ -14079,10 +14079,10 @@
         <v>6.271</v>
       </c>
       <c r="L258" t="n">
-        <v>-7</v>
+        <v>-2.406</v>
       </c>
       <c r="M258" t="n">
-        <v>30.54</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="259">
@@ -14124,10 +14124,10 @@
         <v>4.961</v>
       </c>
       <c r="L259" t="n">
-        <v>-7</v>
+        <v>-2.86</v>
       </c>
       <c r="M259" t="n">
-        <v>27.658</v>
+        <v>19.802</v>
       </c>
     </row>
     <row r="260">
@@ -14169,10 +14169,10 @@
         <v>5.262</v>
       </c>
       <c r="L260" t="n">
-        <v>-7</v>
+        <v>-2.756</v>
       </c>
       <c r="M260" t="n">
-        <v>28.046</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="261">
@@ -14214,10 +14214,10 @@
         <v>6.345</v>
       </c>
       <c r="L261" t="n">
-        <v>-7</v>
+        <v>-2.381</v>
       </c>
       <c r="M261" t="n">
-        <v>30.842</v>
+        <v>22.363</v>
       </c>
     </row>
     <row r="262">
@@ -14259,10 +14259,10 @@
         <v>4.675</v>
       </c>
       <c r="L262" t="n">
-        <v>-9</v>
+        <v>-4.267</v>
       </c>
       <c r="M262" t="n">
-        <v>27.022</v>
+        <v>19.287</v>
       </c>
     </row>
     <row r="263">
@@ -14304,10 +14304,10 @@
         <v>5.811</v>
       </c>
       <c r="L263" t="n">
-        <v>-7</v>
+        <v>-2.566</v>
       </c>
       <c r="M263" t="n">
-        <v>29.424</v>
+        <v>21.251</v>
       </c>
     </row>
     <row r="264">
@@ -14349,10 +14349,10 @@
         <v>5.581</v>
       </c>
       <c r="L264" t="n">
-        <v>-7</v>
+        <v>-2.645</v>
       </c>
       <c r="M264" t="n">
-        <v>28.988</v>
+        <v>20.886</v>
       </c>
     </row>
     <row r="265">
@@ -14394,10 +14394,10 @@
         <v>5.484</v>
       </c>
       <c r="L265" t="n">
-        <v>-7</v>
+        <v>-2.679</v>
       </c>
       <c r="M265" t="n">
-        <v>28.746</v>
+        <v>20.694</v>
       </c>
     </row>
     <row r="266">
@@ -14439,10 +14439,10 @@
         <v>5.515</v>
       </c>
       <c r="L266" t="n">
-        <v>-7</v>
+        <v>-2.668</v>
       </c>
       <c r="M266" t="n">
-        <v>28.588</v>
+        <v>20.602</v>
       </c>
     </row>
     <row r="267">
@@ -14484,10 +14484,10 @@
         <v>5.528</v>
       </c>
       <c r="L267" t="n">
-        <v>-9</v>
+        <v>-3.971</v>
       </c>
       <c r="M267" t="n">
-        <v>26.518</v>
+        <v>19.253</v>
       </c>
     </row>
     <row r="268">
@@ -14529,10 +14529,10 @@
         <v>5.589</v>
       </c>
       <c r="L268" t="n">
-        <v>-9</v>
+        <v>-3.95</v>
       </c>
       <c r="M268" t="n">
-        <v>29.708</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="269">
@@ -14574,10 +14574,10 @@
         <v>5.624</v>
       </c>
       <c r="L269" t="n">
-        <v>-7</v>
+        <v>-2.63</v>
       </c>
       <c r="M269" t="n">
-        <v>29.088</v>
+        <v>20.966</v>
       </c>
     </row>
     <row r="270">
@@ -14619,10 +14619,10 @@
         <v>5.297</v>
       </c>
       <c r="L270" t="n">
-        <v>-7</v>
+        <v>-2.744</v>
       </c>
       <c r="M270" t="n">
-        <v>28.096</v>
+        <v>20.204</v>
       </c>
     </row>
     <row r="271">
@@ -14664,10 +14664,10 @@
         <v>6.86</v>
       </c>
       <c r="L271" t="n">
-        <v>-7</v>
+        <v>-2.203</v>
       </c>
       <c r="M271" t="n">
-        <v>29.866</v>
+        <v>21.903</v>
       </c>
     </row>
     <row r="272">
@@ -14709,10 +14709,10 @@
         <v>6.206</v>
       </c>
       <c r="L272" t="n">
-        <v>-7</v>
+        <v>-2.429</v>
       </c>
       <c r="M272" t="n">
-        <v>30.612</v>
+        <v>22.164</v>
       </c>
     </row>
     <row r="273">
@@ -14754,10 +14754,10 @@
         <v>5.379</v>
       </c>
       <c r="L273" t="n">
-        <v>-7</v>
+        <v>-2.715</v>
       </c>
       <c r="M273" t="n">
-        <v>28.246</v>
+        <v>20.331</v>
       </c>
     </row>
     <row r="274">
@@ -14799,10 +14799,10 @@
         <v>7.123</v>
       </c>
       <c r="L274" t="n">
-        <v>-7</v>
+        <v>-2.112</v>
       </c>
       <c r="M274" t="n">
-        <v>29.548</v>
+        <v>21.786</v>
       </c>
     </row>
     <row r="275">
@@ -14844,10 +14844,10 @@
         <v>5.378</v>
       </c>
       <c r="L275" t="n">
-        <v>-9</v>
+        <v>-4.023</v>
       </c>
       <c r="M275" t="n">
-        <v>27.802</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="276">
@@ -14889,10 +14889,10 @@
         <v>6.177</v>
       </c>
       <c r="L276" t="n">
-        <v>-7</v>
+        <v>-2.439</v>
       </c>
       <c r="M276" t="n">
-        <v>29.52</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="277">
@@ -14934,10 +14934,10 @@
         <v>5.549</v>
       </c>
       <c r="L277" t="n">
-        <v>-9</v>
+        <v>-3.964</v>
       </c>
       <c r="M277" t="n">
-        <v>28.188</v>
+        <v>20.352</v>
       </c>
     </row>
     <row r="278">
@@ -14979,10 +14979,10 @@
         <v>5.24</v>
       </c>
       <c r="L278" t="n">
-        <v>-9</v>
+        <v>-4.071</v>
       </c>
       <c r="M278" t="n">
-        <v>27.642</v>
+        <v>19.888</v>
       </c>
     </row>
     <row r="279">
@@ -15024,10 +15024,10 @@
         <v>6</v>
       </c>
       <c r="L279" t="n">
-        <v>-9</v>
+        <v>-3.808</v>
       </c>
       <c r="M279" t="n">
-        <v>29.132</v>
+        <v>21.125</v>
       </c>
     </row>
     <row r="280">
@@ -15069,10 +15069,10 @@
         <v>5.701</v>
       </c>
       <c r="L280" t="n">
-        <v>-9</v>
+        <v>-3.911</v>
       </c>
       <c r="M280" t="n">
-        <v>28.462</v>
+        <v>20.584</v>
       </c>
     </row>
     <row r="281">
@@ -15114,10 +15114,10 @@
         <v>6.643</v>
       </c>
       <c r="L281" t="n">
-        <v>-7</v>
+        <v>-2.278</v>
       </c>
       <c r="M281" t="n">
-        <v>30.654</v>
+        <v>22.343</v>
       </c>
     </row>
     <row r="282">
@@ -15159,10 +15159,10 @@
         <v>6.369</v>
       </c>
       <c r="L282" t="n">
-        <v>-7</v>
+        <v>-2.373</v>
       </c>
       <c r="M282" t="n">
-        <v>30.168</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="283">
@@ -15204,10 +15204,10 @@
         <v>5.882</v>
       </c>
       <c r="L283" t="n">
-        <v>-9</v>
+        <v>-3.849</v>
       </c>
       <c r="M283" t="n">
-        <v>28.922</v>
+        <v>20.947</v>
       </c>
     </row>
     <row r="284">
@@ -15249,10 +15249,10 @@
         <v>6.148</v>
       </c>
       <c r="L284" t="n">
-        <v>-7</v>
+        <v>-2.449</v>
       </c>
       <c r="M284" t="n">
-        <v>29.598</v>
+        <v>21.481</v>
       </c>
     </row>
     <row r="285">
@@ -15294,10 +15294,10 @@
         <v>5.445</v>
       </c>
       <c r="L285" t="n">
-        <v>-7</v>
+        <v>-2.692</v>
       </c>
       <c r="M285" t="n">
-        <v>28.05</v>
+        <v>20.226</v>
       </c>
     </row>
     <row r="286">
@@ -15339,10 +15339,10 @@
         <v>6.011</v>
       </c>
       <c r="L286" t="n">
-        <v>-7</v>
+        <v>-2.496</v>
       </c>
       <c r="M286" t="n">
-        <v>29.378</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="287">
@@ -15384,10 +15384,10 @@
         <v>6.018</v>
       </c>
       <c r="L287" t="n">
-        <v>-9</v>
+        <v>-3.802</v>
       </c>
       <c r="M287" t="n">
-        <v>29.184</v>
+        <v>21.165</v>
       </c>
     </row>
     <row r="288">
@@ -15429,10 +15429,10 @@
         <v>5.144</v>
       </c>
       <c r="L288" t="n">
-        <v>-9</v>
+        <v>-4.104</v>
       </c>
       <c r="M288" t="n">
-        <v>27.548</v>
+        <v>19.793</v>
       </c>
     </row>
     <row r="289">
@@ -15474,10 +15474,10 @@
         <v>5.667</v>
       </c>
       <c r="L289" t="n">
-        <v>-9</v>
+        <v>-3.923</v>
       </c>
       <c r="M289" t="n">
-        <v>28.588</v>
+        <v>20.654</v>
       </c>
     </row>
     <row r="290">
@@ -15519,10 +15519,10 @@
         <v>5.268</v>
       </c>
       <c r="L290" t="n">
-        <v>-9</v>
+        <v>-4.061</v>
       </c>
       <c r="M290" t="n">
-        <v>27.758</v>
+        <v>19.973</v>
       </c>
     </row>
     <row r="291">
@@ -15564,10 +15564,10 @@
         <v>6.65</v>
       </c>
       <c r="L291" t="n">
-        <v>-7</v>
+        <v>-2.275</v>
       </c>
       <c r="M291" t="n">
-        <v>28.906</v>
+        <v>21.202</v>
       </c>
     </row>
     <row r="292">
@@ -15609,10 +15609,10 @@
         <v>5.72</v>
       </c>
       <c r="L292" t="n">
-        <v>-7</v>
+        <v>-2.597</v>
       </c>
       <c r="M292" t="n">
-        <v>29.044</v>
+        <v>20.971</v>
       </c>
     </row>
     <row r="293">
@@ -15654,10 +15654,10 @@
         <v>4.837</v>
       </c>
       <c r="L293" t="n">
-        <v>-9</v>
+        <v>-4.211</v>
       </c>
       <c r="M293" t="n">
-        <v>27.286</v>
+        <v>19.516</v>
       </c>
     </row>
     <row r="294">
@@ -15699,10 +15699,10 @@
         <v>4.901</v>
       </c>
       <c r="L294" t="n">
-        <v>-9</v>
+        <v>-4.188</v>
       </c>
       <c r="M294" t="n">
-        <v>27.596</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="295">
@@ -15744,10 +15744,10 @@
         <v>7.061</v>
       </c>
       <c r="L295" t="n">
-        <v>-7</v>
+        <v>-2.133</v>
       </c>
       <c r="M295" t="n">
-        <v>29.978</v>
+        <v>22.046</v>
       </c>
     </row>
     <row r="296">
@@ -15789,10 +15789,10 @@
         <v>5.129</v>
       </c>
       <c r="L296" t="n">
-        <v>-7</v>
+        <v>-2.802</v>
       </c>
       <c r="M296" t="n">
-        <v>27.902</v>
+        <v>20.019</v>
       </c>
     </row>
     <row r="297">
@@ -15834,10 +15834,10 @@
         <v>4.867</v>
       </c>
       <c r="L297" t="n">
-        <v>-9</v>
+        <v>-4.2</v>
       </c>
       <c r="M297" t="n">
-        <v>27.376</v>
+        <v>19.585</v>
       </c>
     </row>
     <row r="298">
@@ -15879,10 +15879,10 @@
         <v>5.532</v>
       </c>
       <c r="L298" t="n">
-        <v>-7</v>
+        <v>-2.662</v>
       </c>
       <c r="M298" t="n">
-        <v>28.688</v>
+        <v>20.673</v>
       </c>
     </row>
     <row r="299">
@@ -15924,10 +15924,10 @@
         <v>5.672</v>
       </c>
       <c r="L299" t="n">
-        <v>-7</v>
+        <v>-2.614</v>
       </c>
       <c r="M299" t="n">
-        <v>29.044</v>
+        <v>20.954</v>
       </c>
     </row>
     <row r="300">
@@ -15969,10 +15969,10 @@
         <v>5.78</v>
       </c>
       <c r="L300" t="n">
-        <v>-7</v>
+        <v>-2.576</v>
       </c>
       <c r="M300" t="n">
-        <v>29.512</v>
+        <v>21.298</v>
       </c>
     </row>
     <row r="301">
@@ -16014,10 +16014,10 @@
         <v>6.491</v>
       </c>
       <c r="L301" t="n">
-        <v>-7</v>
+        <v>-2.33</v>
       </c>
       <c r="M301" t="n">
-        <v>31.59</v>
+        <v>22.902</v>
       </c>
     </row>
     <row r="302">
@@ -16059,10 +16059,10 @@
         <v>5.285</v>
       </c>
       <c r="L302" t="n">
-        <v>-9</v>
+        <v>-4.055</v>
       </c>
       <c r="M302" t="n">
-        <v>28.29</v>
+        <v>20.327</v>
       </c>
     </row>
     <row r="303">
@@ -16104,10 +16104,10 @@
         <v>5.535</v>
       </c>
       <c r="L303" t="n">
-        <v>-7</v>
+        <v>-2.661</v>
       </c>
       <c r="M303" t="n">
-        <v>28.704</v>
+        <v>20.684</v>
       </c>
     </row>
     <row r="304">
@@ -16149,10 +16149,10 @@
         <v>6.111</v>
       </c>
       <c r="L304" t="n">
-        <v>-7</v>
+        <v>-2.462</v>
       </c>
       <c r="M304" t="n">
-        <v>30.574</v>
+        <v>22.106</v>
       </c>
     </row>
     <row r="305">
@@ -16194,10 +16194,10 @@
         <v>5.222</v>
       </c>
       <c r="L305" t="n">
-        <v>-7</v>
+        <v>-2.77</v>
       </c>
       <c r="M305" t="n">
-        <v>28.26</v>
+        <v>20.286</v>
       </c>
     </row>
     <row r="306">
@@ -16239,10 +16239,10 @@
         <v>6.212</v>
       </c>
       <c r="L306" t="n">
-        <v>-7</v>
+        <v>-2.427</v>
       </c>
       <c r="M306" t="n">
-        <v>28.042</v>
+        <v>20.486</v>
       </c>
     </row>
     <row r="307">
@@ -16284,10 +16284,10 @@
         <v>5.828</v>
       </c>
       <c r="L307" t="n">
-        <v>-7</v>
+        <v>-2.56</v>
       </c>
       <c r="M307" t="n">
-        <v>29.528</v>
+        <v>21.325</v>
       </c>
     </row>
     <row r="308">
@@ -16329,10 +16329,10 @@
         <v>5.061</v>
       </c>
       <c r="L308" t="n">
-        <v>-7</v>
+        <v>-2.825</v>
       </c>
       <c r="M308" t="n">
-        <v>27.892</v>
+        <v>19.989</v>
       </c>
     </row>
     <row r="309">
@@ -16374,10 +16374,10 @@
         <v>5.867</v>
       </c>
       <c r="L309" t="n">
-        <v>-7</v>
+        <v>-2.546</v>
       </c>
       <c r="M309" t="n">
-        <v>29.706</v>
+        <v>21.454</v>
       </c>
     </row>
     <row r="310">
@@ -16419,10 +16419,10 @@
         <v>5.626</v>
       </c>
       <c r="L310" t="n">
-        <v>-9</v>
+        <v>-3.937</v>
       </c>
       <c r="M310" t="n">
-        <v>29.104</v>
+        <v>20.977</v>
       </c>
     </row>
     <row r="311">
@@ -16464,10 +16464,10 @@
         <v>4.929</v>
       </c>
       <c r="L311" t="n">
-        <v>-7</v>
+        <v>-2.871</v>
       </c>
       <c r="M311" t="n">
-        <v>27.466</v>
+        <v>19.665</v>
       </c>
     </row>
     <row r="312">
@@ -16509,10 +16509,10 @@
         <v>5.019</v>
       </c>
       <c r="L312" t="n">
-        <v>-9</v>
+        <v>-4.148</v>
       </c>
       <c r="M312" t="n">
-        <v>27.634</v>
+        <v>19.806</v>
       </c>
     </row>
     <row r="313">
@@ -16554,10 +16554,10 @@
         <v>4.636</v>
       </c>
       <c r="L313" t="n">
-        <v>-9</v>
+        <v>-4.28</v>
       </c>
       <c r="M313" t="n">
-        <v>26.85</v>
+        <v>19.161</v>
       </c>
     </row>
     <row r="314">
@@ -16599,10 +16599,10 @@
         <v>4.639</v>
       </c>
       <c r="L314" t="n">
-        <v>-9</v>
+        <v>-4.279</v>
       </c>
       <c r="M314" t="n">
-        <v>26.912</v>
+        <v>19.203</v>
       </c>
     </row>
     <row r="315">
@@ -16644,10 +16644,10 @@
         <v>5.316</v>
       </c>
       <c r="L315" t="n">
-        <v>-7</v>
+        <v>-2.737</v>
       </c>
       <c r="M315" t="n">
-        <v>28.514</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="316">
@@ -16689,10 +16689,10 @@
         <v>5.46</v>
       </c>
       <c r="L316" t="n">
-        <v>-7</v>
+        <v>-2.687</v>
       </c>
       <c r="M316" t="n">
-        <v>25.77</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="317">
@@ -16734,10 +16734,10 @@
         <v>4.596</v>
       </c>
       <c r="L317" t="n">
-        <v>-7</v>
+        <v>-2.986</v>
       </c>
       <c r="M317" t="n">
-        <v>26.846</v>
+        <v>19.144</v>
       </c>
     </row>
     <row r="318">
@@ -16779,10 +16779,10 @@
         <v>5.449</v>
       </c>
       <c r="L318" t="n">
-        <v>-7</v>
+        <v>-2.691</v>
       </c>
       <c r="M318" t="n">
-        <v>25.606</v>
+        <v>18.629</v>
       </c>
     </row>
     <row r="319">
@@ -16824,10 +16824,10 @@
         <v>4.938</v>
       </c>
       <c r="L319" t="n">
-        <v>-9</v>
+        <v>-4.176</v>
       </c>
       <c r="M319" t="n">
-        <v>27.576</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="320">
@@ -16869,10 +16869,10 @@
         <v>5.983</v>
       </c>
       <c r="L320" t="n">
-        <v>-7</v>
+        <v>-2.506</v>
       </c>
       <c r="M320" t="n">
-        <v>29.906</v>
+        <v>21.625</v>
       </c>
     </row>
     <row r="321">
@@ -16914,10 +16914,10 @@
         <v>5.574</v>
       </c>
       <c r="L321" t="n">
-        <v>-7</v>
+        <v>-2.648</v>
       </c>
       <c r="M321" t="n">
-        <v>28.816</v>
+        <v>20.771</v>
       </c>
     </row>
     <row r="322">
@@ -16959,10 +16959,10 @@
         <v>5.709</v>
       </c>
       <c r="L322" t="n">
-        <v>-7</v>
+        <v>-2.601</v>
       </c>
       <c r="M322" t="n">
-        <v>29.346</v>
+        <v>21.164</v>
       </c>
     </row>
     <row r="323">
@@ -17004,10 +17004,10 @@
         <v>5.093</v>
       </c>
       <c r="L323" t="n">
-        <v>-9</v>
+        <v>-4.122</v>
       </c>
       <c r="M323" t="n">
-        <v>27.798</v>
+        <v>19.939</v>
       </c>
     </row>
     <row r="324">
@@ -17049,10 +17049,10 @@
         <v>4.876</v>
       </c>
       <c r="L324" t="n">
-        <v>-9</v>
+        <v>-4.197</v>
       </c>
       <c r="M324" t="n">
-        <v>27.376</v>
+        <v>19.588</v>
       </c>
     </row>
     <row r="325">
@@ -17094,10 +17094,10 @@
         <v>5.247</v>
       </c>
       <c r="L325" t="n">
-        <v>-9</v>
+        <v>-4.069</v>
       </c>
       <c r="M325" t="n">
-        <v>28.616</v>
+        <v>20.527</v>
       </c>
     </row>
     <row r="326">
@@ -17139,10 +17139,10 @@
         <v>5.421</v>
       </c>
       <c r="L326" t="n">
-        <v>-9</v>
+        <v>-4.008</v>
       </c>
       <c r="M326" t="n">
-        <v>29.2</v>
+        <v>20.969</v>
       </c>
     </row>
     <row r="327">
@@ -17184,10 +17184,10 @@
         <v>4.985</v>
       </c>
       <c r="L327" t="n">
-        <v>-7</v>
+        <v>-2.852</v>
       </c>
       <c r="M327" t="n">
-        <v>28.152</v>
+        <v>20.133</v>
       </c>
     </row>
     <row r="328">
@@ -17229,10 +17229,10 @@
         <v>4.959</v>
       </c>
       <c r="L328" t="n">
-        <v>-9</v>
+        <v>-4.168</v>
       </c>
       <c r="M328" t="n">
-        <v>28.112</v>
+        <v>20.098</v>
       </c>
     </row>
     <row r="329">
@@ -17274,10 +17274,10 @@
         <v>5.619</v>
       </c>
       <c r="L329" t="n">
-        <v>-7</v>
+        <v>-2.632</v>
       </c>
       <c r="M329" t="n">
-        <v>29.566</v>
+        <v>21.277</v>
       </c>
     </row>
     <row r="330">
@@ -17319,10 +17319,10 @@
         <v>5.294</v>
       </c>
       <c r="L330" t="n">
-        <v>-9</v>
+        <v>-4.052</v>
       </c>
       <c r="M330" t="n">
-        <v>28.97</v>
+        <v>20.775</v>
       </c>
     </row>
     <row r="331">
@@ -17364,10 +17364,10 @@
         <v>5.189</v>
       </c>
       <c r="L331" t="n">
-        <v>-9</v>
+        <v>-4.089</v>
       </c>
       <c r="M331" t="n">
-        <v>28.504</v>
+        <v>20.434</v>
       </c>
     </row>
     <row r="332">
@@ -17409,10 +17409,10 @@
         <v>5.288</v>
       </c>
       <c r="L332" t="n">
-        <v>-9</v>
+        <v>-4.054</v>
       </c>
       <c r="M332" t="n">
-        <v>28.752</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="333">
@@ -17454,10 +17454,10 @@
         <v>5.696</v>
       </c>
       <c r="L333" t="n">
-        <v>-9</v>
+        <v>-3.913</v>
       </c>
       <c r="M333" t="n">
-        <v>29.756</v>
+        <v>21.428</v>
       </c>
     </row>
     <row r="334">
@@ -17499,10 +17499,10 @@
         <v>4.782</v>
       </c>
       <c r="L334" t="n">
-        <v>-9</v>
+        <v>-4.23</v>
       </c>
       <c r="M334" t="n">
-        <v>27.704</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="335">
@@ -17544,10 +17544,10 @@
         <v>5.455</v>
       </c>
       <c r="L335" t="n">
-        <v>-7</v>
+        <v>-2.689</v>
       </c>
       <c r="M335" t="n">
-        <v>29.3</v>
+        <v>21.046</v>
       </c>
     </row>
     <row r="336">
@@ -17589,10 +17589,10 @@
         <v>5.518</v>
       </c>
       <c r="L336" t="n">
-        <v>-7</v>
+        <v>-2.667</v>
       </c>
       <c r="M336" t="n">
-        <v>29.308</v>
+        <v>21.073</v>
       </c>
     </row>
     <row r="337">
@@ -17634,10 +17634,10 @@
         <v>5.578</v>
       </c>
       <c r="L337" t="n">
-        <v>-9</v>
+        <v>-3.954</v>
       </c>
       <c r="M337" t="n">
-        <v>29.956</v>
+        <v>21.518</v>
       </c>
     </row>
     <row r="338">
@@ -17679,10 +17679,10 @@
         <v>5.526</v>
       </c>
       <c r="L338" t="n">
-        <v>-9</v>
+        <v>-3.972</v>
       </c>
       <c r="M338" t="n">
-        <v>29.474</v>
+        <v>21.185</v>
       </c>
     </row>
     <row r="339">
@@ -17724,10 +17724,10 @@
         <v>5.935</v>
       </c>
       <c r="L339" t="n">
-        <v>-7</v>
+        <v>-2.523</v>
       </c>
       <c r="M339" t="n">
-        <v>30.388</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="340">
@@ -17769,10 +17769,10 @@
         <v>4.861</v>
       </c>
       <c r="L340" t="n">
-        <v>-9</v>
+        <v>-4.202</v>
       </c>
       <c r="M340" t="n">
-        <v>27.864</v>
+        <v>19.902</v>
       </c>
     </row>
     <row r="341">
@@ -17814,10 +17814,10 @@
         <v>5.1</v>
       </c>
       <c r="L341" t="n">
-        <v>-9</v>
+        <v>-4.119</v>
       </c>
       <c r="M341" t="n">
-        <v>28.334</v>
+        <v>20.292</v>
       </c>
     </row>
     <row r="342">
@@ -17859,10 +17859,10 @@
         <v>6.017</v>
       </c>
       <c r="L342" t="n">
-        <v>-7</v>
+        <v>-2.494</v>
       </c>
       <c r="M342" t="n">
-        <v>30.612</v>
+        <v>22.099</v>
       </c>
     </row>
     <row r="343">
@@ -17904,10 +17904,10 @@
         <v>5.901</v>
       </c>
       <c r="L343" t="n">
-        <v>-9</v>
+        <v>-3.842</v>
       </c>
       <c r="M343" t="n">
-        <v>30.446</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>5.513</v>
       </c>
       <c r="L344" t="n">
-        <v>-9</v>
+        <v>-3.977</v>
       </c>
       <c r="M344" t="n">
-        <v>29.628</v>
+        <v>21.281</v>
       </c>
     </row>
     <row r="345">
@@ -17994,10 +17994,10 @@
         <v>5.554</v>
       </c>
       <c r="L345" t="n">
-        <v>-7</v>
+        <v>-2.655</v>
       </c>
       <c r="M345" t="n">
-        <v>29.558</v>
+        <v>21.249</v>
       </c>
     </row>
     <row r="346">
@@ -18039,10 +18039,10 @@
         <v>6.294</v>
       </c>
       <c r="L346" t="n">
-        <v>-9</v>
+        <v>-3.706</v>
       </c>
       <c r="M346" t="n">
-        <v>31.29</v>
+        <v>22.638</v>
       </c>
     </row>
     <row r="347">
@@ -18084,10 +18084,10 @@
         <v>6.403</v>
       </c>
       <c r="L347" t="n">
-        <v>-7</v>
+        <v>-2.361</v>
       </c>
       <c r="M347" t="n">
-        <v>31.33</v>
+        <v>22.702</v>
       </c>
     </row>
     <row r="348">
@@ -18129,10 +18129,10 @@
         <v>5.619</v>
       </c>
       <c r="L348" t="n">
-        <v>-9</v>
+        <v>-3.94</v>
       </c>
       <c r="M348" t="n">
-        <v>29.666</v>
+        <v>21.342</v>
       </c>
     </row>
     <row r="349">
@@ -18174,10 +18174,10 @@
         <v>5.3</v>
       </c>
       <c r="L349" t="n">
-        <v>-7</v>
+        <v>-2.743</v>
       </c>
       <c r="M349" t="n">
-        <v>29.09</v>
+        <v>20.855</v>
       </c>
     </row>
     <row r="350">
@@ -18219,10 +18219,10 @@
         <v>5.888</v>
       </c>
       <c r="L350" t="n">
-        <v>-7</v>
+        <v>-2.539</v>
       </c>
       <c r="M350" t="n">
-        <v>30.362</v>
+        <v>21.891</v>
       </c>
     </row>
     <row r="351">
@@ -18264,10 +18264,10 @@
         <v>5.742</v>
       </c>
       <c r="L351" t="n">
-        <v>-7</v>
+        <v>-2.59</v>
       </c>
       <c r="M351" t="n">
-        <v>29.998</v>
+        <v>21.602</v>
       </c>
     </row>
     <row r="352">
@@ -18309,10 +18309,10 @@
         <v>5.844</v>
       </c>
       <c r="L352" t="n">
-        <v>-7</v>
+        <v>-2.554</v>
       </c>
       <c r="M352" t="n">
-        <v>30.12</v>
+        <v>21.717</v>
       </c>
     </row>
     <row r="353">
@@ -18354,10 +18354,10 @@
         <v>5.87</v>
       </c>
       <c r="L353" t="n">
-        <v>-7</v>
+        <v>-2.545</v>
       </c>
       <c r="M353" t="n">
-        <v>30.304</v>
+        <v>21.847</v>
       </c>
     </row>
     <row r="354">
@@ -18399,10 +18399,10 @@
         <v>5.708</v>
       </c>
       <c r="L354" t="n">
-        <v>-9</v>
+        <v>-3.909</v>
       </c>
       <c r="M354" t="n">
-        <v>29.91</v>
+        <v>21.533</v>
       </c>
     </row>
     <row r="355">
@@ -18444,10 +18444,10 @@
         <v>5.795</v>
       </c>
       <c r="L355" t="n">
-        <v>-7</v>
+        <v>-2.571</v>
       </c>
       <c r="M355" t="n">
-        <v>29.996</v>
+        <v>21.619</v>
       </c>
     </row>
     <row r="356">
@@ -18489,10 +18489,10 @@
         <v>6.316</v>
       </c>
       <c r="L356" t="n">
-        <v>-7</v>
+        <v>-2.391</v>
       </c>
       <c r="M356" t="n">
-        <v>31.286</v>
+        <v>22.643</v>
       </c>
     </row>
     <row r="357">
@@ -18534,10 +18534,10 @@
         <v>5.807</v>
       </c>
       <c r="L357" t="n">
-        <v>-7</v>
+        <v>-2.567</v>
       </c>
       <c r="M357" t="n">
-        <v>30.202</v>
+        <v>21.758</v>
       </c>
     </row>
     <row r="358">
@@ -18579,10 +18579,10 @@
         <v>5.987</v>
       </c>
       <c r="L358" t="n">
-        <v>-9</v>
+        <v>-3.812</v>
       </c>
       <c r="M358" t="n">
-        <v>30.596</v>
+        <v>22.078</v>
       </c>
     </row>
     <row r="359">
@@ -18624,10 +18624,10 @@
         <v>4.669</v>
       </c>
       <c r="L359" t="n">
-        <v>-9</v>
+        <v>-4.269</v>
       </c>
       <c r="M359" t="n">
-        <v>27.116</v>
+        <v>19.346</v>
       </c>
     </row>
     <row r="360">
@@ -18669,10 +18669,10 @@
         <v>5.747</v>
       </c>
       <c r="L360" t="n">
-        <v>-7</v>
+        <v>-2.588</v>
       </c>
       <c r="M360" t="n">
-        <v>29.56</v>
+        <v>21.317</v>
       </c>
     </row>
     <row r="361">
@@ -18714,10 +18714,10 @@
         <v>5.081</v>
       </c>
       <c r="L361" t="n">
-        <v>-9</v>
+        <v>-4.126</v>
       </c>
       <c r="M361" t="n">
-        <v>27.958</v>
+        <v>20.039</v>
       </c>
     </row>
     <row r="362">
@@ -18759,10 +18759,10 @@
         <v>4.855</v>
       </c>
       <c r="L362" t="n">
-        <v>-9</v>
+        <v>-4.204</v>
       </c>
       <c r="M362" t="n">
-        <v>27.542</v>
+        <v>19.689</v>
       </c>
     </row>
     <row r="363">
@@ -18804,10 +18804,10 @@
         <v>5.386</v>
       </c>
       <c r="L363" t="n">
-        <v>-7</v>
+        <v>-2.713</v>
       </c>
       <c r="M363" t="n">
-        <v>28.516</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="364">
@@ -18849,10 +18849,10 @@
         <v>5.745</v>
       </c>
       <c r="L364" t="n">
-        <v>-7</v>
+        <v>-2.589</v>
       </c>
       <c r="M364" t="n">
-        <v>29.596</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="365">
@@ -18894,10 +18894,10 @@
         <v>5.443</v>
       </c>
       <c r="L365" t="n">
-        <v>-9</v>
+        <v>-4.001</v>
       </c>
       <c r="M365" t="n">
-        <v>28.974</v>
+        <v>20.829</v>
       </c>
     </row>
     <row r="366">
@@ -18939,10 +18939,10 @@
         <v>5.154</v>
       </c>
       <c r="L366" t="n">
-        <v>-7</v>
+        <v>-2.793</v>
       </c>
       <c r="M366" t="n">
-        <v>28.276</v>
+        <v>20.273</v>
       </c>
     </row>
     <row r="367">
@@ -18984,10 +18984,10 @@
         <v>5.689</v>
       </c>
       <c r="L367" t="n">
-        <v>-7</v>
+        <v>-2.608</v>
       </c>
       <c r="M367" t="n">
-        <v>29.456</v>
+        <v>21.229</v>
       </c>
     </row>
     <row r="368">
@@ -19029,10 +19029,10 @@
         <v>5.349</v>
       </c>
       <c r="L368" t="n">
-        <v>-9</v>
+        <v>-4.033</v>
       </c>
       <c r="M368" t="n">
-        <v>28.562</v>
+        <v>20.527</v>
       </c>
     </row>
     <row r="369">
@@ -19074,10 +19074,10 @@
         <v>6.165</v>
       </c>
       <c r="L369" t="n">
-        <v>-7</v>
+        <v>-2.443</v>
       </c>
       <c r="M369" t="n">
-        <v>30.596</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="370">
@@ -19119,10 +19119,10 @@
         <v>4.932</v>
       </c>
       <c r="L370" t="n">
-        <v>-9</v>
+        <v>-4.178</v>
       </c>
       <c r="M370" t="n">
-        <v>27.682</v>
+        <v>19.807</v>
       </c>
     </row>
     <row r="371">
@@ -19164,10 +19164,10 @@
         <v>5.173</v>
       </c>
       <c r="L371" t="n">
-        <v>-7</v>
+        <v>-2.786</v>
       </c>
       <c r="M371" t="n">
-        <v>28.13</v>
+        <v>20.184</v>
       </c>
     </row>
     <row r="372">
@@ -19209,10 +19209,10 @@
         <v>4.885</v>
       </c>
       <c r="L372" t="n">
-        <v>-9</v>
+        <v>-4.194</v>
       </c>
       <c r="M372" t="n">
-        <v>27.488</v>
+        <v>19.664</v>
       </c>
     </row>
     <row r="373">
@@ -19254,10 +19254,10 @@
         <v>5.609</v>
       </c>
       <c r="L373" t="n">
-        <v>-7</v>
+        <v>-2.636</v>
       </c>
       <c r="M373" t="n">
-        <v>29.356</v>
+        <v>21.136</v>
       </c>
     </row>
     <row r="374">
@@ -19299,10 +19299,10 @@
         <v>5.863</v>
       </c>
       <c r="L374" t="n">
-        <v>-7</v>
+        <v>-2.548</v>
       </c>
       <c r="M374" t="n">
-        <v>29.61</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="375">
@@ -19344,10 +19344,10 @@
         <v>5.257</v>
       </c>
       <c r="L375" t="n">
-        <v>-7</v>
+        <v>-2.757</v>
       </c>
       <c r="M375" t="n">
-        <v>28.456</v>
+        <v>20.426</v>
       </c>
     </row>
     <row r="376">
@@ -19389,10 +19389,10 @@
         <v>5.781</v>
       </c>
       <c r="L376" t="n">
-        <v>-9</v>
+        <v>-3.884</v>
       </c>
       <c r="M376" t="n">
-        <v>29.724</v>
+        <v>21.436</v>
       </c>
     </row>
     <row r="377">
@@ -19434,10 +19434,10 @@
         <v>5.97</v>
       </c>
       <c r="L377" t="n">
-        <v>-9</v>
+        <v>-3.818</v>
       </c>
       <c r="M377" t="n">
-        <v>30.042</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="378">
@@ -19479,10 +19479,10 @@
         <v>5.918</v>
       </c>
       <c r="L378" t="n">
-        <v>-7</v>
+        <v>-2.529</v>
       </c>
       <c r="M378" t="n">
-        <v>29.92</v>
+        <v>21.612</v>
       </c>
     </row>
     <row r="379">
@@ -19524,10 +19524,10 @@
         <v>5.997</v>
       </c>
       <c r="L379" t="n">
-        <v>-7</v>
+        <v>-2.501</v>
       </c>
       <c r="M379" t="n">
-        <v>30.182</v>
+        <v>21.811</v>
       </c>
     </row>
     <row r="380">
@@ -19569,10 +19569,10 @@
         <v>5.614</v>
       </c>
       <c r="L380" t="n">
-        <v>-7</v>
+        <v>-2.634</v>
       </c>
       <c r="M380" t="n">
-        <v>29.336</v>
+        <v>21.125</v>
       </c>
     </row>
     <row r="381">
@@ -19614,10 +19614,10 @@
         <v>5.769</v>
       </c>
       <c r="L381" t="n">
-        <v>-9</v>
+        <v>-3.888</v>
       </c>
       <c r="M381" t="n">
-        <v>29.634</v>
+        <v>21.373</v>
       </c>
     </row>
     <row r="382">
@@ -19659,10 +19659,10 @@
         <v>6.11</v>
       </c>
       <c r="L382" t="n">
-        <v>-7</v>
+        <v>-2.462</v>
       </c>
       <c r="M382" t="n">
-        <v>30.522</v>
+        <v>22.072</v>
       </c>
     </row>
     <row r="383">
@@ -19704,10 +19704,10 @@
         <v>6.09</v>
       </c>
       <c r="L383" t="n">
-        <v>-9</v>
+        <v>-3.777</v>
       </c>
       <c r="M383" t="n">
-        <v>30.432</v>
+        <v>22.006</v>
       </c>
     </row>
     <row r="384">
@@ -19749,10 +19749,10 @@
         <v>6.004</v>
       </c>
       <c r="L384" t="n">
-        <v>-7</v>
+        <v>-2.499</v>
       </c>
       <c r="M384" t="n">
-        <v>30.166</v>
+        <v>21.803</v>
       </c>
     </row>
     <row r="385">
@@ -19794,10 +19794,10 @@
         <v>5.874</v>
       </c>
       <c r="L385" t="n">
-        <v>-9</v>
+        <v>-3.852</v>
       </c>
       <c r="M385" t="n">
-        <v>30.004</v>
+        <v>21.652</v>
       </c>
     </row>
     <row r="386">
@@ -19839,10 +19839,10 @@
         <v>5.945</v>
       </c>
       <c r="L386" t="n">
-        <v>-7</v>
+        <v>-2.519</v>
       </c>
       <c r="M386" t="n">
-        <v>29.996</v>
+        <v>21.671</v>
       </c>
     </row>
     <row r="387">
@@ -19884,10 +19884,10 @@
         <v>6.751</v>
       </c>
       <c r="L387" t="n">
-        <v>-7</v>
+        <v>-2.24</v>
       </c>
       <c r="M387" t="n">
-        <v>32.398</v>
+        <v>23.521</v>
       </c>
     </row>
     <row r="388">
@@ -19929,10 +19929,10 @@
         <v>5.915</v>
       </c>
       <c r="L388" t="n">
-        <v>-9</v>
+        <v>-3.837</v>
       </c>
       <c r="M388" t="n">
-        <v>30.016</v>
+        <v>21.674</v>
       </c>
     </row>
     <row r="389">
@@ -19974,10 +19974,10 @@
         <v>5.539</v>
       </c>
       <c r="L389" t="n">
-        <v>-9</v>
+        <v>-3.968</v>
       </c>
       <c r="M389" t="n">
-        <v>29.19</v>
+        <v>21.004</v>
       </c>
     </row>
     <row r="390">
@@ -20019,10 +20019,10 @@
         <v>5.968</v>
       </c>
       <c r="L390" t="n">
-        <v>-7</v>
+        <v>-2.511</v>
       </c>
       <c r="M390" t="n">
-        <v>30.016</v>
+        <v>21.692</v>
       </c>
     </row>
     <row r="391">
@@ -20064,10 +20064,10 @@
         <v>5.914</v>
       </c>
       <c r="L391" t="n">
-        <v>-9</v>
+        <v>-3.838</v>
       </c>
       <c r="M391" t="n">
-        <v>30.042</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="392">
@@ -20109,10 +20109,10 @@
         <v>5.685</v>
       </c>
       <c r="L392" t="n">
-        <v>-7</v>
+        <v>-2.609</v>
       </c>
       <c r="M392" t="n">
-        <v>29.46</v>
+        <v>21.231</v>
       </c>
     </row>
     <row r="393">
@@ -20154,10 +20154,10 @@
         <v>5.739</v>
       </c>
       <c r="L393" t="n">
-        <v>-9</v>
+        <v>-3.898</v>
       </c>
       <c r="M393" t="n">
-        <v>29.184</v>
+        <v>21.069</v>
       </c>
     </row>
     <row r="394">
@@ -20199,10 +20199,10 @@
         <v>5.001</v>
       </c>
       <c r="L394" t="n">
-        <v>-9</v>
+        <v>-4.154</v>
       </c>
       <c r="M394" t="n">
-        <v>27.712</v>
+        <v>19.851</v>
       </c>
     </row>
     <row r="395">
@@ -20244,10 +20244,10 @@
         <v>6.087</v>
       </c>
       <c r="L395" t="n">
-        <v>-7</v>
+        <v>-2.47</v>
       </c>
       <c r="M395" t="n">
-        <v>30.084</v>
+        <v>21.778</v>
       </c>
     </row>
     <row r="396">
@@ -20289,10 +20289,10 @@
         <v>5.798</v>
       </c>
       <c r="L396" t="n">
-        <v>-9</v>
+        <v>-3.878</v>
       </c>
       <c r="M396" t="n">
-        <v>29.258</v>
+        <v>21.138</v>
       </c>
     </row>
     <row r="397">
@@ -20334,10 +20334,10 @@
         <v>6.02</v>
       </c>
       <c r="L397" t="n">
-        <v>-7</v>
+        <v>-2.493</v>
       </c>
       <c r="M397" t="n">
-        <v>29.952</v>
+        <v>21.668</v>
       </c>
     </row>
     <row r="398">
@@ -20379,10 +20379,10 @@
         <v>6.115</v>
       </c>
       <c r="L398" t="n">
-        <v>-9</v>
+        <v>-3.768</v>
       </c>
       <c r="M398" t="n">
-        <v>30.078</v>
+        <v>21.784</v>
       </c>
     </row>
     <row r="399">
@@ -20424,10 +20424,10 @@
         <v>5.6</v>
       </c>
       <c r="L399" t="n">
-        <v>-9</v>
+        <v>-3.946</v>
       </c>
       <c r="M399" t="n">
-        <v>28.932</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="400">
@@ -20469,10 +20469,10 @@
         <v>5.295</v>
       </c>
       <c r="L400" t="n">
-        <v>-9</v>
+        <v>-4.052</v>
       </c>
       <c r="M400" t="n">
-        <v>28.178</v>
+        <v>20.257</v>
       </c>
     </row>
     <row r="401">
@@ -20514,10 +20514,10 @@
         <v>6.182</v>
       </c>
       <c r="L401" t="n">
-        <v>-7</v>
+        <v>-2.437</v>
       </c>
       <c r="M401" t="n">
-        <v>30.242</v>
+        <v>21.914</v>
       </c>
     </row>
     <row r="402">
@@ -20559,10 +20559,10 @@
         <v>5.556</v>
       </c>
       <c r="L402" t="n">
-        <v>-9</v>
+        <v>-3.962</v>
       </c>
       <c r="M402" t="n">
-        <v>28.852</v>
+        <v>20.788</v>
       </c>
     </row>
     <row r="403">
@@ -20604,10 +20604,10 @@
         <v>6.068</v>
       </c>
       <c r="L403" t="n">
-        <v>-9</v>
+        <v>-3.784</v>
       </c>
       <c r="M403" t="n">
-        <v>29.926</v>
+        <v>21.668</v>
       </c>
     </row>
     <row r="404">
@@ -20649,10 +20649,10 @@
         <v>5.938</v>
       </c>
       <c r="L404" t="n">
-        <v>-7</v>
+        <v>-2.522</v>
       </c>
       <c r="M404" t="n">
-        <v>29.68</v>
+        <v>21.462</v>
       </c>
     </row>
     <row r="405">
@@ -20694,10 +20694,10 @@
         <v>4.965</v>
       </c>
       <c r="L405" t="n">
-        <v>-9</v>
+        <v>-4.166</v>
       </c>
       <c r="M405" t="n">
-        <v>27.66</v>
+        <v>19.804</v>
       </c>
     </row>
     <row r="406">
@@ -20739,10 +20739,10 @@
         <v>5.603</v>
       </c>
       <c r="L406" t="n">
-        <v>-9</v>
+        <v>-3.945</v>
       </c>
       <c r="M406" t="n">
-        <v>28.968</v>
+        <v>20.881</v>
       </c>
     </row>
     <row r="407">
@@ -20784,10 +20784,10 @@
         <v>5.547</v>
       </c>
       <c r="L407" t="n">
-        <v>-9</v>
+        <v>-3.965</v>
       </c>
       <c r="M407" t="n">
-        <v>28.82</v>
+        <v>20.764</v>
       </c>
     </row>
     <row r="408">
@@ -20829,10 +20829,10 @@
         <v>5.646</v>
       </c>
       <c r="L408" t="n">
-        <v>-9</v>
+        <v>-3.931</v>
       </c>
       <c r="M408" t="n">
-        <v>29.004</v>
+        <v>20.919</v>
       </c>
     </row>
     <row r="409">
@@ -20874,10 +20874,10 @@
         <v>5.364</v>
       </c>
       <c r="L409" t="n">
-        <v>-9</v>
+        <v>-4.028</v>
       </c>
       <c r="M409" t="n">
-        <v>28.308</v>
+        <v>20.366</v>
       </c>
     </row>
     <row r="410">
@@ -20919,10 +20919,10 @@
         <v>5.391</v>
       </c>
       <c r="L410" t="n">
-        <v>-9</v>
+        <v>-4.019</v>
       </c>
       <c r="M410" t="n">
-        <v>24.942</v>
+        <v>18.175</v>
       </c>
     </row>
     <row r="411">
@@ -20964,10 +20964,10 @@
         <v>5.48</v>
       </c>
       <c r="L411" t="n">
-        <v>-7</v>
+        <v>-2.68</v>
       </c>
       <c r="M411" t="n">
-        <v>28.038</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="412">
@@ -21009,10 +21009,10 @@
         <v>4.797</v>
       </c>
       <c r="L412" t="n">
-        <v>-9</v>
+        <v>-4.224</v>
       </c>
       <c r="M412" t="n">
-        <v>26.394</v>
+        <v>18.919</v>
       </c>
     </row>
     <row r="413">
@@ -21054,10 +21054,10 @@
         <v>5.177</v>
       </c>
       <c r="L413" t="n">
-        <v>-9</v>
+        <v>-4.093</v>
       </c>
       <c r="M413" t="n">
-        <v>24.62</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="414">
@@ -21099,10 +21099,10 @@
         <v>4.897</v>
       </c>
       <c r="L414" t="n">
-        <v>-9</v>
+        <v>-4.19</v>
       </c>
       <c r="M414" t="n">
-        <v>26.684</v>
+        <v>19.143</v>
       </c>
     </row>
     <row r="415">
@@ -21144,10 +21144,10 @@
         <v>4.837</v>
       </c>
       <c r="L415" t="n">
-        <v>-9</v>
+        <v>-4.211</v>
       </c>
       <c r="M415" t="n">
-        <v>23.46</v>
+        <v>17.014</v>
       </c>
     </row>
     <row r="416">
@@ -21189,10 +21189,10 @@
         <v>4.944</v>
       </c>
       <c r="L416" t="n">
-        <v>-7</v>
+        <v>-2.866</v>
       </c>
       <c r="M416" t="n">
-        <v>26.934</v>
+        <v>19.322</v>
       </c>
     </row>
     <row r="417">
@@ -21234,10 +21234,10 @@
         <v>5.106</v>
       </c>
       <c r="L417" t="n">
-        <v>-7</v>
+        <v>-2.81</v>
       </c>
       <c r="M417" t="n">
-        <v>26.948</v>
+        <v>19.388</v>
       </c>
     </row>
     <row r="418">
@@ -21279,10 +21279,10 @@
         <v>4.631</v>
       </c>
       <c r="L418" t="n">
-        <v>-9</v>
+        <v>-4.282</v>
       </c>
       <c r="M418" t="n">
-        <v>23.072</v>
+        <v>16.689</v>
       </c>
     </row>
     <row r="419">
@@ -21324,10 +21324,10 @@
         <v>4.499</v>
       </c>
       <c r="L419" t="n">
-        <v>-9</v>
+        <v>-4.328</v>
       </c>
       <c r="M419" t="n">
-        <v>25.794</v>
+        <v>18.423</v>
       </c>
     </row>
     <row r="420">
@@ -21369,10 +21369,10 @@
         <v>5.854</v>
       </c>
       <c r="L420" t="n">
-        <v>-7</v>
+        <v>-2.551</v>
       </c>
       <c r="M420" t="n">
-        <v>26.028</v>
+        <v>19.045</v>
       </c>
     </row>
     <row r="421">
@@ -21414,10 +21414,10 @@
         <v>4.815</v>
       </c>
       <c r="L421" t="n">
-        <v>-9</v>
+        <v>-4.218</v>
       </c>
       <c r="M421" t="n">
-        <v>23.714</v>
+        <v>17.172</v>
       </c>
     </row>
     <row r="422">
@@ -21459,10 +21459,10 @@
         <v>5.489</v>
       </c>
       <c r="L422" t="n">
-        <v>-7</v>
+        <v>-2.677</v>
       </c>
       <c r="M422" t="n">
-        <v>27.882</v>
+        <v>20.131</v>
       </c>
     </row>
     <row r="423">
@@ -21504,10 +21504,10 @@
         <v>4.885</v>
       </c>
       <c r="L423" t="n">
-        <v>-9</v>
+        <v>-4.194</v>
       </c>
       <c r="M423" t="n">
-        <v>23.576</v>
+        <v>17.106</v>
       </c>
     </row>
     <row r="424">
@@ -21549,10 +21549,10 @@
         <v>4.957</v>
       </c>
       <c r="L424" t="n">
-        <v>-9</v>
+        <v>-4.169</v>
       </c>
       <c r="M424" t="n">
-        <v>23.67</v>
+        <v>17.193</v>
       </c>
     </row>
     <row r="425">
@@ -21594,10 +21594,10 @@
         <v>4.754</v>
       </c>
       <c r="L425" t="n">
-        <v>-9</v>
+        <v>-4.239</v>
       </c>
       <c r="M425" t="n">
-        <v>23.276</v>
+        <v>16.865</v>
       </c>
     </row>
     <row r="426">
@@ -21639,10 +21639,10 @@
         <v>4.399</v>
       </c>
       <c r="L426" t="n">
-        <v>-9</v>
+        <v>-4.362</v>
       </c>
       <c r="M426" t="n">
-        <v>22.624</v>
+        <v>16.316</v>
       </c>
     </row>
     <row r="427">
@@ -21684,10 +21684,10 @@
         <v>9.242000000000001</v>
       </c>
       <c r="L427" t="n">
-        <v>-7</v>
+        <v>-1.378</v>
       </c>
       <c r="M427" t="n">
-        <v>30.406</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="428">
@@ -21729,10 +21729,10 @@
         <v>5.986</v>
       </c>
       <c r="L428" t="n">
-        <v>-7</v>
+        <v>-2.505</v>
       </c>
       <c r="M428" t="n">
-        <v>29.948</v>
+        <v>21.654</v>
       </c>
     </row>
     <row r="429">
@@ -21774,10 +21774,10 @@
         <v>5.659</v>
       </c>
       <c r="L429" t="n">
-        <v>-9</v>
+        <v>-3.926</v>
       </c>
       <c r="M429" t="n">
-        <v>29.132</v>
+        <v>21.007</v>
       </c>
     </row>
     <row r="430">
@@ -21819,10 +21819,10 @@
         <v>6.129</v>
       </c>
       <c r="L430" t="n">
-        <v>-7</v>
+        <v>-2.456</v>
       </c>
       <c r="M430" t="n">
-        <v>30.898</v>
+        <v>22.325</v>
       </c>
     </row>
     <row r="431">
@@ -21864,10 +21864,10 @@
         <v>5.474</v>
       </c>
       <c r="L431" t="n">
-        <v>-9</v>
+        <v>-3.99</v>
       </c>
       <c r="M431" t="n">
-        <v>28.616</v>
+        <v>20.606</v>
       </c>
     </row>
     <row r="432">
@@ -21909,10 +21909,10 @@
         <v>6.784</v>
       </c>
       <c r="L432" t="n">
-        <v>-7</v>
+        <v>-2.229</v>
       </c>
       <c r="M432" t="n">
-        <v>32.29</v>
+        <v>23.461</v>
       </c>
     </row>
     <row r="433">
@@ -21954,10 +21954,10 @@
         <v>6.834</v>
       </c>
       <c r="L433" t="n">
-        <v>-7</v>
+        <v>-2.212</v>
       </c>
       <c r="M433" t="n">
-        <v>32.308</v>
+        <v>23.491</v>
       </c>
     </row>
     <row r="434">
@@ -21999,10 +21999,10 @@
         <v>6.099</v>
       </c>
       <c r="L434" t="n">
-        <v>-7</v>
+        <v>-2.466</v>
       </c>
       <c r="M434" t="n">
-        <v>30.166</v>
+        <v>21.836</v>
       </c>
     </row>
     <row r="435">
@@ -22044,10 +22044,10 @@
         <v>5.347</v>
       </c>
       <c r="L435" t="n">
-        <v>-7</v>
+        <v>-2.726</v>
       </c>
       <c r="M435" t="n">
-        <v>28.24</v>
+        <v>20.316</v>
       </c>
     </row>
     <row r="436">
@@ -22089,10 +22089,10 @@
         <v>5.795</v>
       </c>
       <c r="L436" t="n">
-        <v>-7</v>
+        <v>-2.571</v>
       </c>
       <c r="M436" t="n">
-        <v>29.32</v>
+        <v>21.177</v>
       </c>
     </row>
     <row r="437">
@@ -22134,10 +22134,10 @@
         <v>5.736</v>
       </c>
       <c r="L437" t="n">
-        <v>-9</v>
+        <v>-3.899</v>
       </c>
       <c r="M437" t="n">
-        <v>29.148</v>
+        <v>21.044</v>
       </c>
     </row>
     <row r="438">
@@ -22179,10 +22179,10 @@
         <v>5.643</v>
       </c>
       <c r="L438" t="n">
-        <v>-7</v>
+        <v>-2.624</v>
       </c>
       <c r="M438" t="n">
-        <v>28.896</v>
+        <v>20.847</v>
       </c>
     </row>
     <row r="439">
@@ -22224,10 +22224,10 @@
         <v>6.355</v>
       </c>
       <c r="L439" t="n">
-        <v>-7</v>
+        <v>-2.377</v>
       </c>
       <c r="M439" t="n">
-        <v>30.524</v>
+        <v>22.158</v>
       </c>
     </row>
     <row r="440">
@@ -22269,10 +22269,10 @@
         <v>6.243</v>
       </c>
       <c r="L440" t="n">
-        <v>-7</v>
+        <v>-2.416</v>
       </c>
       <c r="M440" t="n">
-        <v>28.282</v>
+        <v>20.654</v>
       </c>
     </row>
     <row r="441">
@@ -22314,10 +22314,10 @@
         <v>5.736</v>
       </c>
       <c r="L441" t="n">
-        <v>-7</v>
+        <v>-2.592</v>
       </c>
       <c r="M441" t="n">
-        <v>29.102</v>
+        <v>21.014</v>
       </c>
     </row>
     <row r="442">
@@ -22359,10 +22359,10 @@
         <v>5.71</v>
       </c>
       <c r="L442" t="n">
-        <v>-7</v>
+        <v>-2.601</v>
       </c>
       <c r="M442" t="n">
-        <v>29.252</v>
+        <v>21.103</v>
       </c>
     </row>
     <row r="443">
@@ -22404,10 +22404,10 @@
         <v>5.247</v>
       </c>
       <c r="L443" t="n">
-        <v>-9</v>
+        <v>-4.069</v>
       </c>
       <c r="M443" t="n">
-        <v>28.06</v>
+        <v>20.164</v>
       </c>
     </row>
     <row r="444">
@@ -22449,10 +22449,10 @@
         <v>7.112</v>
       </c>
       <c r="L444" t="n">
-        <v>-7</v>
+        <v>-2.115</v>
       </c>
       <c r="M444" t="n">
-        <v>29.746</v>
+        <v>21.912</v>
       </c>
     </row>
     <row r="445">
@@ -22494,10 +22494,10 @@
         <v>5.782</v>
       </c>
       <c r="L445" t="n">
-        <v>-9</v>
+        <v>-3.883</v>
       </c>
       <c r="M445" t="n">
-        <v>28.842</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="446">
@@ -22539,10 +22539,10 @@
         <v>6.208</v>
       </c>
       <c r="L446" t="n">
-        <v>-7</v>
+        <v>-2.428</v>
       </c>
       <c r="M446" t="n">
-        <v>29.79</v>
+        <v>21.627</v>
       </c>
     </row>
     <row r="447">
@@ -22584,10 +22584,10 @@
         <v>5.889</v>
       </c>
       <c r="L447" t="n">
-        <v>-9</v>
+        <v>-3.846</v>
       </c>
       <c r="M447" t="n">
-        <v>29.244</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="448">
@@ -22629,10 +22629,10 @@
         <v>7.727</v>
       </c>
       <c r="L448" t="n">
-        <v>-7</v>
+        <v>-1.902</v>
       </c>
       <c r="M448" t="n">
-        <v>30.98</v>
+        <v>22.931</v>
       </c>
     </row>
     <row r="449">
@@ -22674,10 +22674,10 @@
         <v>5.733</v>
       </c>
       <c r="L449" t="n">
-        <v>-9</v>
+        <v>-3.9</v>
       </c>
       <c r="M449" t="n">
-        <v>28.85</v>
+        <v>20.848</v>
       </c>
     </row>
     <row r="450">
@@ -22719,10 +22719,10 @@
         <v>6.379</v>
       </c>
       <c r="L450" t="n">
-        <v>-9</v>
+        <v>-3.677</v>
       </c>
       <c r="M450" t="n">
-        <v>30.16</v>
+        <v>21.929</v>
       </c>
     </row>
     <row r="451">
@@ -22764,10 +22764,10 @@
         <v>5.983</v>
       </c>
       <c r="L451" t="n">
-        <v>-9</v>
+        <v>-3.814</v>
       </c>
       <c r="M451" t="n">
-        <v>29.404</v>
+        <v>21.297</v>
       </c>
     </row>
     <row r="452">
@@ -22809,10 +22809,10 @@
         <v>6.105</v>
       </c>
       <c r="L452" t="n">
-        <v>-9</v>
+        <v>-3.772</v>
       </c>
       <c r="M452" t="n">
-        <v>29.62</v>
+        <v>21.481</v>
       </c>
     </row>
     <row r="453">
@@ -22854,10 +22854,10 @@
         <v>5.596</v>
       </c>
       <c r="L453" t="n">
-        <v>-9</v>
+        <v>-3.948</v>
       </c>
       <c r="M453" t="n">
-        <v>28.576</v>
+        <v>20.622</v>
       </c>
     </row>
     <row r="454">
@@ -22899,10 +22899,10 @@
         <v>6.454</v>
       </c>
       <c r="L454" t="n">
-        <v>-7</v>
+        <v>-2.343</v>
       </c>
       <c r="M454" t="n">
-        <v>30.358</v>
+        <v>22.084</v>
       </c>
     </row>
     <row r="455">
@@ -22944,10 +22944,10 @@
         <v>7.053</v>
       </c>
       <c r="L455" t="n">
-        <v>-9</v>
+        <v>-3.443</v>
       </c>
       <c r="M455" t="n">
-        <v>29.442</v>
+        <v>21.692</v>
       </c>
     </row>
     <row r="456">
@@ -22989,10 +22989,10 @@
         <v>5.742</v>
       </c>
       <c r="L456" t="n">
-        <v>-9</v>
+        <v>-3.897</v>
       </c>
       <c r="M456" t="n">
-        <v>28.888</v>
+        <v>20.876</v>
       </c>
     </row>
     <row r="457">
@@ -23034,10 +23034,10 @@
         <v>6.227</v>
       </c>
       <c r="L457" t="n">
-        <v>-7</v>
+        <v>-2.422</v>
       </c>
       <c r="M457" t="n">
-        <v>29.742</v>
+        <v>21.603</v>
       </c>
     </row>
     <row r="458">
@@ -23079,10 +23079,10 @@
         <v>7.109</v>
       </c>
       <c r="L458" t="n">
-        <v>-9</v>
+        <v>-3.424</v>
       </c>
       <c r="M458" t="n">
-        <v>29.68</v>
+        <v>21.867</v>
       </c>
     </row>
     <row r="459">
@@ -23124,10 +23124,10 @@
         <v>6.329</v>
       </c>
       <c r="L459" t="n">
-        <v>-7</v>
+        <v>-2.386</v>
       </c>
       <c r="M459" t="n">
-        <v>30.3</v>
+        <v>22.003</v>
       </c>
     </row>
     <row r="460">
@@ -23169,10 +23169,10 @@
         <v>6.112</v>
       </c>
       <c r="L460" t="n">
-        <v>-9</v>
+        <v>-3.769</v>
       </c>
       <c r="M460" t="n">
-        <v>29.542</v>
+        <v>21.432</v>
       </c>
     </row>
     <row r="461">
@@ -23214,10 +23214,10 @@
         <v>7.047</v>
       </c>
       <c r="L461" t="n">
-        <v>-7</v>
+        <v>-2.138</v>
       </c>
       <c r="M461" t="n">
-        <v>29.668</v>
+        <v>21.838</v>
       </c>
     </row>
     <row r="462">
@@ -23259,10 +23259,10 @@
         <v>6.932</v>
       </c>
       <c r="L462" t="n">
-        <v>-9</v>
+        <v>-3.485</v>
       </c>
       <c r="M462" t="n">
-        <v>29.45</v>
+        <v>21.656</v>
       </c>
     </row>
     <row r="463">
@@ -23304,10 +23304,10 @@
         <v>6.686</v>
       </c>
       <c r="L463" t="n">
-        <v>-7</v>
+        <v>-2.263</v>
       </c>
       <c r="M463" t="n">
-        <v>31.152</v>
+        <v>22.683</v>
       </c>
     </row>
     <row r="464">
@@ -23349,10 +23349,10 @@
         <v>10.379</v>
       </c>
       <c r="L464" t="n">
-        <v>-7</v>
+        <v>-0.985</v>
       </c>
       <c r="M464" t="n">
-        <v>32.558</v>
+        <v>24.881</v>
       </c>
     </row>
     <row r="465">
@@ -23394,10 +23394,10 @@
         <v>9.254</v>
       </c>
       <c r="L465" t="n">
-        <v>-7</v>
+        <v>-1.374</v>
       </c>
       <c r="M465" t="n">
-        <v>30.184</v>
+        <v>22.939</v>
       </c>
     </row>
     <row r="466">
@@ -23439,10 +23439,10 @@
         <v>6.351</v>
       </c>
       <c r="L466" t="n">
-        <v>-7</v>
+        <v>-2.379</v>
       </c>
       <c r="M466" t="n">
-        <v>30.386</v>
+        <v>22.067</v>
       </c>
     </row>
     <row r="467">
@@ -23484,10 +23484,10 @@
         <v>6.592</v>
       </c>
       <c r="L467" t="n">
-        <v>-7</v>
+        <v>-2.295</v>
       </c>
       <c r="M467" t="n">
-        <v>28.798</v>
+        <v>21.112</v>
       </c>
     </row>
     <row r="468">
@@ -23529,10 +23529,10 @@
         <v>7.164</v>
       </c>
       <c r="L468" t="n">
-        <v>-9</v>
+        <v>-3.405</v>
       </c>
       <c r="M468" t="n">
-        <v>30</v>
+        <v>22.096</v>
       </c>
     </row>
     <row r="469">
@@ -23574,10 +23574,10 @@
         <v>7.083</v>
       </c>
       <c r="L469" t="n">
-        <v>-7</v>
+        <v>-2.125</v>
       </c>
       <c r="M469" t="n">
-        <v>29.73</v>
+        <v>21.891</v>
       </c>
     </row>
     <row r="470">
@@ -23619,10 +23619,10 @@
         <v>5.895</v>
       </c>
       <c r="L470" t="n">
-        <v>-7</v>
+        <v>-2.537</v>
       </c>
       <c r="M470" t="n">
-        <v>29.358</v>
+        <v>21.237</v>
       </c>
     </row>
     <row r="471">
@@ -23664,10 +23664,10 @@
         <v>6.119</v>
       </c>
       <c r="L471" t="n">
-        <v>-7</v>
+        <v>-2.459</v>
       </c>
       <c r="M471" t="n">
-        <v>29.954</v>
+        <v>21.704</v>
       </c>
     </row>
     <row r="472">
@@ -23709,10 +23709,10 @@
         <v>7.462</v>
       </c>
       <c r="L472" t="n">
-        <v>-7</v>
+        <v>-1.994</v>
       </c>
       <c r="M472" t="n">
-        <v>30.53</v>
+        <v>22.545</v>
       </c>
     </row>
     <row r="473">
@@ -23754,10 +23754,10 @@
         <v>7.045</v>
       </c>
       <c r="L473" t="n">
-        <v>-9</v>
+        <v>-3.446</v>
       </c>
       <c r="M473" t="n">
-        <v>29.674</v>
+        <v>21.841</v>
       </c>
     </row>
     <row r="474">
@@ -23799,10 +23799,10 @@
         <v>6.614</v>
       </c>
       <c r="L474" t="n">
-        <v>-9</v>
+        <v>-3.595</v>
       </c>
       <c r="M474" t="n">
-        <v>28.816</v>
+        <v>21.131</v>
       </c>
     </row>
     <row r="475">
@@ -23844,10 +23844,10 @@
         <v>6.466</v>
       </c>
       <c r="L475" t="n">
-        <v>-7</v>
+        <v>-2.339</v>
       </c>
       <c r="M475" t="n">
-        <v>28.538</v>
+        <v>20.898</v>
       </c>
     </row>
     <row r="476">
@@ -23889,10 +23889,10 @@
         <v>7.297</v>
       </c>
       <c r="L476" t="n">
-        <v>-9</v>
+        <v>-3.359</v>
       </c>
       <c r="M476" t="n">
-        <v>30.27</v>
+        <v>22.318</v>
       </c>
     </row>
     <row r="477">
@@ -23934,10 +23934,10 @@
         <v>6.374</v>
       </c>
       <c r="L477" t="n">
-        <v>-9</v>
+        <v>-3.679</v>
       </c>
       <c r="M477" t="n">
-        <v>28.378</v>
+        <v>20.762</v>
       </c>
     </row>
     <row r="478">
@@ -23979,10 +23979,10 @@
         <v>4.606</v>
       </c>
       <c r="L478" t="n">
-        <v>-9</v>
+        <v>-4.29</v>
       </c>
       <c r="M478" t="n">
-        <v>27.03</v>
+        <v>19.268</v>
       </c>
     </row>
     <row r="479">
@@ -24024,10 +24024,10 @@
         <v>5.061</v>
       </c>
       <c r="L479" t="n">
-        <v>-7</v>
+        <v>-2.825</v>
       </c>
       <c r="M479" t="n">
-        <v>28.03</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="480">
@@ -24069,10 +24069,10 @@
         <v>5.319</v>
       </c>
       <c r="L480" t="n">
-        <v>-9</v>
+        <v>-4.044</v>
       </c>
       <c r="M480" t="n">
-        <v>28.432</v>
+        <v>20.432</v>
       </c>
     </row>
     <row r="481">
@@ -24114,10 +24114,10 @@
         <v>5.541</v>
       </c>
       <c r="L481" t="n">
-        <v>-7</v>
+        <v>-2.659</v>
       </c>
       <c r="M481" t="n">
-        <v>28.91</v>
+        <v>20.821</v>
       </c>
     </row>
     <row r="482">
@@ -24159,10 +24159,10 @@
         <v>4.566</v>
       </c>
       <c r="L482" t="n">
-        <v>-9</v>
+        <v>-4.304</v>
       </c>
       <c r="M482" t="n">
-        <v>26.974</v>
+        <v>19.218</v>
       </c>
     </row>
     <row r="483">
@@ -24204,10 +24204,10 @@
         <v>5.946</v>
       </c>
       <c r="L483" t="n">
-        <v>-7</v>
+        <v>-2.519</v>
       </c>
       <c r="M483" t="n">
-        <v>30.03</v>
+        <v>21.694</v>
       </c>
     </row>
     <row r="484">
@@ -24249,10 +24249,10 @@
         <v>5.248</v>
       </c>
       <c r="L484" t="n">
-        <v>-9</v>
+        <v>-4.068</v>
       </c>
       <c r="M484" t="n">
-        <v>28.458</v>
+        <v>20.424</v>
       </c>
     </row>
     <row r="485">
@@ -24294,10 +24294,10 @@
         <v>5.098</v>
       </c>
       <c r="L485" t="n">
-        <v>-7</v>
+        <v>-2.812</v>
       </c>
       <c r="M485" t="n">
-        <v>27.868</v>
+        <v>19.987</v>
       </c>
     </row>
     <row r="486">
@@ -24339,10 +24339,10 @@
         <v>5.235</v>
       </c>
       <c r="L486" t="n">
-        <v>-9</v>
+        <v>-4.073</v>
       </c>
       <c r="M486" t="n">
-        <v>28.31</v>
+        <v>20.323</v>
       </c>
     </row>
     <row r="487">
@@ -24384,10 +24384,10 @@
         <v>4.936</v>
       </c>
       <c r="L487" t="n">
-        <v>-7</v>
+        <v>-2.869</v>
       </c>
       <c r="M487" t="n">
-        <v>27.654</v>
+        <v>19.791</v>
       </c>
     </row>
     <row r="488">
@@ -24429,10 +24429,10 @@
         <v>4.695</v>
       </c>
       <c r="L488" t="n">
-        <v>-9</v>
+        <v>-4.26</v>
       </c>
       <c r="M488" t="n">
-        <v>27.214</v>
+        <v>19.419</v>
       </c>
     </row>
     <row r="489">
@@ -24474,10 +24474,10 @@
         <v>4.563</v>
       </c>
       <c r="L489" t="n">
-        <v>-9</v>
+        <v>-4.305</v>
       </c>
       <c r="M489" t="n">
-        <v>26.748</v>
+        <v>19.069</v>
       </c>
     </row>
     <row r="490">
@@ -24519,10 +24519,10 @@
         <v>4.694</v>
       </c>
       <c r="L490" t="n">
-        <v>-9</v>
+        <v>-4.26</v>
       </c>
       <c r="M490" t="n">
-        <v>27.19</v>
+        <v>19.403</v>
       </c>
     </row>
     <row r="491">
@@ -24564,10 +24564,10 @@
         <v>5.91</v>
       </c>
       <c r="L491" t="n">
-        <v>-7</v>
+        <v>-2.531</v>
       </c>
       <c r="M491" t="n">
-        <v>30.006</v>
+        <v>21.666</v>
       </c>
     </row>
     <row r="492">
@@ -24609,10 +24609,10 @@
         <v>4.757</v>
       </c>
       <c r="L492" t="n">
-        <v>-9</v>
+        <v>-4.238</v>
       </c>
       <c r="M492" t="n">
-        <v>27.306</v>
+        <v>19.501</v>
       </c>
     </row>
     <row r="493">
@@ -24654,10 +24654,10 @@
         <v>4.917</v>
       </c>
       <c r="L493" t="n">
-        <v>-9</v>
+        <v>-4.183</v>
       </c>
       <c r="M493" t="n">
-        <v>27.518</v>
+        <v>19.695</v>
       </c>
     </row>
     <row r="494">
@@ -24699,10 +24699,10 @@
         <v>5.187</v>
       </c>
       <c r="L494" t="n">
-        <v>-9</v>
+        <v>-4.089</v>
       </c>
       <c r="M494" t="n">
-        <v>28.192</v>
+        <v>20.229</v>
       </c>
     </row>
     <row r="495">
@@ -24744,10 +24744,10 @@
         <v>5.562</v>
       </c>
       <c r="L495" t="n">
-        <v>-9</v>
+        <v>-3.96</v>
       </c>
       <c r="M495" t="n">
-        <v>28.982</v>
+        <v>20.876</v>
       </c>
     </row>
     <row r="496">
@@ -24789,10 +24789,10 @@
         <v>5.302</v>
       </c>
       <c r="L496" t="n">
-        <v>-9</v>
+        <v>-4.05</v>
       </c>
       <c r="M496" t="n">
-        <v>28.398</v>
+        <v>20.404</v>
       </c>
     </row>
     <row r="497">
@@ -24834,10 +24834,10 @@
         <v>5.055</v>
       </c>
       <c r="L497" t="n">
-        <v>-7</v>
+        <v>-2.827</v>
       </c>
       <c r="M497" t="n">
-        <v>27.794</v>
+        <v>19.923</v>
       </c>
     </row>
     <row r="498">
@@ -24879,10 +24879,10 @@
         <v>5.672</v>
       </c>
       <c r="L498" t="n">
-        <v>-7</v>
+        <v>-2.614</v>
       </c>
       <c r="M498" t="n">
-        <v>29.248</v>
+        <v>21.088</v>
       </c>
     </row>
     <row r="499">
@@ -24924,10 +24924,10 @@
         <v>5.345</v>
       </c>
       <c r="L499" t="n">
-        <v>-9</v>
+        <v>-4.035</v>
       </c>
       <c r="M499" t="n">
-        <v>28.424</v>
+        <v>20.436</v>
       </c>
     </row>
     <row r="500">
@@ -24969,10 +24969,10 @@
         <v>5.508</v>
       </c>
       <c r="L500" t="n">
-        <v>-9</v>
+        <v>-3.978</v>
       </c>
       <c r="M500" t="n">
-        <v>28.832</v>
+        <v>20.759</v>
       </c>
     </row>
     <row r="501">
@@ -25014,10 +25014,10 @@
         <v>5.404</v>
       </c>
       <c r="L501" t="n">
-        <v>-9</v>
+        <v>-4.014</v>
       </c>
       <c r="M501" t="n">
-        <v>28.682</v>
+        <v>20.625</v>
       </c>
     </row>
     <row r="502">
@@ -25059,10 +25059,10 @@
         <v>5.464</v>
       </c>
       <c r="L502" t="n">
-        <v>-7</v>
+        <v>-2.686</v>
       </c>
       <c r="M502" t="n">
-        <v>28.742</v>
+        <v>20.685</v>
       </c>
     </row>
     <row r="503">
@@ -25104,10 +25104,10 @@
         <v>5.308</v>
       </c>
       <c r="L503" t="n">
-        <v>-9</v>
+        <v>-4.047</v>
       </c>
       <c r="M503" t="n">
-        <v>28.504</v>
+        <v>20.475</v>
       </c>
     </row>
     <row r="504">
@@ -25149,10 +25149,10 @@
         <v>5.2</v>
       </c>
       <c r="L504" t="n">
-        <v>-9</v>
+        <v>-4.085</v>
       </c>
       <c r="M504" t="n">
-        <v>28.1</v>
+        <v>20.174</v>
       </c>
     </row>
     <row r="505">
@@ -25194,10 +25194,10 @@
         <v>5.49</v>
       </c>
       <c r="L505" t="n">
-        <v>-9</v>
+        <v>-3.985</v>
       </c>
       <c r="M505" t="n">
-        <v>28.822</v>
+        <v>20.746</v>
       </c>
     </row>
     <row r="506">
@@ -25239,10 +25239,10 @@
         <v>6.043</v>
       </c>
       <c r="L506" t="n">
-        <v>-7</v>
+        <v>-2.485</v>
       </c>
       <c r="M506" t="n">
-        <v>30.034</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="507">
@@ -25284,10 +25284,10 @@
         <v>5.409</v>
       </c>
       <c r="L507" t="n">
-        <v>-9</v>
+        <v>-4.013</v>
       </c>
       <c r="M507" t="n">
-        <v>28.48</v>
+        <v>20.494</v>
       </c>
     </row>
     <row r="508">
@@ -25329,10 +25329,10 @@
         <v>5.84</v>
       </c>
       <c r="L508" t="n">
-        <v>-9</v>
+        <v>-3.863</v>
       </c>
       <c r="M508" t="n">
-        <v>29.536</v>
+        <v>21.334</v>
       </c>
     </row>
     <row r="509">
@@ -25374,10 +25374,10 @@
         <v>5.392</v>
       </c>
       <c r="L509" t="n">
-        <v>-9</v>
+        <v>-4.018</v>
       </c>
       <c r="M509" t="n">
-        <v>28.622</v>
+        <v>20.581</v>
       </c>
     </row>
     <row r="510">
@@ -25419,10 +25419,10 @@
         <v>4.823</v>
       </c>
       <c r="L510" t="n">
-        <v>-9</v>
+        <v>-4.215</v>
       </c>
       <c r="M510" t="n">
-        <v>27.364</v>
+        <v>19.562</v>
       </c>
     </row>
     <row r="511">
@@ -25464,10 +25464,10 @@
         <v>5.686</v>
       </c>
       <c r="L511" t="n">
-        <v>-9</v>
+        <v>-3.917</v>
       </c>
       <c r="M511" t="n">
-        <v>29.256</v>
+        <v>21.098</v>
       </c>
     </row>
     <row r="512">
@@ -25509,10 +25509,10 @@
         <v>5.466</v>
       </c>
       <c r="L512" t="n">
-        <v>-7</v>
+        <v>-2.685</v>
       </c>
       <c r="M512" t="n">
-        <v>28.402</v>
+        <v>20.463</v>
       </c>
     </row>
     <row r="513">
@@ -25554,10 +25554,10 @@
         <v>4.947</v>
       </c>
       <c r="L513" t="n">
-        <v>-9</v>
+        <v>-4.172</v>
       </c>
       <c r="M513" t="n">
-        <v>27.13</v>
+        <v>19.452</v>
       </c>
     </row>
     <row r="514">
@@ -25599,10 +25599,10 @@
         <v>4.982</v>
       </c>
       <c r="L514" t="n">
-        <v>-9</v>
+        <v>-4.16</v>
       </c>
       <c r="M514" t="n">
-        <v>23.34</v>
+        <v>16.986</v>
       </c>
     </row>
     <row r="515">
@@ -25644,10 +25644,10 @@
         <v>5.343</v>
       </c>
       <c r="L515" t="n">
-        <v>-9</v>
+        <v>-4.035</v>
       </c>
       <c r="M515" t="n">
-        <v>24.98</v>
+        <v>18.183</v>
       </c>
     </row>
     <row r="516">
@@ -25689,10 +25689,10 @@
         <v>5.207</v>
       </c>
       <c r="L516" t="n">
-        <v>-9</v>
+        <v>-4.082</v>
       </c>
       <c r="M516" t="n">
-        <v>27.704</v>
+        <v>19.917</v>
       </c>
     </row>
     <row r="517">
@@ -25734,10 +25734,10 @@
         <v>5.854</v>
       </c>
       <c r="L517" t="n">
-        <v>-9</v>
+        <v>-3.859</v>
       </c>
       <c r="M517" t="n">
-        <v>29.148</v>
+        <v>21.085</v>
       </c>
     </row>
     <row r="518">
@@ -25779,10 +25779,10 @@
         <v>5.201</v>
       </c>
       <c r="L518" t="n">
-        <v>-9</v>
+        <v>-4.085</v>
       </c>
       <c r="M518" t="n">
-        <v>27.838</v>
+        <v>20.003</v>
       </c>
     </row>
     <row r="519">
@@ -25824,10 +25824,10 @@
         <v>5.595</v>
       </c>
       <c r="L519" t="n">
-        <v>-9</v>
+        <v>-3.948</v>
       </c>
       <c r="M519" t="n">
-        <v>25.61</v>
+        <v>18.682</v>
       </c>
     </row>
     <row r="520">
@@ -25869,10 +25869,10 @@
         <v>5.141</v>
       </c>
       <c r="L520" t="n">
-        <v>-9</v>
+        <v>-4.105</v>
       </c>
       <c r="M520" t="n">
-        <v>27.668</v>
+        <v>19.871</v>
       </c>
     </row>
     <row r="521">
@@ -25914,10 +25914,10 @@
         <v>5.275</v>
       </c>
       <c r="L521" t="n">
-        <v>-9</v>
+        <v>-4.059</v>
       </c>
       <c r="M521" t="n">
-        <v>27.918</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="522">
@@ -25959,10 +25959,10 @@
         <v>5.082</v>
       </c>
       <c r="L522" t="n">
-        <v>-9</v>
+        <v>-4.126</v>
       </c>
       <c r="M522" t="n">
-        <v>24.568</v>
+        <v>17.823</v>
       </c>
     </row>
     <row r="523">
@@ -26004,10 +26004,10 @@
         <v>6.089</v>
       </c>
       <c r="L523" t="n">
-        <v>-7</v>
+        <v>-2.469</v>
       </c>
       <c r="M523" t="n">
-        <v>29.872</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="524">
@@ -26049,10 +26049,10 @@
         <v>5.14</v>
       </c>
       <c r="L524" t="n">
-        <v>-9</v>
+        <v>-4.106</v>
       </c>
       <c r="M524" t="n">
-        <v>27.696</v>
+        <v>19.889</v>
       </c>
     </row>
     <row r="525">
@@ -26094,10 +26094,10 @@
         <v>6.003</v>
       </c>
       <c r="L525" t="n">
-        <v>-7</v>
+        <v>-2.499</v>
       </c>
       <c r="M525" t="n">
-        <v>29.428</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="526">
@@ -26139,10 +26139,10 @@
         <v>5.271</v>
       </c>
       <c r="L526" t="n">
-        <v>-9</v>
+        <v>-4.06</v>
       </c>
       <c r="M526" t="n">
-        <v>24.818</v>
+        <v>18.052</v>
       </c>
     </row>
     <row r="527">
@@ -26184,10 +26184,10 @@
         <v>5.445</v>
       </c>
       <c r="L527" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="M527" t="n">
-        <v>28.398</v>
+        <v>20.453</v>
       </c>
     </row>
     <row r="528">
@@ -26229,10 +26229,10 @@
         <v>5.105</v>
       </c>
       <c r="L528" t="n">
-        <v>-9</v>
+        <v>-4.118</v>
       </c>
       <c r="M528" t="n">
-        <v>26.524</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="529">
@@ -26274,10 +26274,10 @@
         <v>4.996</v>
       </c>
       <c r="L529" t="n">
-        <v>-9</v>
+        <v>-4.155</v>
       </c>
       <c r="M529" t="n">
-        <v>26.19</v>
+        <v>18.854</v>
       </c>
     </row>
     <row r="530">
@@ -26319,10 +26319,10 @@
         <v>5.235</v>
       </c>
       <c r="L530" t="n">
-        <v>-9</v>
+        <v>-4.073</v>
       </c>
       <c r="M530" t="n">
-        <v>27.786</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="531">
@@ -26364,10 +26364,10 @@
         <v>4.645</v>
       </c>
       <c r="L531" t="n">
-        <v>-9</v>
+        <v>-4.277</v>
       </c>
       <c r="M531" t="n">
-        <v>23.524</v>
+        <v>16.989</v>
       </c>
     </row>
     <row r="532">
@@ -26409,10 +26409,10 @@
         <v>6</v>
       </c>
       <c r="L532" t="n">
-        <v>-9</v>
+        <v>-3.808</v>
       </c>
       <c r="M532" t="n">
-        <v>29.738</v>
+        <v>21.521</v>
       </c>
     </row>
     <row r="533">
@@ -26454,10 +26454,10 @@
         <v>4.697</v>
       </c>
       <c r="L533" t="n">
-        <v>-9</v>
+        <v>-4.259</v>
       </c>
       <c r="M533" t="n">
-        <v>22.476</v>
+        <v>16.322</v>
       </c>
     </row>
     <row r="534">
@@ -26499,10 +26499,10 @@
         <v>5.562</v>
       </c>
       <c r="L534" t="n">
-        <v>-9</v>
+        <v>-3.96</v>
       </c>
       <c r="M534" t="n">
-        <v>29.098</v>
+        <v>20.951</v>
       </c>
     </row>
     <row r="535">
@@ -26544,10 +26544,10 @@
         <v>5.039</v>
       </c>
       <c r="L535" t="n">
-        <v>-9</v>
+        <v>-4.141</v>
       </c>
       <c r="M535" t="n">
-        <v>26.27</v>
+        <v>18.921</v>
       </c>
     </row>
     <row r="536">
@@ -26589,10 +26589,10 @@
         <v>4.677</v>
       </c>
       <c r="L536" t="n">
-        <v>-9</v>
+        <v>-4.266</v>
       </c>
       <c r="M536" t="n">
-        <v>22.654</v>
+        <v>16.432</v>
       </c>
     </row>
     <row r="537">
@@ -26634,10 +26634,10 @@
         <v>4.623</v>
       </c>
       <c r="L537" t="n">
-        <v>-9</v>
+        <v>-4.285</v>
       </c>
       <c r="M537" t="n">
-        <v>22.336</v>
+        <v>16.205</v>
       </c>
     </row>
     <row r="538">
@@ -26679,10 +26679,10 @@
         <v>5.659</v>
       </c>
       <c r="L538" t="n">
-        <v>-9</v>
+        <v>-3.926</v>
       </c>
       <c r="M538" t="n">
-        <v>28.918</v>
+        <v>20.867</v>
       </c>
     </row>
     <row r="539">
@@ -26724,10 +26724,10 @@
         <v>5.263</v>
       </c>
       <c r="L539" t="n">
-        <v>-9</v>
+        <v>-4.063</v>
       </c>
       <c r="M539" t="n">
-        <v>27.81</v>
+        <v>20.006</v>
       </c>
     </row>
     <row r="540">
@@ -26769,10 +26769,10 @@
         <v>5.544</v>
       </c>
       <c r="L540" t="n">
-        <v>-9</v>
+        <v>-3.966</v>
       </c>
       <c r="M540" t="n">
-        <v>28.784</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="541">
@@ -26814,10 +26814,10 @@
         <v>5.254</v>
       </c>
       <c r="L541" t="n">
-        <v>-9</v>
+        <v>-4.066</v>
       </c>
       <c r="M541" t="n">
-        <v>26.796</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="542">
@@ -26859,10 +26859,10 @@
         <v>5.446</v>
       </c>
       <c r="L542" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="M542" t="n">
-        <v>28.484</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="543">
@@ -26904,10 +26904,10 @@
         <v>4.762</v>
       </c>
       <c r="L543" t="n">
-        <v>-9</v>
+        <v>-4.236</v>
       </c>
       <c r="M543" t="n">
-        <v>26.742</v>
+        <v>19.134</v>
       </c>
     </row>
     <row r="544">
@@ -26949,10 +26949,10 @@
         <v>5.051</v>
       </c>
       <c r="L544" t="n">
-        <v>-9</v>
+        <v>-4.136</v>
       </c>
       <c r="M544" t="n">
-        <v>24.428</v>
+        <v>17.721</v>
       </c>
     </row>
     <row r="545">
@@ -26994,10 +26994,10 @@
         <v>5.299</v>
       </c>
       <c r="L545" t="n">
-        <v>-9</v>
+        <v>-4.051</v>
       </c>
       <c r="M545" t="n">
-        <v>27.926</v>
+        <v>20.094</v>
       </c>
     </row>
   </sheetData>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -550,10 +550,10 @@
         <v>120.76</v>
       </c>
       <c r="J2" t="n">
-        <v>72.59999999999999</v>
+        <v>47.1</v>
       </c>
       <c r="K2" t="n">
-        <v>181.79</v>
+        <v>214.1</v>
       </c>
       <c r="L2" t="n">
         <v>42</v>
@@ -610,10 +610,10 @@
         <v>112.98</v>
       </c>
       <c r="J3" t="n">
-        <v>71.47</v>
+        <v>49.5</v>
       </c>
       <c r="K3" t="n">
-        <v>179.6</v>
+        <v>214.86</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
@@ -670,10 +670,10 @@
         <v>110.81</v>
       </c>
       <c r="J4" t="n">
-        <v>70</v>
+        <v>48.4</v>
       </c>
       <c r="K4" t="n">
-        <v>179.98</v>
+        <v>216.6</v>
       </c>
       <c r="L4" t="n">
         <v>42</v>
@@ -730,10 +730,10 @@
         <v>107.54</v>
       </c>
       <c r="J5" t="n">
-        <v>69</v>
+        <v>48.6</v>
       </c>
       <c r="K5" t="n">
-        <v>176.39</v>
+        <v>212.84</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
@@ -790,10 +790,10 @@
         <v>106.48</v>
       </c>
       <c r="J6" t="n">
-        <v>67.39</v>
+        <v>46.7</v>
       </c>
       <c r="K6" t="n">
-        <v>173.44</v>
+        <v>208.88</v>
       </c>
       <c r="L6" t="n">
         <v>45</v>
@@ -850,10 +850,10 @@
         <v>104.02</v>
       </c>
       <c r="J7" t="n">
-        <v>66.02</v>
+        <v>45.9</v>
       </c>
       <c r="K7" t="n">
-        <v>169.16</v>
+        <v>203.64</v>
       </c>
       <c r="L7" t="n">
         <v>39</v>
@@ -910,10 +910,10 @@
         <v>103.18</v>
       </c>
       <c r="J8" t="n">
-        <v>67.88</v>
+        <v>49.2</v>
       </c>
       <c r="K8" t="n">
-        <v>174.28</v>
+        <v>211.92</v>
       </c>
       <c r="L8" t="n">
         <v>41</v>
@@ -970,10 +970,10 @@
         <v>103</v>
       </c>
       <c r="J9" t="n">
-        <v>56.12</v>
+        <v>31.3</v>
       </c>
       <c r="K9" t="n">
-        <v>152.14</v>
+        <v>178.16</v>
       </c>
       <c r="L9" t="n">
         <v>39</v>
@@ -1030,10 +1030,10 @@
         <v>100.84</v>
       </c>
       <c r="J10" t="n">
-        <v>53.47</v>
+        <v>28.4</v>
       </c>
       <c r="K10" t="n">
-        <v>172.44</v>
+        <v>210.34</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
@@ -1090,10 +1090,10 @@
         <v>99.76000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>65.06999999999999</v>
+        <v>46.7</v>
       </c>
       <c r="K11" t="n">
-        <v>169.21</v>
+        <v>205.98</v>
       </c>
       <c r="L11" t="n">
         <v>44</v>
@@ -1150,10 +1150,10 @@
         <v>99.56</v>
       </c>
       <c r="J12" t="n">
-        <v>54.21</v>
+        <v>30.2</v>
       </c>
       <c r="K12" t="n">
-        <v>147.7</v>
+        <v>173.18</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
@@ -1210,10 +1210,10 @@
         <v>99.52</v>
       </c>
       <c r="J13" t="n">
-        <v>65.18000000000001</v>
+        <v>47</v>
       </c>
       <c r="K13" t="n">
-        <v>169.84</v>
+        <v>207.06</v>
       </c>
       <c r="L13" t="n">
         <v>39</v>
@@ -1270,10 +1270,10 @@
         <v>98.69</v>
       </c>
       <c r="J14" t="n">
-        <v>52.86</v>
+        <v>28.6</v>
       </c>
       <c r="K14" t="n">
-        <v>146.94</v>
+        <v>172.48</v>
       </c>
       <c r="L14" t="n">
         <v>41</v>
@@ -1330,10 +1330,10 @@
         <v>97.5</v>
       </c>
       <c r="J15" t="n">
-        <v>61.15</v>
+        <v>41.9</v>
       </c>
       <c r="K15" t="n">
-        <v>165.45</v>
+        <v>201.42</v>
       </c>
       <c r="L15" t="n">
         <v>41</v>
@@ -1390,10 +1390,10 @@
         <v>96.83</v>
       </c>
       <c r="J16" t="n">
-        <v>61.44</v>
+        <v>42.7</v>
       </c>
       <c r="K16" t="n">
-        <v>163.19</v>
+        <v>198.32</v>
       </c>
       <c r="L16" t="n">
         <v>40</v>
@@ -1450,10 +1450,10 @@
         <v>96.52</v>
       </c>
       <c r="J17" t="n">
-        <v>52.17</v>
+        <v>28.7</v>
       </c>
       <c r="K17" t="n">
-        <v>143.86</v>
+        <v>168.92</v>
       </c>
       <c r="L17" t="n">
         <v>40</v>
@@ -1510,10 +1510,10 @@
         <v>96.38</v>
       </c>
       <c r="J18" t="n">
-        <v>61.54</v>
+        <v>43.1</v>
       </c>
       <c r="K18" t="n">
-        <v>163.62</v>
+        <v>199.22</v>
       </c>
       <c r="L18" t="n">
         <v>41</v>
@@ -1570,10 +1570,10 @@
         <v>92.67</v>
       </c>
       <c r="J19" t="n">
-        <v>48.82</v>
+        <v>25.6</v>
       </c>
       <c r="K19" t="n">
-        <v>139.48</v>
+        <v>164.26</v>
       </c>
       <c r="L19" t="n">
         <v>39</v>
@@ -1630,10 +1630,10 @@
         <v>92.5</v>
       </c>
       <c r="J20" t="n">
-        <v>48.49</v>
+        <v>25.2</v>
       </c>
       <c r="K20" t="n">
-        <v>139.33</v>
+        <v>164.12</v>
       </c>
       <c r="L20" t="n">
         <v>42</v>
@@ -1690,10 +1690,10 @@
         <v>91.54000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>47.18</v>
+        <v>23.7</v>
       </c>
       <c r="K21" t="n">
-        <v>138.59</v>
+        <v>163.5</v>
       </c>
       <c r="L21" t="n">
         <v>39</v>
@@ -1750,10 +1750,10 @@
         <v>91.15000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>48.94</v>
+        <v>26.6</v>
       </c>
       <c r="K22" t="n">
-        <v>125.55</v>
+        <v>143.76</v>
       </c>
       <c r="L22" t="n">
         <v>41</v>
@@ -1810,10 +1810,10 @@
         <v>91</v>
       </c>
       <c r="J23" t="n">
-        <v>57.78</v>
+        <v>40.2</v>
       </c>
       <c r="K23" t="n">
-        <v>160.22</v>
+        <v>196.86</v>
       </c>
       <c r="L23" t="n">
         <v>41</v>
@@ -1870,10 +1870,10 @@
         <v>90.45</v>
       </c>
       <c r="J24" t="n">
-        <v>47.2</v>
+        <v>24.3</v>
       </c>
       <c r="K24" t="n">
-        <v>136.58</v>
+        <v>161</v>
       </c>
       <c r="L24" t="n">
         <v>37</v>
@@ -1930,10 +1930,10 @@
         <v>90.03</v>
       </c>
       <c r="J25" t="n">
-        <v>34.69</v>
+        <v>5.4</v>
       </c>
       <c r="K25" t="n">
-        <v>126.94</v>
+        <v>146.48</v>
       </c>
       <c r="L25" t="n">
         <v>37</v>
@@ -1990,10 +1990,10 @@
         <v>89.73999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>47.87</v>
+        <v>25.7</v>
       </c>
       <c r="K26" t="n">
-        <v>124.02</v>
+        <v>142.16</v>
       </c>
       <c r="L26" t="n">
         <v>39</v>
@@ -2050,10 +2050,10 @@
         <v>88.77</v>
       </c>
       <c r="J27" t="n">
-        <v>45.57</v>
+        <v>22.7</v>
       </c>
       <c r="K27" t="n">
-        <v>157.13</v>
+        <v>193.32</v>
       </c>
       <c r="L27" t="n">
         <v>38</v>
@@ -2110,10 +2110,10 @@
         <v>87.75</v>
       </c>
       <c r="J28" t="n">
-        <v>46.2</v>
+        <v>24.2</v>
       </c>
       <c r="K28" t="n">
-        <v>121.55</v>
+        <v>139.44</v>
       </c>
       <c r="L28" t="n">
         <v>42</v>
@@ -2170,10 +2170,10 @@
         <v>86.5</v>
       </c>
       <c r="J29" t="n">
-        <v>54.53</v>
+        <v>37.6</v>
       </c>
       <c r="K29" t="n">
-        <v>154.63</v>
+        <v>190.7</v>
       </c>
       <c r="L29" t="n">
         <v>41</v>
@@ -2230,10 +2230,10 @@
         <v>86.28</v>
       </c>
       <c r="J30" t="n">
-        <v>43.14</v>
+        <v>20.3</v>
       </c>
       <c r="K30" t="n">
-        <v>132.27</v>
+        <v>156.62</v>
       </c>
       <c r="L30" t="n">
         <v>39</v>
@@ -2290,10 +2290,10 @@
         <v>84.91</v>
       </c>
       <c r="J31" t="n">
-        <v>43.38</v>
+        <v>21.4</v>
       </c>
       <c r="K31" t="n">
-        <v>152.04</v>
+        <v>187.58</v>
       </c>
       <c r="L31" t="n">
         <v>39</v>
@@ -2350,10 +2350,10 @@
         <v>83.70999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>42.25</v>
+        <v>20.3</v>
       </c>
       <c r="K32" t="n">
-        <v>117.25</v>
+        <v>135</v>
       </c>
       <c r="L32" t="n">
         <v>38</v>
@@ -2410,10 +2410,10 @@
         <v>83.02</v>
       </c>
       <c r="J33" t="n">
-        <v>41.16</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>116.82</v>
+        <v>134.72</v>
       </c>
       <c r="L33" t="n">
         <v>36</v>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,45 +475,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>espn_sacks</t>
+          <t>draft_sharks_fpts</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>espn_ints</t>
+          <t>fpts_gap</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>espn_fr</t>
+          <t>vlahakis</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>espn_td</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>espn_pa</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>espn_ya</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>espn_fantasy_pts</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>vlahakis</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
         <is>
           <t>williams</t>
         </is>
@@ -556,28 +531,13 @@
         <v>210.5</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>331</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5505</v>
-      </c>
-      <c r="R2" t="n">
-        <v>117</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,28 +576,13 @@
         <v>212.64</v>
       </c>
       <c r="L3" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>318</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5439</v>
-      </c>
-      <c r="R3" t="n">
-        <v>114</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>-14.16</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -676,28 +621,13 @@
         <v>217.56</v>
       </c>
       <c r="L4" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
-      </c>
-      <c r="N4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>322</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5469</v>
-      </c>
-      <c r="R4" t="n">
-        <v>117</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>-17.33</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -736,28 +666,13 @@
         <v>208.94</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>319</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5495</v>
-      </c>
-      <c r="R5" t="n">
-        <v>117</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -796,28 +711,13 @@
         <v>208.62</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>330</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5507</v>
-      </c>
-      <c r="R6" t="n">
-        <v>113</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+        <v>-12.69</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -856,28 +756,13 @@
         <v>204.52</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>370</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5826</v>
-      </c>
-      <c r="R7" t="n">
-        <v>94</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+        <v>-8.4</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -916,28 +801,13 @@
         <v>212.14</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>373</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5897</v>
-      </c>
-      <c r="R8" t="n">
-        <v>88</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -976,28 +846,13 @@
         <v>210.56</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>332</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5464</v>
-      </c>
-      <c r="R9" t="n">
-        <v>113</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+        <v>-11.48</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1036,28 +891,13 @@
         <v>177.86</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>411</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6099</v>
-      </c>
-      <c r="R10" t="n">
-        <v>91</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+        <v>2.69</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1096,28 +936,13 @@
         <v>206.3</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>333</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5569</v>
-      </c>
-      <c r="R11" t="n">
-        <v>106</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+        <v>-11.92</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1156,28 +981,13 @@
         <v>207.16</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="M12" t="n">
-        <v>13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>388</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5894</v>
-      </c>
-      <c r="R12" t="n">
-        <v>93</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+        <v>-11.97</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1216,28 +1026,13 @@
         <v>203.96</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>336</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5688</v>
-      </c>
-      <c r="R13" t="n">
-        <v>112</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+        <v>-13.88</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1276,28 +1071,13 @@
         <v>202.56</v>
       </c>
       <c r="L14" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>352</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5722</v>
-      </c>
-      <c r="R14" t="n">
-        <v>91</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+        <v>-18.26</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1336,28 +1116,13 @@
         <v>168.96</v>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
-      </c>
-      <c r="N15" t="n">
-        <v>9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>380</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5948</v>
-      </c>
-      <c r="R15" t="n">
-        <v>90</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+        <v>-18.71</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1396,28 +1161,13 @@
         <v>194.5</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>359</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5696</v>
-      </c>
-      <c r="R16" t="n">
-        <v>91</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+        <v>-13.99</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1456,28 +1206,13 @@
         <v>169.24</v>
       </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5946</v>
-      </c>
-      <c r="R17" t="n">
-        <v>86</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+        <v>-15.56</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1516,28 +1251,13 @@
         <v>168.44</v>
       </c>
       <c r="L18" t="n">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="M18" t="n">
-        <v>13</v>
-      </c>
-      <c r="N18" t="n">
-        <v>10</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>377</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5894</v>
-      </c>
-      <c r="R18" t="n">
-        <v>97</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+        <v>-13.57</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1576,28 +1296,13 @@
         <v>199.38</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
-      </c>
-      <c r="N19" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>413</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6130</v>
-      </c>
-      <c r="R19" t="n">
-        <v>91</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+        <v>-16.2</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1636,28 +1341,13 @@
         <v>169.3</v>
       </c>
       <c r="L20" t="n">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>341</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5679</v>
-      </c>
-      <c r="R20" t="n">
-        <v>89</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+        <v>-13.5</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1696,28 +1386,13 @@
         <v>198.78</v>
       </c>
       <c r="L21" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>406</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6048</v>
-      </c>
-      <c r="R21" t="n">
-        <v>86</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+        <v>-7.66</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1756,28 +1431,13 @@
         <v>164.76</v>
       </c>
       <c r="L22" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="M22" t="n">
-        <v>12</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>362</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5892</v>
-      </c>
-      <c r="R22" t="n">
-        <v>87</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+        <v>-9.81</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1816,28 +1476,13 @@
         <v>164.62</v>
       </c>
       <c r="L23" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>366</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5846</v>
-      </c>
-      <c r="R23" t="n">
-        <v>87</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+        <v>-13.27</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1876,28 +1521,13 @@
         <v>143.4</v>
       </c>
       <c r="L24" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>404</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5981</v>
-      </c>
-      <c r="R24" t="n">
-        <v>97</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+        <v>-14.43</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1936,28 +1566,13 @@
         <v>160.86</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5761</v>
-      </c>
-      <c r="R25" t="n">
-        <v>88</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+        <v>-18.14</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1996,28 +1611,13 @@
         <v>144.96</v>
       </c>
       <c r="L26" t="n">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="M26" t="n">
-        <v>11</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5888</v>
-      </c>
-      <c r="R26" t="n">
-        <v>81</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+        <v>-9.98</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2056,28 +1656,13 @@
         <v>155.84</v>
       </c>
       <c r="L27" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>10</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>441</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6142</v>
-      </c>
-      <c r="R27" t="n">
-        <v>96</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+        <v>-11.73</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2116,28 +1701,13 @@
         <v>191.2</v>
       </c>
       <c r="L28" t="n">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="M28" t="n">
-        <v>12</v>
-      </c>
-      <c r="N28" t="n">
-        <v>7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>368</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5847</v>
-      </c>
-      <c r="R28" t="n">
-        <v>91</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+        <v>-22.84</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2176,28 +1746,13 @@
         <v>138.82</v>
       </c>
       <c r="L29" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="M29" t="n">
-        <v>11</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>461</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6357</v>
-      </c>
-      <c r="R29" t="n">
-        <v>66</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+        <v>-12.71</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2236,28 +1791,13 @@
         <v>187.9</v>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="M30" t="n">
-        <v>11</v>
-      </c>
-      <c r="N30" t="n">
-        <v>8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>371</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5904</v>
-      </c>
-      <c r="R30" t="n">
-        <v>95</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+        <v>-17.87</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2296,28 +1836,13 @@
         <v>154.98</v>
       </c>
       <c r="L31" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="M31" t="n">
-        <v>11</v>
-      </c>
-      <c r="N31" t="n">
-        <v>9</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>383</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5872</v>
-      </c>
-      <c r="R31" t="n">
-        <v>91</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+        <v>-22.98</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2356,28 +1881,13 @@
         <v>137.28</v>
       </c>
       <c r="L32" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="M32" t="n">
-        <v>11</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2</v>
-      </c>
-      <c r="P32" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5965</v>
-      </c>
-      <c r="R32" t="n">
-        <v>86</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+        <v>-18.84</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2416,28 +1926,13 @@
         <v>130.46</v>
       </c>
       <c r="L33" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>12</v>
-      </c>
-      <c r="N33" t="n">
-        <v>8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2</v>
-      </c>
-      <c r="P33" t="n">
-        <v>454</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6279</v>
-      </c>
-      <c r="R33" t="n">
-        <v>88</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+        <v>-20.27</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -531,10 +531,10 @@
         <v>210.5</v>
       </c>
       <c r="L2" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.19</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -576,10 +576,10 @@
         <v>212.64</v>
       </c>
       <c r="L3" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="M3" t="n">
-        <v>-14.16</v>
+        <v>-7.16</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -621,10 +621,10 @@
         <v>217.56</v>
       </c>
       <c r="L4" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M4" t="n">
-        <v>-17.33</v>
+        <v>-14.33</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -666,10 +666,10 @@
         <v>208.94</v>
       </c>
       <c r="L5" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.550000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -711,10 +711,10 @@
         <v>208.62</v>
       </c>
       <c r="L6" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.69</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -756,10 +756,10 @@
         <v>204.52</v>
       </c>
       <c r="L7" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.4</v>
+        <v>5.6</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -801,10 +801,10 @@
         <v>212.14</v>
       </c>
       <c r="L8" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6899999999999999</v>
+        <v>10.31</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -846,10 +846,10 @@
         <v>210.56</v>
       </c>
       <c r="L9" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.48</v>
+        <v>0.52</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -891,10 +891,10 @@
         <v>177.86</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="M10" t="n">
-        <v>2.69</v>
+        <v>13.69</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -936,10 +936,10 @@
         <v>206.3</v>
       </c>
       <c r="L11" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.92</v>
+        <v>2.08</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -981,10 +981,10 @@
         <v>207.16</v>
       </c>
       <c r="L12" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.97</v>
+        <v>-0.97</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         <v>203.96</v>
       </c>
       <c r="L13" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.88</v>
+        <v>0.12</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
         <v>202.56</v>
       </c>
       <c r="L14" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.26</v>
+        <v>-10.26</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1116,10 +1116,10 @@
         <v>168.96</v>
       </c>
       <c r="L15" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="M15" t="n">
-        <v>-18.71</v>
+        <v>-10.71</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         <v>194.5</v>
       </c>
       <c r="L16" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="M16" t="n">
-        <v>-13.99</v>
+        <v>-1.99</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         <v>169.24</v>
       </c>
       <c r="L17" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.56</v>
+        <v>-3.56</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         <v>168.44</v>
       </c>
       <c r="L18" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="M18" t="n">
-        <v>-13.57</v>
+        <v>-2.57</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         <v>199.38</v>
       </c>
       <c r="L19" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="M19" t="n">
-        <v>-16.2</v>
+        <v>-2.2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         <v>169.3</v>
       </c>
       <c r="L20" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="M20" t="n">
-        <v>-13.5</v>
+        <v>-5.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         <v>198.78</v>
       </c>
       <c r="L21" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.66</v>
+        <v>4.34</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         <v>164.76</v>
       </c>
       <c r="L22" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="M22" t="n">
-        <v>-9.81</v>
+        <v>1.19</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         <v>164.62</v>
       </c>
       <c r="L23" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="M23" t="n">
-        <v>-13.27</v>
+        <v>-3.27</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1521,10 +1521,10 @@
         <v>143.4</v>
       </c>
       <c r="L24" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.43</v>
+        <v>-4.43</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         <v>160.86</v>
       </c>
       <c r="L25" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.14</v>
+        <v>-5.14</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         <v>144.96</v>
       </c>
       <c r="L26" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.98</v>
+        <v>-1.98</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         <v>155.84</v>
       </c>
       <c r="L27" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="M27" t="n">
-        <v>-11.73</v>
+        <v>-1.73</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         <v>191.2</v>
       </c>
       <c r="L28" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="M28" t="n">
-        <v>-22.84</v>
+        <v>-11.84</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
         <v>138.82</v>
       </c>
       <c r="L29" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M29" t="n">
-        <v>-12.71</v>
+        <v>-1.71</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1791,10 +1791,10 @@
         <v>187.9</v>
       </c>
       <c r="L30" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="M30" t="n">
-        <v>-17.87</v>
+        <v>-6.87</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         <v>154.98</v>
       </c>
       <c r="L31" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="M31" t="n">
-        <v>-22.98</v>
+        <v>-10.98</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         <v>137.28</v>
       </c>
       <c r="L32" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="M32" t="n">
-        <v>-18.84</v>
+        <v>-9.84</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         <v>130.46</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M33" t="n">
-        <v>-20.27</v>
+        <v>-13.27</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
